--- a/database/event/5206/event_5206_evp_summary.xlsx
+++ b/database/event/5206/event_5206_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.4635</v>
+        <v>6.3053</v>
       </c>
       <c r="C2" t="n">
-        <v>2.6856</v>
+        <v>2.6199</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1897</v>
+        <v>2.0681</v>
       </c>
       <c r="E2" t="n">
-        <v>6.4635</v>
+        <v>6.3053</v>
       </c>
       <c r="F2" t="n">
-        <v>6.4635</v>
+        <v>6.3053</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>7.843</v>
+        <v>7.5836</v>
       </c>
       <c r="I2" t="n">
         <v>8.1777</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.1555</v>
+        <v>5.1008</v>
       </c>
       <c r="C3" t="n">
-        <v>2.1422</v>
+        <v>2.1194</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6613</v>
+        <v>1.5882</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1555</v>
+        <v>5.1008</v>
       </c>
       <c r="F3" t="n">
-        <v>5.1555</v>
+        <v>5.1008</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>5.7808</v>
+        <v>5.695</v>
       </c>
       <c r="I3" t="n">
         <v>5.8891</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.2731</v>
+        <v>4.2109</v>
       </c>
       <c r="C4" t="n">
-        <v>1.7755</v>
+        <v>1.7497</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3049</v>
+        <v>1.2337</v>
       </c>
       <c r="E4" t="n">
-        <v>4.2731</v>
+        <v>4.2109</v>
       </c>
       <c r="F4" t="n">
-        <v>4.2731</v>
+        <v>4.2109</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>4.3972</v>
+        <v>4.2997</v>
       </c>
       <c r="I4" t="n">
         <v>4.5214</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.0715</v>
+        <v>4.0205</v>
       </c>
       <c r="C5" t="n">
-        <v>1.6917</v>
+        <v>1.6706</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2234</v>
+        <v>1.1579</v>
       </c>
       <c r="E5" t="n">
-        <v>4.0715</v>
+        <v>4.0205</v>
       </c>
       <c r="F5" t="n">
-        <v>4.0715</v>
+        <v>4.0205</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4.0811</v>
+        <v>4.0205</v>
       </c>
       <c r="I5" t="n">
         <v>4.1576</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.4244</v>
+        <v>2.3354</v>
       </c>
       <c r="C6" t="n">
-        <v>1.0074</v>
+        <v>0.9704</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.4865</v>
       </c>
       <c r="E6" t="n">
-        <v>2.4244</v>
+        <v>2.3354</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4244</v>
+        <v>2.3354</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2.4244</v>
+        <v>2.3354</v>
       </c>
       <c r="I6" t="n">
         <v>2.5396</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.3067</v>
+        <v>2.281</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9585</v>
+        <v>0.9478</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5105</v>
+        <v>0.4648</v>
       </c>
       <c r="E7" t="n">
-        <v>2.3067</v>
+        <v>2.281</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3067</v>
+        <v>2.281</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2.3067</v>
+        <v>2.281</v>
       </c>
       <c r="I7" t="n">
         <v>2.339</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.2748</v>
+        <v>2.241</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9452</v>
+        <v>0.9312</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4976</v>
+        <v>0.4489</v>
       </c>
       <c r="E8" t="n">
-        <v>2.2748</v>
+        <v>2.241</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2748</v>
+        <v>2.241</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.2748</v>
+        <v>2.241</v>
       </c>
       <c r="I8" t="n">
         <v>2.3174</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.0424</v>
+        <v>2.0272</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8486</v>
+        <v>0.8423</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4037</v>
+        <v>0.3637</v>
       </c>
       <c r="E9" t="n">
-        <v>2.0424</v>
+        <v>2.0272</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0424</v>
+        <v>2.0272</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.0424</v>
+        <v>2.0272</v>
       </c>
       <c r="I9" t="n">
         <v>2.0615</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.0384</v>
+        <v>1.9932</v>
       </c>
       <c r="C10" t="n">
-        <v>0.847</v>
+        <v>0.8282</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4021</v>
+        <v>0.3502</v>
       </c>
       <c r="E10" t="n">
-        <v>2.0384</v>
+        <v>1.9932</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0384</v>
+        <v>1.9932</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.0384</v>
+        <v>1.9932</v>
       </c>
       <c r="I10" t="n">
         <v>2.096</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.8577</v>
+        <v>1.8301</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7719</v>
+        <v>0.7604</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3291</v>
+        <v>0.2852</v>
       </c>
       <c r="E11" t="n">
-        <v>1.8577</v>
+        <v>1.8301</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8577</v>
+        <v>1.8301</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.8577</v>
+        <v>1.8301</v>
       </c>
       <c r="I11" t="n">
         <v>1.8925</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.5433</v>
+        <v>1.5318</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6413</v>
+        <v>0.6365</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2021</v>
+        <v>0.1664</v>
       </c>
       <c r="E12" t="n">
-        <v>1.5433</v>
+        <v>1.5318</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5433</v>
+        <v>1.5318</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.5433</v>
+        <v>1.5318</v>
       </c>
       <c r="I12" t="n">
         <v>1.5577</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.011</v>
+        <v>0.9997</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4201</v>
+        <v>0.4154</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0129</v>
+        <v>-0.0456</v>
       </c>
       <c r="E13" t="n">
-        <v>1.011</v>
+        <v>0.9997</v>
       </c>
       <c r="F13" t="n">
-        <v>1.011</v>
+        <v>0.9997</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.011</v>
+        <v>0.9997</v>
       </c>
       <c r="I13" t="n">
         <v>1.0252</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9673</v>
+        <v>0.9565</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4019</v>
+        <v>0.3974</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0306</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9673</v>
+        <v>0.9565</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9673</v>
+        <v>0.9565</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9673</v>
+        <v>0.9565</v>
       </c>
       <c r="I14" t="n">
         <v>0.9809</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8774</v>
+        <v>0.8611</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3646</v>
+        <v>0.3578</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0669</v>
+        <v>-0.1008</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8774</v>
+        <v>0.8611</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8774</v>
+        <v>0.8611</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8774</v>
+        <v>0.8611</v>
       </c>
       <c r="I15" t="n">
         <v>0.898</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8579</v>
+        <v>0.8547</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3565</v>
+        <v>0.3551</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.07480000000000001</v>
+        <v>-0.1034</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8579</v>
+        <v>0.8547</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8579</v>
+        <v>0.8547</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8579</v>
+        <v>0.8547</v>
       </c>
       <c r="I16" t="n">
         <v>0.8619</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8092</v>
+        <v>0.7883</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3362</v>
+        <v>0.3275</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0945</v>
+        <v>-0.1299</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8092</v>
+        <v>0.7883</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8092</v>
+        <v>0.7883</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8092</v>
+        <v>0.7883</v>
       </c>
       <c r="I17" t="n">
         <v>0.8359</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7466</v>
+        <v>0.7327</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3102</v>
+        <v>0.3044</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1198</v>
+        <v>-0.152</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7466</v>
+        <v>0.7327</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7466</v>
+        <v>0.7327</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7466</v>
+        <v>0.7327</v>
       </c>
       <c r="I18" t="n">
         <v>0.7641</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.6584</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2808</v>
+        <v>0.2736</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1483</v>
+        <v>-0.1816</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.6584</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.6584</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.6584</v>
       </c>
       <c r="I19" t="n">
         <v>0.6982</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5444</v>
+        <v>0.5303</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2262</v>
+        <v>0.2203</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2014</v>
+        <v>-0.2326</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5444</v>
+        <v>0.5303</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5444</v>
+        <v>0.5303</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5444</v>
+        <v>0.5303</v>
       </c>
       <c r="I20" t="n">
         <v>0.5623</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.4346</v>
+        <v>0.433</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1806</v>
+        <v>0.1799</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2458</v>
+        <v>-0.2714</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4346</v>
+        <v>0.433</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4346</v>
+        <v>0.433</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4346</v>
+        <v>0.433</v>
       </c>
       <c r="I21" t="n">
         <v>0.4366</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2865</v>
+        <v>0.2802</v>
       </c>
       <c r="C22" t="n">
-        <v>0.119</v>
+        <v>0.1164</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3056</v>
+        <v>-0.3323</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2865</v>
+        <v>0.2802</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2865</v>
+        <v>0.2802</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2865</v>
+        <v>0.2802</v>
       </c>
       <c r="I22" t="n">
         <v>0.2946</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1879</v>
+        <v>0.1831</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0781</v>
+        <v>0.0761</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3455</v>
+        <v>-0.371</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1879</v>
+        <v>0.1831</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1879</v>
+        <v>0.1831</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1879</v>
+        <v>0.1831</v>
       </c>
       <c r="I23" t="n">
         <v>0.1941</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1838</v>
+        <v>0.1791</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0764</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3471</v>
+        <v>-0.3726</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1838</v>
+        <v>0.1791</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1838</v>
+        <v>0.1791</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1838</v>
+        <v>0.1791</v>
       </c>
       <c r="I24" t="n">
         <v>0.1899</v>
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1231</v>
+        <v>0.1217</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0511</v>
+        <v>0.0506</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3716</v>
+        <v>-0.3954</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1231</v>
+        <v>0.1217</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1231</v>
+        <v>0.1217</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1231</v>
+        <v>0.1217</v>
       </c>
       <c r="I25" t="n">
         <v>0.1248</v>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0663</v>
+        <v>0.0655</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0275</v>
+        <v>0.0272</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3946</v>
+        <v>-0.4178</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0663</v>
+        <v>0.0655</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0663</v>
+        <v>0.0655</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0663</v>
+        <v>0.0655</v>
       </c>
       <c r="I26" t="n">
         <v>0.0672</v>
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0339</v>
+        <v>0.0335</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0141</v>
+        <v>0.0139</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4077</v>
+        <v>-0.4306</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0339</v>
+        <v>0.0335</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0339</v>
+        <v>0.0335</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0339</v>
+        <v>0.0335</v>
       </c>
       <c r="I27" t="n">
         <v>0.0344</v>
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.3694</v>
+        <v>-0.3612</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1535</v>
+        <v>-0.1501</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5706</v>
+        <v>-0.5878</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.3694</v>
+        <v>-0.3612</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.3694</v>
+        <v>-0.3612</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.3694</v>
+        <v>-0.3612</v>
       </c>
       <c r="I28" t="n">
         <v>-0.3798</v>
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.5854</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.2432</v>
+        <v>-0.2415</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6579</v>
+        <v>-0.6754</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.5854</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.5854</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.5854</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="I29" t="n">
         <v>-0.5909</v>
@@ -1784,25 +1784,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.6211</v>
+        <v>-0.6165</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2581</v>
+        <v>-0.2562</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6723</v>
+        <v>-0.6895</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.6211</v>
+        <v>-0.6165</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.6211</v>
+        <v>-0.6165</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.6211</v>
+        <v>-0.6165</v>
       </c>
       <c r="I30" t="n">
         <v>-0.6269</v>
@@ -1830,25 +1830,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.8423</v>
+        <v>-0.8236</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.35</v>
+        <v>-0.3422</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7616000000000001</v>
+        <v>-0.772</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.8423</v>
+        <v>-0.8236</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.8423</v>
+        <v>-0.8236</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.8423</v>
+        <v>-0.8236</v>
       </c>
       <c r="I31" t="n">
         <v>-0.8661</v>
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-1.1356</v>
+        <v>-1.1229</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.4719</v>
+        <v>-0.4666</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8801</v>
+        <v>-0.8913</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.1356</v>
+        <v>-1.1229</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.1356</v>
+        <v>-1.1229</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.1356</v>
+        <v>-1.1229</v>
       </c>
       <c r="I32" t="n">
         <v>-1.1515</v>
@@ -1922,25 +1922,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.3896</v>
+        <v>-1.3741</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.5774</v>
+        <v>-0.571</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9827</v>
+        <v>-0.9913999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.3896</v>
+        <v>-1.3741</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.3896</v>
+        <v>-1.3741</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.3896</v>
+        <v>-1.3741</v>
       </c>
       <c r="I33" t="n">
         <v>-1.4091</v>
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.4307</v>
+        <v>-1.4042</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.5945</v>
+        <v>-0.5835</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9993</v>
+        <v>-1.0033</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.4307</v>
+        <v>-1.4042</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.4307</v>
+        <v>-1.4042</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.4307</v>
+        <v>-1.4042</v>
       </c>
       <c r="I34" t="n">
         <v>-1.4643</v>
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.5216</v>
+        <v>-1.5046</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.6322</v>
+        <v>-0.6252</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0361</v>
+        <v>-1.0433</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.5216</v>
+        <v>-1.5046</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.5216</v>
+        <v>-1.5046</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.5216</v>
+        <v>-1.5046</v>
       </c>
       <c r="I35" t="n">
         <v>-1.5429</v>
@@ -2060,25 +2060,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.5934</v>
+        <v>-1.5816</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.6621</v>
+        <v>-0.6572</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0651</v>
+        <v>-1.074</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.5934</v>
+        <v>-1.5816</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.5934</v>
+        <v>-1.5816</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.5934</v>
+        <v>-1.5816</v>
       </c>
       <c r="I36" t="n">
         <v>-1.6083</v>
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.6618</v>
+        <v>-1.6494</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.6905</v>
+        <v>-0.6853</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0927</v>
+        <v>-1.101</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.6618</v>
+        <v>-1.6494</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.6618</v>
+        <v>-1.6494</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.6618</v>
+        <v>-1.6494</v>
       </c>
       <c r="I37" t="n">
         <v>-1.6773</v>
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.8582</v>
+        <v>-1.8375</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.7721</v>
+        <v>-0.7635</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.172</v>
+        <v>-1.176</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.8582</v>
+        <v>-1.8375</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.8582</v>
+        <v>-1.8375</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.8582</v>
+        <v>-1.8375</v>
       </c>
       <c r="I38" t="n">
         <v>-1.8843</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.0251</v>
+        <v>-1.9951</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.8414</v>
+        <v>-0.829</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2395</v>
+        <v>-1.2388</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.0251</v>
+        <v>-1.9951</v>
       </c>
       <c r="F39" t="n">
-        <v>-2.0251</v>
+        <v>-1.9951</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-2.0251</v>
+        <v>-1.9951</v>
       </c>
       <c r="I39" t="n">
         <v>-2.0631</v>
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.2842</v>
+        <v>-2.2587</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.9491000000000001</v>
+        <v>-0.9385</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3441</v>
+        <v>-1.3438</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.2842</v>
+        <v>-2.2587</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.2842</v>
+        <v>-2.2587</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.2842</v>
+        <v>-2.2587</v>
       </c>
       <c r="I40" t="n">
         <v>-2.3162</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.4539</v>
+        <v>-2.4265</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.0196</v>
+        <v>-1.0082</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4127</v>
+        <v>-1.4106</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.4539</v>
+        <v>-2.4265</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.4539</v>
+        <v>-2.4265</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.4539</v>
+        <v>-2.4265</v>
       </c>
       <c r="I41" t="n">
         <v>-2.4883</v>
@@ -2336,25 +2336,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-2.5586</v>
+        <v>-2.5396</v>
       </c>
       <c r="C42" t="n">
-        <v>-1.0631</v>
+        <v>-1.0552</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.455</v>
+        <v>-1.4557</v>
       </c>
       <c r="E42" t="n">
-        <v>-2.5586</v>
+        <v>-2.5396</v>
       </c>
       <c r="F42" t="n">
-        <v>-2.5586</v>
+        <v>-2.5396</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>-2.5586</v>
+        <v>-2.5396</v>
       </c>
       <c r="I42" t="n">
         <v>-2.5825</v>
@@ -2382,25 +2382,25 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-3.4136</v>
+        <v>-3.3629</v>
       </c>
       <c r="C43" t="n">
-        <v>-1.4184</v>
+        <v>-1.3973</v>
       </c>
       <c r="D43" t="n">
-        <v>-1.8004</v>
+        <v>-1.7837</v>
       </c>
       <c r="E43" t="n">
-        <v>-3.4136</v>
+        <v>-3.3629</v>
       </c>
       <c r="F43" t="n">
-        <v>-3.4136</v>
+        <v>-3.3629</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-3.4136</v>
+        <v>-3.3629</v>
       </c>
       <c r="I43" t="n">
         <v>-3.4776</v>

--- a/database/event/5206/event_5206_evp_summary.xlsx
+++ b/database/event/5206/event_5206_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.3053</v>
+        <v>4.9573</v>
       </c>
       <c r="C2" t="n">
-        <v>2.6199</v>
+        <v>2.0598</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0681</v>
+        <v>1.6</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3053</v>
+        <v>4.9573</v>
       </c>
       <c r="F2" t="n">
-        <v>6.3053</v>
+        <v>4.9573</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>7.5836</v>
+        <v>7.5254</v>
       </c>
       <c r="I2" t="n">
-        <v>8.1777</v>
+        <v>10.8159</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>8.1777</v>
+        <v>10.8159</v>
       </c>
       <c r="N2" t="n">
         <v>347</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.1008</v>
+        <v>3.9122</v>
       </c>
       <c r="C3" t="n">
-        <v>2.1194</v>
+        <v>1.6256</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5882</v>
+        <v>1.1281</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1008</v>
+        <v>3.9122</v>
       </c>
       <c r="F3" t="n">
-        <v>5.1008</v>
+        <v>3.9122</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>5.695</v>
+        <v>5.2307</v>
       </c>
       <c r="I3" t="n">
-        <v>5.8891</v>
+        <v>6.1457</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>5.8891</v>
+        <v>6.1457</v>
       </c>
       <c r="N3" t="n">
         <v>246</v>
@@ -584,323 +584,323 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.2109</v>
+        <v>3.8052</v>
       </c>
       <c r="C4" t="n">
-        <v>1.7497</v>
+        <v>1.5811</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2337</v>
+        <v>1.0798</v>
       </c>
       <c r="E4" t="n">
-        <v>4.2109</v>
+        <v>3.8052</v>
       </c>
       <c r="F4" t="n">
-        <v>4.2109</v>
+        <v>3.8052</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>4.2997</v>
+        <v>4.9957</v>
       </c>
       <c r="I4" t="n">
-        <v>4.5214</v>
+        <v>5.8696</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>286</v>
+        <v>164</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>4.5214</v>
+        <v>5.8696</v>
       </c>
       <c r="N4" t="n">
-        <v>286</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.0205</v>
+        <v>3.3751</v>
       </c>
       <c r="C5" t="n">
-        <v>1.6706</v>
+        <v>1.4024</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1579</v>
+        <v>0.8857</v>
       </c>
       <c r="E5" t="n">
-        <v>4.0205</v>
+        <v>3.3751</v>
       </c>
       <c r="F5" t="n">
-        <v>4.0205</v>
+        <v>3.3751</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4.0205</v>
+        <v>4.0513</v>
       </c>
       <c r="I5" t="n">
-        <v>4.1576</v>
+        <v>5.1596</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>164</v>
+        <v>286</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4.1576</v>
+        <v>5.1596</v>
       </c>
       <c r="N5" t="n">
-        <v>164</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.3354</v>
+        <v>2.6512</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9704</v>
+        <v>1.1016</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4865</v>
+        <v>0.5589</v>
       </c>
       <c r="E6" t="n">
-        <v>2.3354</v>
+        <v>2.6512</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3354</v>
+        <v>2.6512</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2.3354</v>
+        <v>2.6512</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5396</v>
+        <v>3.3765</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>335</v>
+        <v>402</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.5396</v>
+        <v>3.3765</v>
       </c>
       <c r="N6" t="n">
-        <v>335</v>
+        <v>402</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.281</v>
+        <v>2.5527</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9478</v>
+        <v>1.0607</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4648</v>
+        <v>0.5144</v>
       </c>
       <c r="E7" t="n">
-        <v>2.281</v>
+        <v>2.5527</v>
       </c>
       <c r="F7" t="n">
-        <v>2.281</v>
+        <v>2.5527</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2.281</v>
+        <v>2.5527</v>
       </c>
       <c r="I7" t="n">
-        <v>2.339</v>
+        <v>2.9993</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>214</v>
+        <v>356</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.339</v>
+        <v>2.9993</v>
       </c>
       <c r="N7" t="n">
-        <v>214</v>
+        <v>356</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.241</v>
+        <v>2.4352</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9312</v>
+        <v>1.0118</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4489</v>
+        <v>0.4614</v>
       </c>
       <c r="E8" t="n">
-        <v>2.241</v>
+        <v>2.4352</v>
       </c>
       <c r="F8" t="n">
-        <v>2.241</v>
+        <v>2.4352</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.241</v>
+        <v>2.4352</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3174</v>
+        <v>2.7482</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>356</v>
+        <v>214</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.3174</v>
+        <v>2.7482</v>
       </c>
       <c r="N8" t="n">
-        <v>356</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.0272</v>
+        <v>2.2565</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8423</v>
+        <v>0.9376</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3637</v>
+        <v>0.3807</v>
       </c>
       <c r="E9" t="n">
-        <v>2.0272</v>
+        <v>2.2565</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0272</v>
+        <v>2.2565</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.0272</v>
+        <v>2.2565</v>
       </c>
       <c r="I9" t="n">
-        <v>2.0615</v>
+        <v>3.3766</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>161</v>
+        <v>335</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.0615</v>
+        <v>3.3766</v>
       </c>
       <c r="N9" t="n">
-        <v>161</v>
+        <v>335</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.9932</v>
+        <v>2.1894</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8282</v>
+        <v>0.9097</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3502</v>
+        <v>0.3504</v>
       </c>
       <c r="E10" t="n">
-        <v>1.9932</v>
+        <v>2.1894</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9932</v>
+        <v>2.1894</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1.9932</v>
+        <v>2.1894</v>
       </c>
       <c r="I10" t="n">
-        <v>2.096</v>
+        <v>2.3732</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>402</v>
+        <v>161</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.096</v>
+        <v>2.3732</v>
       </c>
       <c r="N10" t="n">
-        <v>402</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11">
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.8301</v>
+        <v>1.6792</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7604</v>
+        <v>0.6977</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2852</v>
+        <v>0.1201</v>
       </c>
       <c r="E11" t="n">
-        <v>1.8301</v>
+        <v>1.6792</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8301</v>
+        <v>1.6792</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.8301</v>
+        <v>1.6792</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8925</v>
+        <v>1.973</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.8925</v>
+        <v>1.973</v>
       </c>
       <c r="N11" t="n">
         <v>248</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.5318</v>
+        <v>1.4996</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6365</v>
+        <v>0.6231</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1664</v>
+        <v>0.039</v>
       </c>
       <c r="E12" t="n">
-        <v>1.5318</v>
+        <v>1.4996</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5318</v>
+        <v>1.4996</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.5318</v>
+        <v>1.4996</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5577</v>
+        <v>1.6255</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.5577</v>
+        <v>1.6255</v>
       </c>
       <c r="N12" t="n">
         <v>161</v>
@@ -998,277 +998,277 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9997</v>
+        <v>1.3042</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4154</v>
+        <v>0.5419</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0456</v>
+        <v>-0.0492</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9997</v>
+        <v>1.3042</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9997</v>
+        <v>1.3042</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9997</v>
+        <v>1.3042</v>
       </c>
       <c r="I13" t="n">
-        <v>1.0252</v>
+        <v>1.4718</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.0252</v>
+        <v>1.4718</v>
       </c>
       <c r="N13" t="n">
-        <v>205</v>
+        <v>214</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9565</v>
+        <v>1.1886</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3974</v>
+        <v>0.4939</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.06279999999999999</v>
+        <v>-0.1014</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9565</v>
+        <v>1.1886</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9565</v>
+        <v>1.1886</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9565</v>
+        <v>1.1886</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9809</v>
+        <v>1.576</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>214</v>
+        <v>333</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9809</v>
+        <v>1.576</v>
       </c>
       <c r="N14" t="n">
-        <v>214</v>
+        <v>333</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8611</v>
+        <v>1.1595</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3578</v>
+        <v>0.4818</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1008</v>
+        <v>-0.1146</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8611</v>
+        <v>1.1595</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8611</v>
+        <v>1.1595</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8611</v>
+        <v>1.1595</v>
       </c>
       <c r="I15" t="n">
-        <v>0.898</v>
+        <v>1.3085</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>171</v>
+        <v>205</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.898</v>
+        <v>1.3085</v>
       </c>
       <c r="N15" t="n">
-        <v>171</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8547</v>
+        <v>1.109</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3551</v>
+        <v>0.4608</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1034</v>
+        <v>-0.1374</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8547</v>
+        <v>1.109</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8547</v>
+        <v>1.109</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8547</v>
+        <v>1.109</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8619</v>
+        <v>1.3566</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>172</v>
+        <v>300</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8619</v>
+        <v>1.3566</v>
       </c>
       <c r="N16" t="n">
-        <v>172</v>
+        <v>300</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7883</v>
+        <v>0.9748</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3275</v>
+        <v>0.405</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1299</v>
+        <v>-0.1979</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7883</v>
+        <v>0.9748</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7883</v>
+        <v>0.9748</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7883</v>
+        <v>0.9748</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8359</v>
+        <v>1.0149</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>261</v>
+        <v>172</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8359</v>
+        <v>1.0149</v>
       </c>
       <c r="N17" t="n">
-        <v>261</v>
+        <v>172</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7327</v>
+        <v>0.8933</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3044</v>
+        <v>0.3712</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.152</v>
+        <v>-0.2347</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7327</v>
+        <v>0.8933</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7327</v>
+        <v>0.8933</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7327</v>
+        <v>0.8933</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7641</v>
+        <v>1.0927</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>300</v>
+        <v>171</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7641</v>
+        <v>1.0927</v>
       </c>
       <c r="N18" t="n">
-        <v>300</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19">
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6584</v>
+        <v>0.8719</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2736</v>
+        <v>0.3623</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1816</v>
+        <v>-0.2444</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6584</v>
+        <v>0.8719</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6584</v>
+        <v>0.8719</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6584</v>
+        <v>0.8719</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6982</v>
+        <v>1.1561</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6982</v>
+        <v>1.1561</v>
       </c>
       <c r="N19" t="n">
         <v>298</v>
@@ -1320,47 +1320,47 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5303</v>
+        <v>0.7873</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2203</v>
+        <v>0.3271</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2326</v>
+        <v>-0.2826</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5303</v>
+        <v>0.7873</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5303</v>
+        <v>0.7873</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5303</v>
+        <v>0.7873</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5623</v>
+        <v>1.0439</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>333</v>
+        <v>261</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5623</v>
+        <v>1.0439</v>
       </c>
       <c r="N20" t="n">
-        <v>333</v>
+        <v>261</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.433</v>
+        <v>0.7426</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1799</v>
+        <v>0.3086</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2714</v>
+        <v>-0.3028</v>
       </c>
       <c r="E21" t="n">
-        <v>0.433</v>
+        <v>0.7426</v>
       </c>
       <c r="F21" t="n">
-        <v>0.433</v>
+        <v>0.7426</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.433</v>
+        <v>0.7426</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4366</v>
+        <v>0.7731</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4366</v>
+        <v>0.7731</v>
       </c>
       <c r="N21" t="n">
         <v>160</v>
@@ -1412,170 +1412,170 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2802</v>
+        <v>0.6433</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1164</v>
+        <v>0.2673</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3323</v>
+        <v>-0.3476</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2802</v>
+        <v>0.6433</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2802</v>
+        <v>0.6433</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2802</v>
+        <v>0.6433</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2946</v>
+        <v>0.853</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2946</v>
+        <v>0.853</v>
       </c>
       <c r="N22" t="n">
-        <v>298</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1831</v>
+        <v>0.552</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0761</v>
+        <v>0.2294</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.371</v>
+        <v>-0.3888</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1831</v>
+        <v>0.552</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1831</v>
+        <v>0.552</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1831</v>
+        <v>0.552</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1941</v>
+        <v>0.703</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1941</v>
+        <v>0.703</v>
       </c>
       <c r="N23" t="n">
-        <v>286</v>
+        <v>298</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1791</v>
+        <v>0.5159</v>
       </c>
       <c r="C24" t="n">
-        <v>0.07439999999999999</v>
+        <v>0.2144</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3726</v>
+        <v>-0.4051</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1791</v>
+        <v>0.5159</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1791</v>
+        <v>0.5159</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1791</v>
+        <v>0.5159</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1899</v>
+        <v>0.5822000000000001</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>262</v>
+        <v>205</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1899</v>
+        <v>0.5822000000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>262</v>
+        <v>205</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1217</v>
+        <v>0.4116</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0506</v>
+        <v>0.171</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3954</v>
+        <v>-0.4522</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1217</v>
+        <v>0.4116</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1217</v>
+        <v>0.4116</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1217</v>
+        <v>0.4116</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1248</v>
+        <v>0.4645</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1248</v>
+        <v>0.4645</v>
       </c>
       <c r="N25" t="n">
         <v>205</v>
@@ -1596,47 +1596,47 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0655</v>
+        <v>0.4096</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0272</v>
+        <v>0.1702</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4178</v>
+        <v>-0.4531</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0655</v>
+        <v>0.4096</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0655</v>
+        <v>0.4096</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0655</v>
+        <v>0.4096</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0672</v>
+        <v>0.5431</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>205</v>
+        <v>262</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0672</v>
+        <v>0.5431</v>
       </c>
       <c r="N26" t="n">
-        <v>205</v>
+        <v>262</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0335</v>
+        <v>0.3515</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0139</v>
+        <v>0.1461</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4306</v>
+        <v>-0.4793</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0335</v>
+        <v>0.3515</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0335</v>
+        <v>0.3515</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0335</v>
+        <v>0.3515</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0344</v>
+        <v>0.3967</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0344</v>
+        <v>0.3967</v>
       </c>
       <c r="N27" t="n">
         <v>214</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.3612</v>
+        <v>0.3193</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1501</v>
+        <v>0.1327</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5878</v>
+        <v>-0.4939</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.3612</v>
+        <v>0.3193</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.3612</v>
+        <v>0.3193</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.3612</v>
+        <v>0.3193</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.3798</v>
+        <v>0.4066</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.3798</v>
+        <v>0.4066</v>
       </c>
       <c r="N28" t="n">
         <v>332</v>
@@ -1734,32 +1734,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>VINI</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.5810999999999999</v>
+        <v>-0.2059</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.2415</v>
+        <v>-0.0856</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6754</v>
+        <v>-0.731</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.5810999999999999</v>
+        <v>-0.2059</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.5810999999999999</v>
+        <v>-0.2059</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.5810999999999999</v>
+        <v>-0.2059</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.5909</v>
+        <v>-0.2232</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.5909</v>
+        <v>-0.2232</v>
       </c>
       <c r="N29" t="n">
         <v>161</v>
@@ -1780,369 +1780,369 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>VINI</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.6165</v>
+        <v>-0.2849</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2562</v>
+        <v>-0.1184</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6895</v>
+        <v>-0.7665999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.6165</v>
+        <v>-0.2849</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.6165</v>
+        <v>-0.2849</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.6165</v>
+        <v>-0.2849</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.6269</v>
+        <v>-0.3629</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>161</v>
+        <v>250</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.6269</v>
+        <v>-0.3629</v>
       </c>
       <c r="N30" t="n">
-        <v>161</v>
+        <v>250</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.8236</v>
+        <v>-0.3529</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.3422</v>
+        <v>-0.1466</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.772</v>
+        <v>-0.7973</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.8236</v>
+        <v>-0.3529</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.8236</v>
+        <v>-0.3529</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.8236</v>
+        <v>-0.3529</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8661</v>
+        <v>-0.3983</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>250</v>
+        <v>205</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.8661</v>
+        <v>-0.3983</v>
       </c>
       <c r="N31" t="n">
-        <v>250</v>
+        <v>205</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-1.1229</v>
+        <v>-0.3649</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.4666</v>
+        <v>-0.1516</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8913</v>
+        <v>-0.8027</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.1229</v>
+        <v>-0.3649</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.1229</v>
+        <v>-0.3649</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.1229</v>
+        <v>-0.3649</v>
       </c>
       <c r="I32" t="n">
-        <v>-1.1515</v>
+        <v>-0.3955</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>205</v>
+        <v>161</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-1.1515</v>
+        <v>-0.3955</v>
       </c>
       <c r="N32" t="n">
-        <v>205</v>
+        <v>161</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>misutaaa</t>
+          <t>amanek</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.3741</v>
+        <v>-0.7511</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.571</v>
+        <v>-0.3121</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9913999999999999</v>
+        <v>-0.9771</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.3741</v>
+        <v>-0.7511</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.3741</v>
+        <v>-0.7511</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.3741</v>
+        <v>-0.7511</v>
       </c>
       <c r="I33" t="n">
-        <v>-1.4091</v>
+        <v>-0.8476</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>106</v>
+        <v>214</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-1.4091</v>
+        <v>-0.8476</v>
       </c>
       <c r="N33" t="n">
-        <v>106</v>
+        <v>214</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>misutaaa</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.4042</v>
+        <v>-1.0179</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.5835</v>
+        <v>-0.4229</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.0033</v>
+        <v>-1.0975</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.4042</v>
+        <v>-1.0179</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.4042</v>
+        <v>-1.0179</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.4042</v>
+        <v>-1.0179</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.4643</v>
+        <v>-1.1487</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>172</v>
+        <v>106</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.4643</v>
+        <v>-1.1487</v>
       </c>
       <c r="N34" t="n">
-        <v>172</v>
+        <v>106</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>amanek</t>
+          <t>Nivera</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.5046</v>
+        <v>-1.1239</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.6252</v>
+        <v>-0.467</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0433</v>
+        <v>-1.1454</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.5046</v>
+        <v>-1.1239</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.5046</v>
+        <v>-1.1239</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.5046</v>
+        <v>-1.1239</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.5429</v>
+        <v>-1.2182</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>214</v>
+        <v>167</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.5429</v>
+        <v>-1.2182</v>
       </c>
       <c r="N35" t="n">
-        <v>214</v>
+        <v>167</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>honda</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.5816</v>
+        <v>-1.1886</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.6572</v>
+        <v>-0.4939</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.074</v>
+        <v>-1.1746</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.5816</v>
+        <v>-1.1886</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.5816</v>
+        <v>-1.1886</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.5816</v>
+        <v>-1.1886</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.6083</v>
+        <v>-1.3965</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>161</v>
+        <v>217</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.6083</v>
+        <v>-1.3965</v>
       </c>
       <c r="N36" t="n">
-        <v>161</v>
+        <v>217</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Nivera</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.6494</v>
+        <v>-1.2109</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.6853</v>
+        <v>-0.5031</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.101</v>
+        <v>-1.1847</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.6494</v>
+        <v>-1.2109</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.6494</v>
+        <v>-1.2109</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.6494</v>
+        <v>-1.2109</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.6773</v>
+        <v>-1.4813</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.6773</v>
+        <v>-1.4813</v>
       </c>
       <c r="N37" t="n">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="38">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.8375</v>
+        <v>-1.2197</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.7635</v>
+        <v>-0.5068</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.176</v>
+        <v>-1.1886</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.8375</v>
+        <v>-1.2197</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.8375</v>
+        <v>-1.2197</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.8375</v>
+        <v>-1.2197</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.8843</v>
+        <v>-1.3765</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.8843</v>
+        <v>-1.3765</v>
       </c>
       <c r="N38" t="n">
         <v>205</v>
@@ -2194,47 +2194,47 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>honda</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.9951</v>
+        <v>-1.294</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.829</v>
+        <v>-0.5377</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2388</v>
+        <v>-1.2222</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.9951</v>
+        <v>-1.294</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.9951</v>
+        <v>-1.294</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.9951</v>
+        <v>-1.294</v>
       </c>
       <c r="I39" t="n">
-        <v>-2.0631</v>
+        <v>-1.4026</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>217</v>
+        <v>161</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-2.0631</v>
+        <v>-1.4026</v>
       </c>
       <c r="N39" t="n">
-        <v>217</v>
+        <v>161</v>
       </c>
     </row>
     <row r="40">
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.2587</v>
+        <v>-1.5798</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.9385</v>
+        <v>-0.6564</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3438</v>
+        <v>-1.3512</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.2587</v>
+        <v>-1.5798</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.2587</v>
+        <v>-1.5798</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.2587</v>
+        <v>-1.5798</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.3162</v>
+        <v>-1.7828</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.3162</v>
+        <v>-1.7828</v>
       </c>
       <c r="N40" t="n">
         <v>214</v>
@@ -2286,93 +2286,93 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>JUGi</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.4265</v>
+        <v>-1.8815</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.0082</v>
+        <v>-0.7818000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4106</v>
+        <v>-1.4874</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.4265</v>
+        <v>-1.8815</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.4265</v>
+        <v>-1.8815</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.4265</v>
+        <v>-1.8815</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.4883</v>
+        <v>-2.0394</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>76</v>
+        <v>145</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.4883</v>
+        <v>-2.0394</v>
       </c>
       <c r="N41" t="n">
-        <v>76</v>
+        <v>145</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>JUGi</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-2.5396</v>
+        <v>-2.1218</v>
       </c>
       <c r="C42" t="n">
-        <v>-1.0552</v>
+        <v>-0.8816000000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.4557</v>
+        <v>-1.5959</v>
       </c>
       <c r="E42" t="n">
-        <v>-2.5396</v>
+        <v>-2.1218</v>
       </c>
       <c r="F42" t="n">
-        <v>-2.5396</v>
+        <v>-2.1218</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>-2.5396</v>
+        <v>-2.1218</v>
       </c>
       <c r="I42" t="n">
-        <v>-2.5825</v>
+        <v>-2.3945</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>145</v>
+        <v>76</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>-2.5825</v>
+        <v>-2.3945</v>
       </c>
       <c r="N42" t="n">
-        <v>145</v>
+        <v>76</v>
       </c>
     </row>
     <row r="43">
@@ -2382,28 +2382,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-3.3629</v>
+        <v>-2.8636</v>
       </c>
       <c r="C43" t="n">
-        <v>-1.3973</v>
+        <v>-1.1899</v>
       </c>
       <c r="D43" t="n">
-        <v>-1.7837</v>
+        <v>-1.9308</v>
       </c>
       <c r="E43" t="n">
-        <v>-3.3629</v>
+        <v>-2.8636</v>
       </c>
       <c r="F43" t="n">
-        <v>-3.3629</v>
+        <v>-2.8636</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-3.3629</v>
+        <v>-2.8636</v>
       </c>
       <c r="I43" t="n">
-        <v>-3.4776</v>
+        <v>-3.3646</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>-3.4776</v>
+        <v>-3.3646</v>
       </c>
       <c r="N43" t="n">
         <v>100</v>
@@ -2521,10 +2521,10 @@
         <v>1.53</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7327</v>
+        <v>0.9169</v>
       </c>
       <c r="J2" t="n">
-        <v>20.5156</v>
+        <v>25.6732</v>
       </c>
     </row>
     <row r="3">
@@ -2561,10 +2561,10 @@
         <v>1.4</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5795</v>
+        <v>0.717</v>
       </c>
       <c r="J3" t="n">
-        <v>16.226</v>
+        <v>20.076</v>
       </c>
     </row>
     <row r="4">
@@ -2601,10 +2601,10 @@
         <v>1.28</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4227</v>
+        <v>0.5254</v>
       </c>
       <c r="J4" t="n">
-        <v>11.8356</v>
+        <v>14.7112</v>
       </c>
     </row>
     <row r="5">
@@ -2641,10 +2641,10 @@
         <v>1.01</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0402</v>
+        <v>0.002</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.1256</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="6">
@@ -2681,10 +2681,10 @@
         <v>0.85</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3515</v>
+        <v>-0.2103</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.842000000000001</v>
+        <v>-5.8884</v>
       </c>
     </row>
     <row r="7">
@@ -2721,10 +2721,10 @@
         <v>0.83</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5178</v>
+        <v>-0.5034</v>
       </c>
       <c r="J7" t="n">
-        <v>-14.4984</v>
+        <v>-14.0952</v>
       </c>
     </row>
     <row r="8">
@@ -2761,10 +2761,10 @@
         <v>1.06</v>
       </c>
       <c r="I8" t="n">
-        <v>0.358</v>
+        <v>0.2812</v>
       </c>
       <c r="J8" t="n">
-        <v>10.024</v>
+        <v>7.8736</v>
       </c>
     </row>
     <row r="9">
@@ -2801,10 +2801,10 @@
         <v>1.02</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2151</v>
+        <v>0.1388</v>
       </c>
       <c r="J9" t="n">
-        <v>6.0228</v>
+        <v>3.8864</v>
       </c>
     </row>
     <row r="10">
@@ -2841,10 +2841,10 @@
         <v>0.95</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1065</v>
+        <v>-0.1646</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.982</v>
+        <v>-4.6088</v>
       </c>
     </row>
     <row r="11">
@@ -2881,10 +2881,10 @@
         <v>0.51</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.2793</v>
+        <v>-1.2927</v>
       </c>
       <c r="J11" t="n">
-        <v>-35.8204</v>
+        <v>-36.1956</v>
       </c>
     </row>
     <row r="12">
@@ -2921,10 +2921,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6872</v>
+        <v>-0.4606</v>
       </c>
       <c r="J12" t="n">
-        <v>-14.4312</v>
+        <v>-9.672599999999999</v>
       </c>
     </row>
     <row r="13">
@@ -2961,10 +2961,10 @@
         <v>1.35</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6006</v>
+        <v>0.7245</v>
       </c>
       <c r="J13" t="n">
-        <v>12.6126</v>
+        <v>15.2145</v>
       </c>
     </row>
     <row r="14">
@@ -3001,10 +3001,10 @@
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0.03</v>
+        <v>0.0078</v>
       </c>
       <c r="J14" t="n">
-        <v>0.63</v>
+        <v>0.1638</v>
       </c>
     </row>
     <row r="15">
@@ -3041,10 +3041,10 @@
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>0.03</v>
+        <v>0.0078</v>
       </c>
       <c r="J15" t="n">
-        <v>0.63</v>
+        <v>0.1638</v>
       </c>
     </row>
     <row r="16">
@@ -3081,10 +3081,10 @@
         <v>0.85</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2949</v>
+        <v>-0.1824</v>
       </c>
       <c r="J16" t="n">
-        <v>-6.1929</v>
+        <v>-3.8304</v>
       </c>
     </row>
     <row r="17">
@@ -3121,10 +3121,10 @@
         <v>0.16</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.936</v>
+        <v>-2.0714</v>
       </c>
       <c r="J17" t="n">
-        <v>-40.656</v>
+        <v>-43.4994</v>
       </c>
     </row>
     <row r="18">
@@ -3161,10 +3161,10 @@
         <v>1.05</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4795</v>
+        <v>0.4064</v>
       </c>
       <c r="J18" t="n">
-        <v>10.0695</v>
+        <v>8.5344</v>
       </c>
     </row>
     <row r="19">
@@ -3201,10 +3201,10 @@
         <v>0.98</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1637</v>
+        <v>0.0806</v>
       </c>
       <c r="J19" t="n">
-        <v>3.4377</v>
+        <v>1.6926</v>
       </c>
     </row>
     <row r="20">
@@ -3241,10 +3241,10 @@
         <v>0.6</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.982</v>
+        <v>-0.9994</v>
       </c>
       <c r="J20" t="n">
-        <v>-20.622</v>
+        <v>-20.9874</v>
       </c>
     </row>
     <row r="21">
@@ -3281,10 +3281,10 @@
         <v>0.57</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0579</v>
+        <v>-1.072</v>
       </c>
       <c r="J21" t="n">
-        <v>-22.2159</v>
+        <v>-22.512</v>
       </c>
     </row>
     <row r="22">
@@ -3321,10 +3321,10 @@
         <v>1.15</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2974</v>
+        <v>0.3364</v>
       </c>
       <c r="J22" t="n">
-        <v>10.7064</v>
+        <v>12.1104</v>
       </c>
     </row>
     <row r="23">
@@ -3361,10 +3361,10 @@
         <v>1.09</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1975</v>
+        <v>0.2188</v>
       </c>
       <c r="J23" t="n">
-        <v>7.11</v>
+        <v>7.8768</v>
       </c>
     </row>
     <row r="24">
@@ -3401,10 +3401,10 @@
         <v>0.89</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.254</v>
+        <v>-0.1488</v>
       </c>
       <c r="J24" t="n">
-        <v>-9.144</v>
+        <v>-5.3568</v>
       </c>
     </row>
     <row r="25">
@@ -3441,10 +3441,10 @@
         <v>1.21</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3869</v>
+        <v>0.4471</v>
       </c>
       <c r="J25" t="n">
-        <v>13.9284</v>
+        <v>16.0956</v>
       </c>
     </row>
     <row r="26">
@@ -3481,10 +3481,10 @@
         <v>0.82</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3619</v>
+        <v>-0.2225</v>
       </c>
       <c r="J26" t="n">
-        <v>-13.0284</v>
+        <v>-8.01</v>
       </c>
     </row>
     <row r="27">
@@ -3521,10 +3521,10 @@
         <v>0.83</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.5698</v>
+        <v>-0.5286999999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>-20.5128</v>
+        <v>-19.0332</v>
       </c>
     </row>
     <row r="28">
@@ -3561,10 +3561,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.9134</v>
+        <v>-0.8852</v>
       </c>
       <c r="J28" t="n">
-        <v>-32.8824</v>
+        <v>-31.8672</v>
       </c>
     </row>
     <row r="29">
@@ -3601,10 +3601,10 @@
         <v>0.65</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.0033</v>
+        <v>-0.9829</v>
       </c>
       <c r="J29" t="n">
-        <v>-36.1188</v>
+        <v>-35.3844</v>
       </c>
     </row>
     <row r="30">
@@ -3641,10 +3641,10 @@
         <v>1.37</v>
       </c>
       <c r="I30" t="n">
-        <v>1.086</v>
+        <v>1.0414</v>
       </c>
       <c r="J30" t="n">
-        <v>39.096</v>
+        <v>37.4904</v>
       </c>
     </row>
     <row r="31">
@@ -3681,10 +3681,10 @@
         <v>1.24</v>
       </c>
       <c r="I31" t="n">
-        <v>0.7921</v>
+        <v>0.7471</v>
       </c>
       <c r="J31" t="n">
-        <v>28.5156</v>
+        <v>26.8956</v>
       </c>
     </row>
     <row r="32">
@@ -3721,10 +3721,10 @@
         <v>1.17</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2618</v>
+        <v>0.2473</v>
       </c>
       <c r="J32" t="n">
-        <v>7.3304</v>
+        <v>6.9244</v>
       </c>
     </row>
     <row r="33">
@@ -3761,10 +3761,10 @@
         <v>0.97</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.1451</v>
+        <v>-0.0677</v>
       </c>
       <c r="J33" t="n">
-        <v>-4.0628</v>
+        <v>-1.8956</v>
       </c>
     </row>
     <row r="34">
@@ -3801,10 +3801,10 @@
         <v>0.95</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1841</v>
+        <v>-0.094</v>
       </c>
       <c r="J34" t="n">
-        <v>-5.1548</v>
+        <v>-2.632</v>
       </c>
     </row>
     <row r="35">
@@ -3841,10 +3841,10 @@
         <v>1.6</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8213</v>
+        <v>0.7377</v>
       </c>
       <c r="J35" t="n">
-        <v>22.9964</v>
+        <v>20.6556</v>
       </c>
     </row>
     <row r="36">
@@ -3881,10 +3881,10 @@
         <v>1.19</v>
       </c>
       <c r="I36" t="n">
-        <v>0.3018</v>
+        <v>0.2714</v>
       </c>
       <c r="J36" t="n">
-        <v>8.4504</v>
+        <v>7.5992</v>
       </c>
     </row>
     <row r="37">
@@ -3921,10 +3921,10 @@
         <v>1.01</v>
       </c>
       <c r="I37" t="n">
-        <v>0.0404</v>
+        <v>0.0289</v>
       </c>
       <c r="J37" t="n">
-        <v>1.1312</v>
+        <v>0.8092</v>
       </c>
     </row>
     <row r="38">
@@ -3961,10 +3961,10 @@
         <v>0.9</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.2279</v>
+        <v>-0.1342</v>
       </c>
       <c r="J38" t="n">
-        <v>-6.3812</v>
+        <v>-3.7576</v>
       </c>
     </row>
     <row r="39">
@@ -4001,10 +4001,10 @@
         <v>0.7</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.5203</v>
+        <v>-0.3362</v>
       </c>
       <c r="J39" t="n">
-        <v>-14.5684</v>
+        <v>-9.413600000000001</v>
       </c>
     </row>
     <row r="40">
@@ -4041,10 +4041,10 @@
         <v>1.35</v>
       </c>
       <c r="I40" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.5381</v>
       </c>
       <c r="J40" t="n">
-        <v>16.3576</v>
+        <v>15.0668</v>
       </c>
     </row>
     <row r="41">
@@ -4081,10 +4081,10 @@
         <v>1.04</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1145</v>
+        <v>0.0888</v>
       </c>
       <c r="J41" t="n">
-        <v>3.206</v>
+        <v>2.4864</v>
       </c>
     </row>
     <row r="42">
@@ -4121,10 +4121,10 @@
         <v>0.82</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.2686</v>
+        <v>-0.1975</v>
       </c>
       <c r="J42" t="n">
-        <v>-6.9836</v>
+        <v>-5.135</v>
       </c>
     </row>
     <row r="43">
@@ -4161,10 +4161,10 @@
         <v>0.75</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.3983</v>
+        <v>-0.2642</v>
       </c>
       <c r="J43" t="n">
-        <v>-10.3558</v>
+        <v>-6.8692</v>
       </c>
     </row>
     <row r="44">
@@ -4201,10 +4201,10 @@
         <v>0.65</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.5434</v>
+        <v>-0.3593</v>
       </c>
       <c r="J44" t="n">
-        <v>-14.1284</v>
+        <v>-9.341799999999999</v>
       </c>
     </row>
     <row r="45">
@@ -4241,10 +4241,10 @@
         <v>0.95</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0328</v>
+        <v>-0.0521</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.8528</v>
+        <v>-1.3546</v>
       </c>
     </row>
     <row r="46">
@@ -4281,10 +4281,10 @@
         <v>0.88</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1612</v>
+        <v>-0.1354</v>
       </c>
       <c r="J46" t="n">
-        <v>-4.1912</v>
+        <v>-3.5204</v>
       </c>
     </row>
     <row r="47">
@@ -4321,10 +4321,10 @@
         <v>1.18</v>
       </c>
       <c r="I47" t="n">
-        <v>0.522</v>
+        <v>0.5209</v>
       </c>
       <c r="J47" t="n">
-        <v>13.572</v>
+        <v>13.5434</v>
       </c>
     </row>
     <row r="48">
@@ -4361,10 +4361,10 @@
         <v>0.85</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.5924</v>
+        <v>-0.5295</v>
       </c>
       <c r="J48" t="n">
-        <v>-15.4024</v>
+        <v>-13.767</v>
       </c>
     </row>
     <row r="49">
@@ -4401,10 +4401,10 @@
         <v>0.64</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.0721</v>
+        <v>-1.0563</v>
       </c>
       <c r="J49" t="n">
-        <v>-27.8746</v>
+        <v>-27.4638</v>
       </c>
     </row>
     <row r="50">
@@ -4441,10 +4441,10 @@
         <v>1.74</v>
       </c>
       <c r="I50" t="n">
-        <v>1.703</v>
+        <v>1.4606</v>
       </c>
       <c r="J50" t="n">
-        <v>44.278</v>
+        <v>37.9756</v>
       </c>
     </row>
     <row r="51">
@@ -4481,10 +4481,10 @@
         <v>1.32</v>
       </c>
       <c r="I51" t="n">
-        <v>0.8683999999999999</v>
+        <v>0.8569</v>
       </c>
       <c r="J51" t="n">
-        <v>22.5784</v>
+        <v>22.2794</v>
       </c>
     </row>
     <row r="52">
@@ -4521,10 +4521,10 @@
         <v>0.89</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.2051</v>
+        <v>-0.1351</v>
       </c>
       <c r="J52" t="n">
-        <v>-5.9479</v>
+        <v>-3.9179</v>
       </c>
     </row>
     <row r="53">
@@ -4561,10 +4561,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.5137</v>
+        <v>-0.3342</v>
       </c>
       <c r="J53" t="n">
-        <v>-14.8973</v>
+        <v>-9.691800000000001</v>
       </c>
     </row>
     <row r="54">
@@ -4601,10 +4601,10 @@
         <v>0.68</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.5271</v>
+        <v>-0.3437</v>
       </c>
       <c r="J54" t="n">
-        <v>-15.2859</v>
+        <v>-9.9673</v>
       </c>
     </row>
     <row r="55">
@@ -4641,10 +4641,10 @@
         <v>1.17</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3743</v>
+        <v>0.4173</v>
       </c>
       <c r="J55" t="n">
-        <v>10.8547</v>
+        <v>12.1017</v>
       </c>
     </row>
     <row r="56">
@@ -4681,10 +4681,10 @@
         <v>1.09</v>
       </c>
       <c r="I56" t="n">
-        <v>0.2475</v>
+        <v>0.2545</v>
       </c>
       <c r="J56" t="n">
-        <v>7.1775</v>
+        <v>7.3805</v>
       </c>
     </row>
     <row r="57">
@@ -4721,10 +4721,10 @@
         <v>0.91</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.3663</v>
+        <v>-0.3198</v>
       </c>
       <c r="J57" t="n">
-        <v>-10.6227</v>
+        <v>-9.2742</v>
       </c>
     </row>
     <row r="58">
@@ -4761,10 +4761,10 @@
         <v>0.67</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.9724</v>
+        <v>-0.9472</v>
       </c>
       <c r="J58" t="n">
-        <v>-28.1996</v>
+        <v>-27.4688</v>
       </c>
     </row>
     <row r="59">
@@ -4801,10 +4801,10 @@
         <v>0.67</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.9724</v>
+        <v>-0.9472</v>
       </c>
       <c r="J59" t="n">
-        <v>-28.1996</v>
+        <v>-27.4688</v>
       </c>
     </row>
     <row r="60">
@@ -4841,10 +4841,10 @@
         <v>1.62</v>
       </c>
       <c r="I60" t="n">
-        <v>1.5622</v>
+        <v>1.3676</v>
       </c>
       <c r="J60" t="n">
-        <v>45.3038</v>
+        <v>39.6604</v>
       </c>
     </row>
     <row r="61">
@@ -4881,10 +4881,10 @@
         <v>1.13</v>
       </c>
       <c r="I61" t="n">
-        <v>0.4829</v>
+        <v>0.4336</v>
       </c>
       <c r="J61" t="n">
-        <v>14.0041</v>
+        <v>12.5744</v>
       </c>
     </row>
     <row r="62">
@@ -4921,10 +4921,10 @@
         <v>0.79</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.3729</v>
+        <v>-0.2376</v>
       </c>
       <c r="J62" t="n">
-        <v>-11.187</v>
+        <v>-7.128</v>
       </c>
     </row>
     <row r="63">
@@ -4961,10 +4961,10 @@
         <v>0.68</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.5275</v>
+        <v>-0.3439</v>
       </c>
       <c r="J63" t="n">
-        <v>-15.825</v>
+        <v>-10.317</v>
       </c>
     </row>
     <row r="64">
@@ -5001,10 +5001,10 @@
         <v>0.67</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.5407999999999999</v>
+        <v>-0.3534</v>
       </c>
       <c r="J64" t="n">
-        <v>-16.224</v>
+        <v>-10.602</v>
       </c>
     </row>
     <row r="65">
@@ -5041,10 +5041,10 @@
         <v>1.27</v>
       </c>
       <c r="I65" t="n">
-        <v>0.5138</v>
+        <v>0.6045</v>
       </c>
       <c r="J65" t="n">
-        <v>15.414</v>
+        <v>18.135</v>
       </c>
     </row>
     <row r="66">
@@ -5081,10 +5081,10 @@
         <v>1.12</v>
       </c>
       <c r="I66" t="n">
-        <v>0.2965</v>
+        <v>0.3167</v>
       </c>
       <c r="J66" t="n">
-        <v>8.895</v>
+        <v>9.500999999999999</v>
       </c>
     </row>
     <row r="67">
@@ -5121,10 +5121,10 @@
         <v>0.95</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.2092</v>
+        <v>-0.1895</v>
       </c>
       <c r="J67" t="n">
-        <v>-6.276</v>
+        <v>-5.685</v>
       </c>
     </row>
     <row r="68">
@@ -5161,10 +5161,10 @@
         <v>0.9</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.3774</v>
+        <v>-0.3397</v>
       </c>
       <c r="J68" t="n">
-        <v>-11.322</v>
+        <v>-10.191</v>
       </c>
     </row>
     <row r="69">
@@ -5201,10 +5201,10 @@
         <v>0.68</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.9401</v>
+        <v>-0.9134</v>
       </c>
       <c r="J69" t="n">
-        <v>-28.203</v>
+        <v>-27.402</v>
       </c>
     </row>
     <row r="70">
@@ -5241,10 +5241,10 @@
         <v>1.22</v>
       </c>
       <c r="I70" t="n">
-        <v>0.7364000000000001</v>
+        <v>0.6888</v>
       </c>
       <c r="J70" t="n">
-        <v>22.092</v>
+        <v>20.664</v>
       </c>
     </row>
     <row r="71">
@@ -5281,10 +5281,10 @@
         <v>1.09</v>
       </c>
       <c r="I71" t="n">
-        <v>0.388</v>
+        <v>0.3315</v>
       </c>
       <c r="J71" t="n">
-        <v>11.64</v>
+        <v>9.945</v>
       </c>
     </row>
     <row r="72">
@@ -5321,10 +5321,10 @@
         <v>0.84</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.5501</v>
+        <v>-0.5063</v>
       </c>
       <c r="J72" t="n">
-        <v>-16.503</v>
+        <v>-15.189</v>
       </c>
     </row>
     <row r="73">
@@ -5361,10 +5361,10 @@
         <v>0.75</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.7781</v>
+        <v>-0.74</v>
       </c>
       <c r="J73" t="n">
-        <v>-23.343</v>
+        <v>-22.2</v>
       </c>
     </row>
     <row r="74">
@@ -5401,10 +5401,10 @@
         <v>0.73</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.8257</v>
+        <v>-0.7903</v>
       </c>
       <c r="J74" t="n">
-        <v>-24.771</v>
+        <v>-23.709</v>
       </c>
     </row>
     <row r="75">
@@ -5441,10 +5441,10 @@
         <v>1.32</v>
       </c>
       <c r="I75" t="n">
-        <v>0.968</v>
+        <v>0.9385</v>
       </c>
       <c r="J75" t="n">
-        <v>29.04</v>
+        <v>28.155</v>
       </c>
     </row>
     <row r="76">
@@ -5481,10 +5481,10 @@
         <v>1.21</v>
       </c>
       <c r="I76" t="n">
-        <v>0.7106</v>
+        <v>0.6617</v>
       </c>
       <c r="J76" t="n">
-        <v>21.318</v>
+        <v>19.851</v>
       </c>
     </row>
     <row r="77">
@@ -5521,10 +5521,10 @@
         <v>1.14</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2382</v>
+        <v>0.2987</v>
       </c>
       <c r="J77" t="n">
-        <v>7.146</v>
+        <v>8.961</v>
       </c>
     </row>
     <row r="78">
@@ -5561,10 +5561,10 @@
         <v>0.99</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.0888</v>
+        <v>-0.0331</v>
       </c>
       <c r="J78" t="n">
-        <v>-2.664</v>
+        <v>-0.993</v>
       </c>
     </row>
     <row r="79">
@@ -5601,10 +5601,10 @@
         <v>0.73</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.5024999999999999</v>
+        <v>-0.3214</v>
       </c>
       <c r="J79" t="n">
-        <v>-15.075</v>
+        <v>-9.641999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -5641,10 +5641,10 @@
         <v>1.7</v>
       </c>
       <c r="I80" t="n">
-        <v>0.9412</v>
+        <v>1.1207</v>
       </c>
       <c r="J80" t="n">
-        <v>28.236</v>
+        <v>33.621</v>
       </c>
     </row>
     <row r="81">
@@ -5681,10 +5681,10 @@
         <v>1.1</v>
       </c>
       <c r="I81" t="n">
-        <v>0.159</v>
+        <v>0.2244</v>
       </c>
       <c r="J81" t="n">
-        <v>4.77</v>
+        <v>6.732</v>
       </c>
     </row>
     <row r="82">
@@ -5721,10 +5721,10 @@
         <v>1.09</v>
       </c>
       <c r="I82" t="n">
-        <v>0.1975</v>
+        <v>0.1674</v>
       </c>
       <c r="J82" t="n">
-        <v>5.135</v>
+        <v>4.3524</v>
       </c>
     </row>
     <row r="83">
@@ -5761,10 +5761,10 @@
         <v>1.06</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1405</v>
+        <v>0.1191</v>
       </c>
       <c r="J83" t="n">
-        <v>3.653</v>
+        <v>3.0966</v>
       </c>
     </row>
     <row r="84">
@@ -5801,10 +5801,10 @@
         <v>0.96</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.127</v>
+        <v>-0.0664</v>
       </c>
       <c r="J84" t="n">
-        <v>-3.302</v>
+        <v>-1.7264</v>
       </c>
     </row>
     <row r="85">
@@ -5841,10 +5841,10 @@
         <v>1.17</v>
       </c>
       <c r="I85" t="n">
-        <v>0.3281</v>
+        <v>0.2861</v>
       </c>
       <c r="J85" t="n">
-        <v>8.5306</v>
+        <v>7.4386</v>
       </c>
     </row>
     <row r="86">
@@ -5881,10 +5881,10 @@
         <v>0.88</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2702</v>
+        <v>-0.1597</v>
       </c>
       <c r="J86" t="n">
-        <v>-7.0252</v>
+        <v>-4.1522</v>
       </c>
     </row>
     <row r="87">
@@ -5921,10 +5921,10 @@
         <v>0.95</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.1659</v>
+        <v>-0.0859</v>
       </c>
       <c r="J87" t="n">
-        <v>-4.3134</v>
+        <v>-2.2334</v>
       </c>
     </row>
     <row r="88">
@@ -5961,10 +5961,10 @@
         <v>0.83</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.3605</v>
+        <v>-0.2193</v>
       </c>
       <c r="J88" t="n">
-        <v>-9.372999999999999</v>
+        <v>-5.7018</v>
       </c>
     </row>
     <row r="89">
@@ -6001,10 +6001,10 @@
         <v>0.63</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.6223</v>
+        <v>-0.4112</v>
       </c>
       <c r="J89" t="n">
-        <v>-16.1798</v>
+        <v>-10.6912</v>
       </c>
     </row>
     <row r="90">
@@ -6041,10 +6041,10 @@
         <v>1.67</v>
       </c>
       <c r="I90" t="n">
-        <v>0.9204</v>
+        <v>0.837</v>
       </c>
       <c r="J90" t="n">
-        <v>23.9304</v>
+        <v>21.762</v>
       </c>
     </row>
     <row r="91">
@@ -6081,10 +6081,10 @@
         <v>1.4</v>
       </c>
       <c r="I91" t="n">
-        <v>0.615</v>
+        <v>0.5345</v>
       </c>
       <c r="J91" t="n">
-        <v>15.99</v>
+        <v>13.897</v>
       </c>
     </row>
     <row r="92">
@@ -6121,10 +6121,10 @@
         <v>1.22</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4809</v>
+        <v>0.5783</v>
       </c>
       <c r="J92" t="n">
-        <v>10.0989</v>
+        <v>12.1443</v>
       </c>
     </row>
     <row r="93">
@@ -6161,10 +6161,10 @@
         <v>1.22</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4809</v>
+        <v>0.5783</v>
       </c>
       <c r="J93" t="n">
-        <v>10.0989</v>
+        <v>12.1443</v>
       </c>
     </row>
     <row r="94">
@@ -6201,10 +6201,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.4023</v>
+        <v>-0.319</v>
       </c>
       <c r="J94" t="n">
-        <v>-8.4483</v>
+        <v>-6.699</v>
       </c>
     </row>
     <row r="95">
@@ -6241,10 +6241,10 @@
         <v>1.78</v>
       </c>
       <c r="I95" t="n">
-        <v>1.6761</v>
+        <v>1.4459</v>
       </c>
       <c r="J95" t="n">
-        <v>35.1981</v>
+        <v>30.3639</v>
       </c>
     </row>
     <row r="96">
@@ -6281,10 +6281,10 @@
         <v>1.62</v>
       </c>
       <c r="I96" t="n">
-        <v>1.3828</v>
+        <v>1.256</v>
       </c>
       <c r="J96" t="n">
-        <v>29.0388</v>
+        <v>26.376</v>
       </c>
     </row>
     <row r="97">
@@ -6321,10 +6321,10 @@
         <v>1.74</v>
       </c>
       <c r="I97" t="n">
-        <v>0.9566</v>
+        <v>1.1336</v>
       </c>
       <c r="J97" t="n">
-        <v>20.0886</v>
+        <v>23.8056</v>
       </c>
     </row>
     <row r="98">
@@ -6361,10 +6361,10 @@
         <v>1.47</v>
       </c>
       <c r="I98" t="n">
-        <v>0.6607</v>
+        <v>0.8231000000000001</v>
       </c>
       <c r="J98" t="n">
-        <v>13.8747</v>
+        <v>17.2851</v>
       </c>
     </row>
     <row r="99">
@@ -6401,10 +6401,10 @@
         <v>0.95</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1932</v>
+        <v>-0.0987</v>
       </c>
       <c r="J99" t="n">
-        <v>-4.0572</v>
+        <v>-2.0727</v>
       </c>
     </row>
     <row r="100">
@@ -6441,10 +6441,10 @@
         <v>1.3</v>
       </c>
       <c r="I100" t="n">
-        <v>0.4469</v>
+        <v>0.556</v>
       </c>
       <c r="J100" t="n">
-        <v>9.3849</v>
+        <v>11.676</v>
       </c>
     </row>
     <row r="101">
@@ -6481,10 +6481,10 @@
         <v>0.66</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.6005</v>
+        <v>-0.3946</v>
       </c>
       <c r="J101" t="n">
-        <v>-12.6105</v>
+        <v>-8.2866</v>
       </c>
     </row>
     <row r="102">
@@ -6521,10 +6521,10 @@
         <v>1.65</v>
       </c>
       <c r="I102" t="n">
-        <v>1.4537</v>
+        <v>1.2988</v>
       </c>
       <c r="J102" t="n">
-        <v>31.9814</v>
+        <v>28.5736</v>
       </c>
     </row>
     <row r="103">
@@ -6561,10 +6561,10 @@
         <v>1.47</v>
       </c>
       <c r="I103" t="n">
-        <v>1.1002</v>
+        <v>1.0785</v>
       </c>
       <c r="J103" t="n">
-        <v>24.2044</v>
+        <v>23.727</v>
       </c>
     </row>
     <row r="104">
@@ -6601,10 +6601,10 @@
         <v>1.21</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4701</v>
+        <v>0.5609</v>
       </c>
       <c r="J104" t="n">
-        <v>10.3422</v>
+        <v>12.3398</v>
       </c>
     </row>
     <row r="105">
@@ -6641,10 +6641,10 @@
         <v>1.15</v>
       </c>
       <c r="I105" t="n">
-        <v>0.3195</v>
+        <v>0.4096</v>
       </c>
       <c r="J105" t="n">
-        <v>7.029</v>
+        <v>9.011200000000001</v>
       </c>
     </row>
     <row r="106">
@@ -6681,10 +6681,10 @@
         <v>1.14</v>
       </c>
       <c r="I106" t="n">
-        <v>0.2936</v>
+        <v>0.3832</v>
       </c>
       <c r="J106" t="n">
-        <v>6.4592</v>
+        <v>8.430400000000001</v>
       </c>
     </row>
     <row r="107">
@@ -6721,10 +6721,10 @@
         <v>0.98</v>
       </c>
       <c r="I107" t="n">
-        <v>0.0362</v>
+        <v>-0.007</v>
       </c>
       <c r="J107" t="n">
-        <v>0.7964</v>
+        <v>-0.154</v>
       </c>
     </row>
     <row r="108">
@@ -6761,10 +6761,10 @@
         <v>0.86</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.19</v>
+        <v>-0.1551</v>
       </c>
       <c r="J108" t="n">
-        <v>-4.18</v>
+        <v>-3.4122</v>
       </c>
     </row>
     <row r="109">
@@ -6801,10 +6801,10 @@
         <v>0.77</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.3598</v>
+        <v>-0.2436</v>
       </c>
       <c r="J109" t="n">
-        <v>-7.9156</v>
+        <v>-5.3592</v>
       </c>
     </row>
     <row r="110">
@@ -6841,10 +6841,10 @@
         <v>0.72</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.4393</v>
+        <v>-0.2912</v>
       </c>
       <c r="J110" t="n">
-        <v>-9.6646</v>
+        <v>-6.4064</v>
       </c>
     </row>
     <row r="111">
@@ -6881,10 +6881,10 @@
         <v>0.66</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.526</v>
+        <v>-0.3481</v>
       </c>
       <c r="J111" t="n">
-        <v>-11.572</v>
+        <v>-7.6582</v>
       </c>
     </row>
     <row r="112">
@@ -6921,10 +6921,10 @@
         <v>1.49</v>
       </c>
       <c r="I112" t="n">
-        <v>1.1454</v>
+        <v>1.1047</v>
       </c>
       <c r="J112" t="n">
-        <v>27.4896</v>
+        <v>26.5128</v>
       </c>
     </row>
     <row r="113">
@@ -6961,10 +6961,10 @@
         <v>1.46</v>
       </c>
       <c r="I113" t="n">
-        <v>1.0833</v>
+        <v>1.0673</v>
       </c>
       <c r="J113" t="n">
-        <v>25.9992</v>
+        <v>25.6152</v>
       </c>
     </row>
     <row r="114">
@@ -7001,10 +7001,10 @@
         <v>1.26</v>
       </c>
       <c r="I114" t="n">
-        <v>0.5969</v>
+        <v>0.681</v>
       </c>
       <c r="J114" t="n">
-        <v>14.3256</v>
+        <v>16.344</v>
       </c>
     </row>
     <row r="115">
@@ -7041,10 +7041,10 @@
         <v>1.22</v>
       </c>
       <c r="I115" t="n">
-        <v>0.4984</v>
+        <v>0.5868</v>
       </c>
       <c r="J115" t="n">
-        <v>11.9616</v>
+        <v>14.0832</v>
       </c>
     </row>
     <row r="116">
@@ -7081,10 +7081,10 @@
         <v>1.15</v>
       </c>
       <c r="I116" t="n">
-        <v>0.3225</v>
+        <v>0.4114</v>
       </c>
       <c r="J116" t="n">
-        <v>7.74</v>
+        <v>9.8736</v>
       </c>
     </row>
     <row r="117">
@@ -7121,10 +7121,10 @@
         <v>1.16</v>
       </c>
       <c r="I117" t="n">
-        <v>0.423</v>
+        <v>0.4828</v>
       </c>
       <c r="J117" t="n">
-        <v>10.152</v>
+        <v>11.5872</v>
       </c>
     </row>
     <row r="118">
@@ -7161,10 +7161,10 @@
         <v>0.91</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.0795</v>
+        <v>-0.08840000000000001</v>
       </c>
       <c r="J118" t="n">
-        <v>-1.908</v>
+        <v>-2.1216</v>
       </c>
     </row>
     <row r="119">
@@ -7201,10 +7201,10 @@
         <v>0.77</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.3164</v>
+        <v>-0.2387</v>
       </c>
       <c r="J119" t="n">
-        <v>-7.5936</v>
+        <v>-5.7288</v>
       </c>
     </row>
     <row r="120">
@@ -7241,10 +7241,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.6465</v>
+        <v>-0.4343</v>
       </c>
       <c r="J120" t="n">
-        <v>-15.516</v>
+        <v>-10.4232</v>
       </c>
     </row>
     <row r="121">
@@ -7281,10 +7281,10 @@
         <v>0.34</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.9166</v>
+        <v>-0.6378</v>
       </c>
       <c r="J121" t="n">
-        <v>-21.9984</v>
+        <v>-15.3072</v>
       </c>
     </row>
     <row r="122">
@@ -7321,10 +7321,10 @@
         <v>1.28</v>
       </c>
       <c r="I122" t="n">
-        <v>0.4799</v>
+        <v>0.5676</v>
       </c>
       <c r="J122" t="n">
-        <v>13.4372</v>
+        <v>15.8928</v>
       </c>
     </row>
     <row r="123">
@@ -7361,10 +7361,10 @@
         <v>1.14</v>
       </c>
       <c r="I123" t="n">
-        <v>0.2779</v>
+        <v>0.3149</v>
       </c>
       <c r="J123" t="n">
-        <v>7.7812</v>
+        <v>8.8172</v>
       </c>
     </row>
     <row r="124">
@@ -7401,10 +7401,10 @@
         <v>1.09</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1931</v>
+        <v>0.2168</v>
       </c>
       <c r="J124" t="n">
-        <v>5.4068</v>
+        <v>6.0704</v>
       </c>
     </row>
     <row r="125">
@@ -7441,10 +7441,10 @@
         <v>1.04</v>
       </c>
       <c r="I125" t="n">
-        <v>0.0863</v>
+        <v>0.1101</v>
       </c>
       <c r="J125" t="n">
-        <v>2.4164</v>
+        <v>3.0828</v>
       </c>
     </row>
     <row r="126">
@@ -7481,10 +7481,10 @@
         <v>0.66</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5782</v>
+        <v>-0.3783</v>
       </c>
       <c r="J126" t="n">
-        <v>-16.1896</v>
+        <v>-10.5924</v>
       </c>
     </row>
     <row r="127">
@@ -7521,10 +7521,10 @@
         <v>1.3</v>
       </c>
       <c r="I127" t="n">
-        <v>0.8844</v>
+        <v>0.8552999999999999</v>
       </c>
       <c r="J127" t="n">
-        <v>24.7632</v>
+        <v>23.9484</v>
       </c>
     </row>
     <row r="128">
@@ -7561,10 +7561,10 @@
         <v>1.05</v>
       </c>
       <c r="I128" t="n">
-        <v>0.204</v>
+        <v>0.1885</v>
       </c>
       <c r="J128" t="n">
-        <v>5.712</v>
+        <v>5.278</v>
       </c>
     </row>
     <row r="129">
@@ -7601,10 +7601,10 @@
         <v>1.02</v>
       </c>
       <c r="I129" t="n">
-        <v>0.0693</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="J129" t="n">
-        <v>1.9404</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="130">
@@ -7641,10 +7641,10 @@
         <v>0.93</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3241</v>
+        <v>-0.2699</v>
       </c>
       <c r="J130" t="n">
-        <v>-9.0748</v>
+        <v>-7.5572</v>
       </c>
     </row>
     <row r="131">
@@ -7681,10 +7681,10 @@
         <v>0.88</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.472</v>
+        <v>-0.4163</v>
       </c>
       <c r="J131" t="n">
-        <v>-13.216</v>
+        <v>-11.6564</v>
       </c>
     </row>
     <row r="132">
@@ -7721,10 +7721,10 @@
         <v>0.82</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.197</v>
+        <v>-0.1739</v>
       </c>
       <c r="J132" t="n">
-        <v>-4.728</v>
+        <v>-4.1736</v>
       </c>
     </row>
     <row r="133">
@@ -7761,10 +7761,10 @@
         <v>0.72</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.3575</v>
+        <v>-0.2764</v>
       </c>
       <c r="J133" t="n">
-        <v>-8.58</v>
+        <v>-6.6336</v>
       </c>
     </row>
     <row r="134">
@@ -7801,10 +7801,10 @@
         <v>0.65</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.4905</v>
+        <v>-0.3398</v>
       </c>
       <c r="J134" t="n">
-        <v>-11.772</v>
+        <v>-8.155200000000001</v>
       </c>
     </row>
     <row r="135">
@@ -7841,10 +7841,10 @@
         <v>0.65</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.4905</v>
+        <v>-0.3398</v>
       </c>
       <c r="J135" t="n">
-        <v>-11.772</v>
+        <v>-8.155200000000001</v>
       </c>
     </row>
     <row r="136">
@@ -7881,10 +7881,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.6252</v>
+        <v>-0.4232</v>
       </c>
       <c r="J136" t="n">
-        <v>-15.0048</v>
+        <v>-10.1568</v>
       </c>
     </row>
     <row r="137">
@@ -7921,10 +7921,10 @@
         <v>2.07</v>
       </c>
       <c r="I137" t="n">
-        <v>2.0361</v>
+        <v>1.7509</v>
       </c>
       <c r="J137" t="n">
-        <v>48.8664</v>
+        <v>42.0216</v>
       </c>
     </row>
     <row r="138">
@@ -7961,10 +7961,10 @@
         <v>1.46</v>
       </c>
       <c r="I138" t="n">
-        <v>0.9961</v>
+        <v>1.0499</v>
       </c>
       <c r="J138" t="n">
-        <v>23.9064</v>
+        <v>25.1976</v>
       </c>
     </row>
     <row r="139">
@@ -8001,10 +8001,10 @@
         <v>1.38</v>
       </c>
       <c r="I139" t="n">
-        <v>0.8037</v>
+        <v>0.9199000000000001</v>
       </c>
       <c r="J139" t="n">
-        <v>19.2888</v>
+        <v>22.0776</v>
       </c>
     </row>
     <row r="140">
@@ -8041,10 +8041,10 @@
         <v>1.38</v>
       </c>
       <c r="I140" t="n">
-        <v>0.8037</v>
+        <v>0.9199000000000001</v>
       </c>
       <c r="J140" t="n">
-        <v>19.2888</v>
+        <v>22.0776</v>
       </c>
     </row>
     <row r="141">
@@ -8081,10 +8081,10 @@
         <v>1</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.1946</v>
+        <v>-0.1068</v>
       </c>
       <c r="J141" t="n">
-        <v>-4.6704</v>
+        <v>-2.5632</v>
       </c>
     </row>
     <row r="142">
@@ -8121,10 +8121,10 @@
         <v>1.04</v>
       </c>
       <c r="I142" t="n">
-        <v>0.0926</v>
+        <v>0.141</v>
       </c>
       <c r="J142" t="n">
-        <v>2.778</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="143">
@@ -8161,10 +8161,10 @@
         <v>1</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.0858</v>
+        <v>-0.026</v>
       </c>
       <c r="J143" t="n">
-        <v>-2.574</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="144">
@@ -8201,10 +8201,10 @@
         <v>0.78</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.754</v>
+        <v>-0.7045</v>
       </c>
       <c r="J144" t="n">
-        <v>-22.62</v>
+        <v>-21.135</v>
       </c>
     </row>
     <row r="145">
@@ -8241,10 +8241,10 @@
         <v>1.52</v>
       </c>
       <c r="I145" t="n">
-        <v>1.3067</v>
+        <v>1.192</v>
       </c>
       <c r="J145" t="n">
-        <v>39.201</v>
+        <v>35.76</v>
       </c>
     </row>
     <row r="146">
@@ -8281,10 +8281,10 @@
         <v>1.22</v>
       </c>
       <c r="I146" t="n">
-        <v>0.6501</v>
+        <v>0.6291</v>
       </c>
       <c r="J146" t="n">
-        <v>19.503</v>
+        <v>18.873</v>
       </c>
     </row>
     <row r="147">
@@ -8321,10 +8321,10 @@
         <v>1.25</v>
       </c>
       <c r="I147" t="n">
-        <v>0.3895</v>
+        <v>0.4805</v>
       </c>
       <c r="J147" t="n">
-        <v>11.685</v>
+        <v>14.415</v>
       </c>
     </row>
     <row r="148">
@@ -8361,10 +8361,10 @@
         <v>1.24</v>
       </c>
       <c r="I148" t="n">
-        <v>0.3749</v>
+        <v>0.4638</v>
       </c>
       <c r="J148" t="n">
-        <v>11.247</v>
+        <v>13.914</v>
       </c>
     </row>
     <row r="149">
@@ -8401,10 +8401,10 @@
         <v>1.23</v>
       </c>
       <c r="I149" t="n">
-        <v>0.36</v>
+        <v>0.4471</v>
       </c>
       <c r="J149" t="n">
-        <v>10.8</v>
+        <v>13.413</v>
       </c>
     </row>
     <row r="150">
@@ -8441,10 +8441,10 @@
         <v>1.13</v>
       </c>
       <c r="I150" t="n">
-        <v>0.189</v>
+        <v>0.2736</v>
       </c>
       <c r="J150" t="n">
-        <v>5.67</v>
+        <v>8.208</v>
       </c>
     </row>
     <row r="151">
@@ -8481,10 +8481,10 @@
         <v>1.09</v>
       </c>
       <c r="I151" t="n">
-        <v>0.1223</v>
+        <v>0.1955</v>
       </c>
       <c r="J151" t="n">
-        <v>3.669</v>
+        <v>5.865</v>
       </c>
     </row>
     <row r="152">
@@ -8521,10 +8521,10 @@
         <v>0.95</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.3015</v>
+        <v>-0.2312</v>
       </c>
       <c r="J152" t="n">
-        <v>-8.140499999999999</v>
+        <v>-6.2424</v>
       </c>
     </row>
     <row r="153">
@@ -8561,10 +8561,10 @@
         <v>0.88</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.5072</v>
+        <v>-0.4414</v>
       </c>
       <c r="J153" t="n">
-        <v>-13.6944</v>
+        <v>-11.9178</v>
       </c>
     </row>
     <row r="154">
@@ -8601,10 +8601,10 @@
         <v>0.85</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.5861</v>
+        <v>-0.5242</v>
       </c>
       <c r="J154" t="n">
-        <v>-15.8247</v>
+        <v>-14.1534</v>
       </c>
     </row>
     <row r="155">
@@ -8641,10 +8641,10 @@
         <v>1.61</v>
       </c>
       <c r="I155" t="n">
-        <v>1.4734</v>
+        <v>1.3037</v>
       </c>
       <c r="J155" t="n">
-        <v>39.7818</v>
+        <v>35.1999</v>
       </c>
     </row>
     <row r="156">
@@ -8681,10 +8681,10 @@
         <v>1.34</v>
       </c>
       <c r="I156" t="n">
-        <v>0.9241</v>
+        <v>0.9105</v>
       </c>
       <c r="J156" t="n">
-        <v>24.9507</v>
+        <v>24.5835</v>
       </c>
     </row>
     <row r="157">
@@ -8721,10 +8721,10 @@
         <v>0.89</v>
       </c>
       <c r="I157" t="n">
-        <v>-0.2259</v>
+        <v>-0.1393</v>
       </c>
       <c r="J157" t="n">
-        <v>-6.0993</v>
+        <v>-3.7611</v>
       </c>
     </row>
     <row r="158">
@@ -8761,10 +8761,10 @@
         <v>0.8</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.3699</v>
+        <v>-0.2326</v>
       </c>
       <c r="J158" t="n">
-        <v>-9.987299999999999</v>
+        <v>-6.2802</v>
       </c>
     </row>
     <row r="159">
@@ -8801,10 +8801,10 @@
         <v>0.72</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.4829</v>
+        <v>-0.3108</v>
       </c>
       <c r="J159" t="n">
-        <v>-13.0383</v>
+        <v>-8.3916</v>
       </c>
     </row>
     <row r="160">
@@ -8841,10 +8841,10 @@
         <v>1.27</v>
       </c>
       <c r="I160" t="n">
-        <v>0.4994</v>
+        <v>0.5861</v>
       </c>
       <c r="J160" t="n">
-        <v>13.4838</v>
+        <v>15.8247</v>
       </c>
     </row>
     <row r="161">
@@ -8881,10 +8881,10 @@
         <v>1.05</v>
       </c>
       <c r="I161" t="n">
-        <v>0.1581</v>
+        <v>0.1521</v>
       </c>
       <c r="J161" t="n">
-        <v>4.2687</v>
+        <v>4.1067</v>
       </c>
     </row>
     <row r="162">
@@ -8921,10 +8921,10 @@
         <v>1</v>
       </c>
       <c r="I162" t="n">
-        <v>0.0271</v>
+        <v>0.005</v>
       </c>
       <c r="J162" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="163">
@@ -8961,10 +8961,10 @@
         <v>0.99</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0174</v>
       </c>
       <c r="J163" t="n">
-        <v>-0.264</v>
+        <v>-0.522</v>
       </c>
     </row>
     <row r="164">
@@ -9001,10 +9001,10 @@
         <v>0.96</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.0861</v>
+        <v>-0.06</v>
       </c>
       <c r="J164" t="n">
-        <v>-2.583</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="165">
@@ -9041,10 +9041,10 @@
         <v>0.92</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1762</v>
+        <v>-0.1073</v>
       </c>
       <c r="J165" t="n">
-        <v>-5.286</v>
+        <v>-3.219</v>
       </c>
     </row>
     <row r="166">
@@ -9081,10 +9081,10 @@
         <v>0.92</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.1762</v>
+        <v>-0.1073</v>
       </c>
       <c r="J166" t="n">
-        <v>-5.286</v>
+        <v>-3.219</v>
       </c>
     </row>
     <row r="167">
@@ -9121,10 +9121,10 @@
         <v>1.44</v>
       </c>
       <c r="I167" t="n">
-        <v>0.68</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="J167" t="n">
-        <v>20.4</v>
+        <v>17.859</v>
       </c>
     </row>
     <row r="168">
@@ -9161,10 +9161,10 @@
         <v>1.03</v>
       </c>
       <c r="I168" t="n">
-        <v>0.0612</v>
+        <v>0.0616</v>
       </c>
       <c r="J168" t="n">
-        <v>1.836</v>
+        <v>1.848</v>
       </c>
     </row>
     <row r="169">
@@ -9201,10 +9201,10 @@
         <v>1.02</v>
       </c>
       <c r="I169" t="n">
-        <v>0.0366</v>
+        <v>0.0434</v>
       </c>
       <c r="J169" t="n">
-        <v>1.098</v>
+        <v>1.302</v>
       </c>
     </row>
     <row r="170">
@@ -9241,10 +9241,10 @@
         <v>0.95</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1505</v>
+        <v>-0.08019999999999999</v>
       </c>
       <c r="J170" t="n">
-        <v>-4.515</v>
+        <v>-2.406</v>
       </c>
     </row>
     <row r="171">
@@ -9281,10 +9281,10 @@
         <v>0.77</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4346</v>
+        <v>-0.2735</v>
       </c>
       <c r="J171" t="n">
-        <v>-13.038</v>
+        <v>-8.205</v>
       </c>
     </row>
     <row r="172">
@@ -9321,10 +9321,10 @@
         <v>1.48</v>
       </c>
       <c r="I172" t="n">
-        <v>1.173</v>
+        <v>1.1116</v>
       </c>
       <c r="J172" t="n">
-        <v>28.152</v>
+        <v>26.6784</v>
       </c>
     </row>
     <row r="173">
@@ -9361,10 +9361,10 @@
         <v>1.34</v>
       </c>
       <c r="I173" t="n">
-        <v>0.8741</v>
+        <v>0.8796</v>
       </c>
       <c r="J173" t="n">
-        <v>20.9784</v>
+        <v>21.1104</v>
       </c>
     </row>
     <row r="174">
@@ -9401,10 +9401,10 @@
         <v>1.19</v>
       </c>
       <c r="I174" t="n">
-        <v>0.4771</v>
+        <v>0.5337</v>
       </c>
       <c r="J174" t="n">
-        <v>11.4504</v>
+        <v>12.8088</v>
       </c>
     </row>
     <row r="175">
@@ -9441,10 +9441,10 @@
         <v>1.1</v>
       </c>
       <c r="I175" t="n">
-        <v>0.2276</v>
+        <v>0.2983</v>
       </c>
       <c r="J175" t="n">
-        <v>5.4624</v>
+        <v>7.1592</v>
       </c>
     </row>
     <row r="176">
@@ -9481,10 +9481,10 @@
         <v>0.98</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.2298</v>
+        <v>-0.1492</v>
       </c>
       <c r="J176" t="n">
-        <v>-5.5152</v>
+        <v>-3.5808</v>
       </c>
     </row>
     <row r="177">
@@ -9521,10 +9521,10 @@
         <v>1.03</v>
       </c>
       <c r="I177" t="n">
-        <v>0.1299</v>
+        <v>0.1122</v>
       </c>
       <c r="J177" t="n">
-        <v>3.1176</v>
+        <v>2.6928</v>
       </c>
     </row>
     <row r="178">
@@ -9561,10 +9561,10 @@
         <v>0.99</v>
       </c>
       <c r="I178" t="n">
-        <v>0.0119</v>
+        <v>-0.0121</v>
       </c>
       <c r="J178" t="n">
-        <v>0.2856</v>
+        <v>-0.2904</v>
       </c>
     </row>
     <row r="179">
@@ -9601,10 +9601,10 @@
         <v>0.86</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.2645</v>
+        <v>-0.1676</v>
       </c>
       <c r="J179" t="n">
-        <v>-6.348</v>
+        <v>-4.0224</v>
       </c>
     </row>
     <row r="180">
@@ -9641,10 +9641,10 @@
         <v>0.85</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2813</v>
+        <v>-0.1779</v>
       </c>
       <c r="J180" t="n">
-        <v>-6.7512</v>
+        <v>-4.2696</v>
       </c>
     </row>
     <row r="181">
@@ -9681,10 +9681,10 @@
         <v>0.84</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2977</v>
+        <v>-0.1882</v>
       </c>
       <c r="J181" t="n">
-        <v>-7.1448</v>
+        <v>-4.5168</v>
       </c>
     </row>
     <row r="182">
@@ -9721,10 +9721,10 @@
         <v>1.57</v>
       </c>
       <c r="I182" t="n">
-        <v>1.3959</v>
+        <v>1.2517</v>
       </c>
       <c r="J182" t="n">
-        <v>41.877</v>
+        <v>37.551</v>
       </c>
     </row>
     <row r="183">
@@ -9761,10 +9761,10 @@
         <v>1.16</v>
       </c>
       <c r="I183" t="n">
-        <v>0.4792</v>
+        <v>0.4746</v>
       </c>
       <c r="J183" t="n">
-        <v>14.376</v>
+        <v>14.238</v>
       </c>
     </row>
     <row r="184">
@@ -9801,10 +9801,10 @@
         <v>1.06</v>
       </c>
       <c r="I184" t="n">
-        <v>0.1517</v>
+        <v>0.2016</v>
       </c>
       <c r="J184" t="n">
-        <v>4.551</v>
+        <v>6.048</v>
       </c>
     </row>
     <row r="185">
@@ -9841,10 +9841,10 @@
         <v>0.98</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1954</v>
+        <v>-0.1261</v>
       </c>
       <c r="J185" t="n">
-        <v>-5.862</v>
+        <v>-3.783</v>
       </c>
     </row>
     <row r="186">
@@ -9881,10 +9881,10 @@
         <v>0.87</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.5346</v>
+        <v>-0.4699</v>
       </c>
       <c r="J186" t="n">
-        <v>-16.038</v>
+        <v>-14.097</v>
       </c>
     </row>
     <row r="187">
@@ -9921,10 +9921,10 @@
         <v>1.05</v>
       </c>
       <c r="I187" t="n">
-        <v>0.1541</v>
+        <v>0.1494</v>
       </c>
       <c r="J187" t="n">
-        <v>4.623</v>
+        <v>4.482</v>
       </c>
     </row>
     <row r="188">
@@ -9961,10 +9961,10 @@
         <v>1.01</v>
       </c>
       <c r="I188" t="n">
-        <v>0.0636</v>
+        <v>0.0456</v>
       </c>
       <c r="J188" t="n">
-        <v>1.908</v>
+        <v>1.368</v>
       </c>
     </row>
     <row r="189">
@@ -10001,10 +10001,10 @@
         <v>0.97</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.0593</v>
+        <v>-0.0469</v>
       </c>
       <c r="J189" t="n">
-        <v>-1.779</v>
+        <v>-1.407</v>
       </c>
     </row>
     <row r="190">
@@ -10041,10 +10041,10 @@
         <v>0.95</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1123</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="J190" t="n">
-        <v>-3.369</v>
+        <v>-2.16</v>
       </c>
     </row>
     <row r="191">
@@ -10081,10 +10081,10 @@
         <v>0.8</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3726</v>
+        <v>-0.2338</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.178</v>
+        <v>-7.014</v>
       </c>
     </row>
     <row r="192">
@@ -10121,10 +10121,10 @@
         <v>1.02</v>
       </c>
       <c r="I192" t="n">
-        <v>0.07439999999999999</v>
+        <v>0.0485</v>
       </c>
       <c r="J192" t="n">
-        <v>2.6784</v>
+        <v>1.746</v>
       </c>
     </row>
     <row r="193">
@@ -10161,10 +10161,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.1505</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="J193" t="n">
-        <v>-5.418</v>
+        <v>-3.1284</v>
       </c>
     </row>
     <row r="194">
@@ -10201,10 +10201,10 @@
         <v>0.72</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.4916</v>
+        <v>-0.3158</v>
       </c>
       <c r="J194" t="n">
-        <v>-17.6976</v>
+        <v>-11.3688</v>
       </c>
     </row>
     <row r="195">
@@ -10241,10 +10241,10 @@
         <v>1.16</v>
       </c>
       <c r="I195" t="n">
-        <v>0.3287</v>
+        <v>0.2618</v>
       </c>
       <c r="J195" t="n">
-        <v>11.8332</v>
+        <v>9.424799999999999</v>
       </c>
     </row>
     <row r="196">
@@ -10281,10 +10281,10 @@
         <v>1.1</v>
       </c>
       <c r="I196" t="n">
-        <v>0.2325</v>
+        <v>0.1776</v>
       </c>
       <c r="J196" t="n">
-        <v>8.369999999999999</v>
+        <v>6.3936</v>
       </c>
     </row>
     <row r="197">
@@ -10321,10 +10321,10 @@
         <v>1.42</v>
       </c>
       <c r="I197" t="n">
-        <v>0.573</v>
+        <v>0.5558</v>
       </c>
       <c r="J197" t="n">
-        <v>20.628</v>
+        <v>20.0088</v>
       </c>
     </row>
     <row r="198">
@@ -10361,10 +10361,10 @@
         <v>1.39</v>
       </c>
       <c r="I198" t="n">
-        <v>0.5348000000000001</v>
+        <v>0.5211</v>
       </c>
       <c r="J198" t="n">
-        <v>19.2528</v>
+        <v>18.7596</v>
       </c>
     </row>
     <row r="199">
@@ -10401,10 +10401,10 @@
         <v>1.31</v>
       </c>
       <c r="I199" t="n">
-        <v>0.4159</v>
+        <v>0.4283</v>
       </c>
       <c r="J199" t="n">
-        <v>14.9724</v>
+        <v>15.4188</v>
       </c>
     </row>
     <row r="200">
@@ -10441,10 +10441,10 @@
         <v>1.29</v>
       </c>
       <c r="I200" t="n">
-        <v>0.3855</v>
+        <v>0.4046</v>
       </c>
       <c r="J200" t="n">
-        <v>13.878</v>
+        <v>14.5656</v>
       </c>
     </row>
     <row r="201">
@@ -10481,10 +10481,10 @@
         <v>1.18</v>
       </c>
       <c r="I201" t="n">
-        <v>0.2288</v>
+        <v>0.2637</v>
       </c>
       <c r="J201" t="n">
-        <v>8.236800000000001</v>
+        <v>9.4932</v>
       </c>
     </row>
     <row r="202">
@@ -10521,10 +10521,10 @@
         <v>1.28</v>
       </c>
       <c r="I202" t="n">
-        <v>0.4662</v>
+        <v>0.5548</v>
       </c>
       <c r="J202" t="n">
-        <v>11.1888</v>
+        <v>13.3152</v>
       </c>
     </row>
     <row r="203">
@@ -10561,10 +10561,10 @@
         <v>1.26</v>
       </c>
       <c r="I203" t="n">
-        <v>0.4392</v>
+        <v>0.5205</v>
       </c>
       <c r="J203" t="n">
-        <v>10.5408</v>
+        <v>12.492</v>
       </c>
     </row>
     <row r="204">
@@ -10601,10 +10601,10 @@
         <v>0.84</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.3435</v>
+        <v>-0.2077</v>
       </c>
       <c r="J204" t="n">
-        <v>-8.244</v>
+        <v>-4.9848</v>
       </c>
     </row>
     <row r="205">
@@ -10641,10 +10641,10 @@
         <v>1.09</v>
       </c>
       <c r="I205" t="n">
-        <v>0.1712</v>
+        <v>0.2104</v>
       </c>
       <c r="J205" t="n">
-        <v>4.1088</v>
+        <v>5.0496</v>
       </c>
     </row>
     <row r="206">
@@ -10681,10 +10681,10 @@
         <v>0.95</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.1628</v>
+        <v>-0.08459999999999999</v>
       </c>
       <c r="J206" t="n">
-        <v>-3.9072</v>
+        <v>-2.0304</v>
       </c>
     </row>
     <row r="207">
@@ -10721,10 +10721,10 @@
         <v>0.83</v>
       </c>
       <c r="I207" t="n">
-        <v>-0.5556</v>
+        <v>-0.5206</v>
       </c>
       <c r="J207" t="n">
-        <v>-13.3344</v>
+        <v>-12.4944</v>
       </c>
     </row>
     <row r="208">
@@ -10761,10 +10761,10 @@
         <v>0.5</v>
       </c>
       <c r="I208" t="n">
-        <v>-1.314</v>
+        <v>-1.3321</v>
       </c>
       <c r="J208" t="n">
-        <v>-31.536</v>
+        <v>-31.9704</v>
       </c>
     </row>
     <row r="209">
@@ -10801,10 +10801,10 @@
         <v>0.36</v>
       </c>
       <c r="I209" t="n">
-        <v>-1.5899</v>
+        <v>-1.6555</v>
       </c>
       <c r="J209" t="n">
-        <v>-38.1576</v>
+        <v>-39.732</v>
       </c>
     </row>
     <row r="210">
@@ -10841,10 +10841,10 @@
         <v>1.49</v>
       </c>
       <c r="I210" t="n">
-        <v>1.3517</v>
+        <v>1.2243</v>
       </c>
       <c r="J210" t="n">
-        <v>32.4408</v>
+        <v>29.3832</v>
       </c>
     </row>
     <row r="211">
@@ -10881,10 +10881,10 @@
         <v>1.47</v>
       </c>
       <c r="I211" t="n">
-        <v>1.3112</v>
+        <v>1.1962</v>
       </c>
       <c r="J211" t="n">
-        <v>31.4688</v>
+        <v>28.7088</v>
       </c>
     </row>
     <row r="212">
@@ -10921,10 +10921,10 @@
         <v>1.53</v>
       </c>
       <c r="I212" t="n">
-        <v>0.7528</v>
+        <v>0.9383</v>
       </c>
       <c r="J212" t="n">
-        <v>20.3256</v>
+        <v>25.3341</v>
       </c>
     </row>
     <row r="213">
@@ -10961,10 +10961,10 @@
         <v>1.07</v>
       </c>
       <c r="I213" t="n">
-        <v>0.1005</v>
+        <v>0.1613</v>
       </c>
       <c r="J213" t="n">
-        <v>2.7135</v>
+        <v>4.3551</v>
       </c>
     </row>
     <row r="214">
@@ -11001,10 +11001,10 @@
         <v>0.83</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.3691</v>
+        <v>-0.2242</v>
       </c>
       <c r="J214" t="n">
-        <v>-9.9657</v>
+        <v>-6.0534</v>
       </c>
     </row>
     <row r="215">
@@ -11041,10 +11041,10 @@
         <v>1.15</v>
       </c>
       <c r="I215" t="n">
-        <v>0.2492</v>
+        <v>0.3153</v>
       </c>
       <c r="J215" t="n">
-        <v>6.7284</v>
+        <v>8.5131</v>
       </c>
     </row>
     <row r="216">
@@ -11081,10 +11081,10 @@
         <v>1.14</v>
       </c>
       <c r="I216" t="n">
-        <v>0.2265</v>
+        <v>0.2978</v>
       </c>
       <c r="J216" t="n">
-        <v>6.1155</v>
+        <v>8.0406</v>
       </c>
     </row>
     <row r="217">
@@ -11121,10 +11121,10 @@
         <v>1.14</v>
       </c>
       <c r="I217" t="n">
-        <v>0.4167</v>
+        <v>0.4233</v>
       </c>
       <c r="J217" t="n">
-        <v>11.2509</v>
+        <v>11.4291</v>
       </c>
     </row>
     <row r="218">
@@ -11161,10 +11161,10 @@
         <v>0.88</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.5085</v>
+        <v>-0.4425</v>
       </c>
       <c r="J218" t="n">
-        <v>-13.7295</v>
+        <v>-11.9475</v>
       </c>
     </row>
     <row r="219">
@@ -11201,10 +11201,10 @@
         <v>0.77</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.7824</v>
+        <v>-0.7346</v>
       </c>
       <c r="J219" t="n">
-        <v>-21.1248</v>
+        <v>-19.8342</v>
       </c>
     </row>
     <row r="220">
@@ -11241,10 +11241,10 @@
         <v>1.5</v>
       </c>
       <c r="I220" t="n">
-        <v>1.2576</v>
+        <v>1.1603</v>
       </c>
       <c r="J220" t="n">
-        <v>33.9552</v>
+        <v>31.3281</v>
       </c>
     </row>
     <row r="221">
@@ -11281,10 +11281,10 @@
         <v>1.36</v>
       </c>
       <c r="I221" t="n">
-        <v>0.966</v>
+        <v>0.9524</v>
       </c>
       <c r="J221" t="n">
-        <v>26.082</v>
+        <v>25.7148</v>
       </c>
     </row>
     <row r="222">
@@ -11321,10 +11321,10 @@
         <v>1.03</v>
       </c>
       <c r="I222" t="n">
-        <v>0.1453</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="J222" t="n">
-        <v>3.6325</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="223">
@@ -11361,10 +11361,10 @@
         <v>1.02</v>
       </c>
       <c r="I223" t="n">
-        <v>0.1228</v>
+        <v>0.0745</v>
       </c>
       <c r="J223" t="n">
-        <v>3.07</v>
+        <v>1.8625</v>
       </c>
     </row>
     <row r="224">
@@ -11401,10 +11401,10 @@
         <v>0.83</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.2985</v>
+        <v>-0.1939</v>
       </c>
       <c r="J224" t="n">
-        <v>-7.4625</v>
+        <v>-4.8475</v>
       </c>
     </row>
     <row r="225">
@@ -11441,10 +11441,10 @@
         <v>0.77</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.393</v>
+        <v>-0.2534</v>
       </c>
       <c r="J225" t="n">
-        <v>-9.824999999999999</v>
+        <v>-6.335</v>
       </c>
     </row>
     <row r="226">
@@ -11481,10 +11481,10 @@
         <v>0.73</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4512</v>
+        <v>-0.2923</v>
       </c>
       <c r="J226" t="n">
-        <v>-11.28</v>
+        <v>-7.3075</v>
       </c>
     </row>
     <row r="227">
@@ -11521,10 +11521,10 @@
         <v>1.66</v>
       </c>
       <c r="I227" t="n">
-        <v>0.864</v>
+        <v>0.7823</v>
       </c>
       <c r="J227" t="n">
-        <v>21.6</v>
+        <v>19.5575</v>
       </c>
     </row>
     <row r="228">
@@ -11561,10 +11561,10 @@
         <v>1.3</v>
       </c>
       <c r="I228" t="n">
-        <v>0.4352</v>
+        <v>0.3922</v>
       </c>
       <c r="J228" t="n">
-        <v>10.88</v>
+        <v>9.805</v>
       </c>
     </row>
     <row r="229">
@@ -11601,10 +11601,10 @@
         <v>1.3</v>
       </c>
       <c r="I229" t="n">
-        <v>0.4352</v>
+        <v>0.3922</v>
       </c>
       <c r="J229" t="n">
-        <v>10.88</v>
+        <v>9.805</v>
       </c>
     </row>
     <row r="230">
@@ -11641,10 +11641,10 @@
         <v>1.19</v>
       </c>
       <c r="I230" t="n">
-        <v>0.2603</v>
+        <v>0.2646</v>
       </c>
       <c r="J230" t="n">
-        <v>6.5075</v>
+        <v>6.615</v>
       </c>
     </row>
     <row r="231">
@@ -11681,10 +11681,10 @@
         <v>0.83</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3858</v>
+        <v>-0.2347</v>
       </c>
       <c r="J231" t="n">
-        <v>-9.645</v>
+        <v>-5.8675</v>
       </c>
     </row>
     <row r="232">
@@ -11721,10 +11721,10 @@
         <v>1.26</v>
       </c>
       <c r="I232" t="n">
-        <v>0.7722</v>
+        <v>0.7425</v>
       </c>
       <c r="J232" t="n">
-        <v>23.166</v>
+        <v>22.275</v>
       </c>
     </row>
     <row r="233">
@@ -11761,10 +11761,10 @@
         <v>1.24</v>
       </c>
       <c r="I233" t="n">
-        <v>0.7243000000000001</v>
+        <v>0.6933</v>
       </c>
       <c r="J233" t="n">
-        <v>21.729</v>
+        <v>20.799</v>
       </c>
     </row>
     <row r="234">
@@ -11801,10 +11801,10 @@
         <v>1.01</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.0023</v>
+        <v>0.0393</v>
       </c>
       <c r="J234" t="n">
-        <v>-0.06900000000000001</v>
+        <v>1.179</v>
       </c>
     </row>
     <row r="235">
@@ -11841,10 +11841,10 @@
         <v>0.98</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.167</v>
+        <v>-0.1108</v>
       </c>
       <c r="J235" t="n">
-        <v>-5.01</v>
+        <v>-3.324</v>
       </c>
     </row>
     <row r="236">
@@ -11881,10 +11881,10 @@
         <v>0.86</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.5405</v>
+        <v>-0.4816</v>
       </c>
       <c r="J236" t="n">
-        <v>-16.215</v>
+        <v>-14.448</v>
       </c>
     </row>
     <row r="237">
@@ -11921,10 +11921,10 @@
         <v>1.27</v>
       </c>
       <c r="I237" t="n">
-        <v>0.4753</v>
+        <v>0.5589</v>
       </c>
       <c r="J237" t="n">
-        <v>14.259</v>
+        <v>16.767</v>
       </c>
     </row>
     <row r="238">
@@ -11961,10 +11961,10 @@
         <v>1.07</v>
       </c>
       <c r="I238" t="n">
-        <v>0.1675</v>
+        <v>0.1802</v>
       </c>
       <c r="J238" t="n">
-        <v>5.025</v>
+        <v>5.406</v>
       </c>
     </row>
     <row r="239">
@@ -12001,10 +12001,10 @@
         <v>0.99</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.0495</v>
+        <v>-0.0218</v>
       </c>
       <c r="J239" t="n">
-        <v>-1.485</v>
+        <v>-0.654</v>
       </c>
     </row>
     <row r="240">
@@ -12041,10 +12041,10 @@
         <v>0.95</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.1416</v>
+        <v>-0.0775</v>
       </c>
       <c r="J240" t="n">
-        <v>-4.248</v>
+        <v>-2.325</v>
       </c>
     </row>
     <row r="241">
@@ -12081,10 +12081,10 @@
         <v>0.8</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.3872</v>
+        <v>-0.2409</v>
       </c>
       <c r="J241" t="n">
-        <v>-11.616</v>
+        <v>-7.227</v>
       </c>
     </row>
     <row r="242">
@@ -12121,10 +12121,10 @@
         <v>1.67</v>
       </c>
       <c r="I242" t="n">
-        <v>1.5247</v>
+        <v>1.3411</v>
       </c>
       <c r="J242" t="n">
-        <v>33.5434</v>
+        <v>29.5042</v>
       </c>
     </row>
     <row r="243">
@@ -12161,10 +12161,10 @@
         <v>1.24</v>
       </c>
       <c r="I243" t="n">
-        <v>0.5913</v>
+        <v>0.6463</v>
       </c>
       <c r="J243" t="n">
-        <v>13.0086</v>
+        <v>14.2186</v>
       </c>
     </row>
     <row r="244">
@@ -12201,10 +12201,10 @@
         <v>1.19</v>
       </c>
       <c r="I244" t="n">
-        <v>0.4564</v>
+        <v>0.5275</v>
       </c>
       <c r="J244" t="n">
-        <v>10.0408</v>
+        <v>11.605</v>
       </c>
     </row>
     <row r="245">
@@ -12241,10 +12241,10 @@
         <v>1.09</v>
       </c>
       <c r="I245" t="n">
-        <v>0.1852</v>
+        <v>0.2621</v>
       </c>
       <c r="J245" t="n">
-        <v>4.0744</v>
+        <v>5.7662</v>
       </c>
     </row>
     <row r="246">
@@ -12281,10 +12281,10 @@
         <v>1.06</v>
       </c>
       <c r="I246" t="n">
-        <v>0.0956</v>
+        <v>0.172</v>
       </c>
       <c r="J246" t="n">
-        <v>2.1032</v>
+        <v>3.784</v>
       </c>
     </row>
     <row r="247">
@@ -12321,10 +12321,10 @@
         <v>1.39</v>
       </c>
       <c r="I247" t="n">
-        <v>0.6798</v>
+        <v>0.8387</v>
       </c>
       <c r="J247" t="n">
-        <v>14.9556</v>
+        <v>18.4514</v>
       </c>
     </row>
     <row r="248">
@@ -12361,10 +12361,10 @@
         <v>0.98</v>
       </c>
       <c r="I248" t="n">
-        <v>0.0046</v>
+        <v>-0.0217</v>
       </c>
       <c r="J248" t="n">
-        <v>0.1012</v>
+        <v>-0.4774</v>
       </c>
     </row>
     <row r="249">
@@ -12401,10 +12401,10 @@
         <v>0.82</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.3133</v>
+        <v>-0.2035</v>
       </c>
       <c r="J249" t="n">
-        <v>-6.8926</v>
+        <v>-4.477</v>
       </c>
     </row>
     <row r="250">
@@ -12441,10 +12441,10 @@
         <v>0.68</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.5194</v>
+        <v>-0.3395</v>
       </c>
       <c r="J250" t="n">
-        <v>-11.4268</v>
+        <v>-7.469</v>
       </c>
     </row>
     <row r="251">
@@ -12481,10 +12481,10 @@
         <v>0.49</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.7588</v>
+        <v>-0.5154</v>
       </c>
       <c r="J251" t="n">
-        <v>-16.6936</v>
+        <v>-11.3388</v>
       </c>
     </row>
     <row r="252">
@@ -12521,10 +12521,10 @@
         <v>1.12</v>
       </c>
       <c r="I252" t="n">
-        <v>0.277</v>
+        <v>0.2987</v>
       </c>
       <c r="J252" t="n">
-        <v>6.094</v>
+        <v>6.5714</v>
       </c>
     </row>
     <row r="253">
@@ -12561,10 +12561,10 @@
         <v>0.84</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.3126</v>
+        <v>-0.1934</v>
       </c>
       <c r="J253" t="n">
-        <v>-6.8772</v>
+        <v>-4.2548</v>
       </c>
     </row>
     <row r="254">
@@ -12601,10 +12601,10 @@
         <v>0.65</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.577</v>
+        <v>-0.3785</v>
       </c>
       <c r="J254" t="n">
-        <v>-12.694</v>
+        <v>-8.327</v>
       </c>
     </row>
     <row r="255">
@@ -12641,10 +12641,10 @@
         <v>1.14</v>
       </c>
       <c r="I255" t="n">
-        <v>0.3088</v>
+        <v>0.3385</v>
       </c>
       <c r="J255" t="n">
-        <v>6.7936</v>
+        <v>7.447</v>
       </c>
     </row>
     <row r="256">
@@ -12681,10 +12681,10 @@
         <v>1.04</v>
       </c>
       <c r="I256" t="n">
-        <v>0.133</v>
+        <v>0.1252</v>
       </c>
       <c r="J256" t="n">
-        <v>2.926</v>
+        <v>2.7544</v>
       </c>
     </row>
     <row r="257">
@@ -12721,10 +12721,10 @@
         <v>0.9</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.376</v>
+        <v>-0.3391</v>
       </c>
       <c r="J257" t="n">
-        <v>-8.272</v>
+        <v>-7.4602</v>
       </c>
     </row>
     <row r="258">
@@ -12761,10 +12761,10 @@
         <v>0.61</v>
       </c>
       <c r="I258" t="n">
-        <v>-1.0935</v>
+        <v>-1.0822</v>
       </c>
       <c r="J258" t="n">
-        <v>-24.057</v>
+        <v>-23.8084</v>
       </c>
     </row>
     <row r="259">
@@ -12801,10 +12801,10 @@
         <v>0.32</v>
       </c>
       <c r="I259" t="n">
-        <v>-1.6704</v>
+        <v>-1.753</v>
       </c>
       <c r="J259" t="n">
-        <v>-36.7488</v>
+        <v>-38.566</v>
       </c>
     </row>
     <row r="260">
@@ -12841,10 +12841,10 @@
         <v>1.7</v>
       </c>
       <c r="I260" t="n">
-        <v>1.7324</v>
+        <v>1.4915</v>
       </c>
       <c r="J260" t="n">
-        <v>38.1128</v>
+        <v>32.813</v>
       </c>
     </row>
     <row r="261">
@@ -12881,10 +12881,10 @@
         <v>1.3</v>
       </c>
       <c r="I261" t="n">
-        <v>0.9255</v>
+        <v>0.8931</v>
       </c>
       <c r="J261" t="n">
-        <v>20.361</v>
+        <v>19.6482</v>
       </c>
     </row>
     <row r="262">
@@ -12921,10 +12921,10 @@
         <v>1.17</v>
       </c>
       <c r="I262" t="n">
-        <v>0.2377</v>
+        <v>0.34</v>
       </c>
       <c r="J262" t="n">
-        <v>7.131</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="263">
@@ -12961,10 +12961,10 @@
         <v>1.13</v>
       </c>
       <c r="I263" t="n">
-        <v>0.1754</v>
+        <v>0.2666</v>
       </c>
       <c r="J263" t="n">
-        <v>5.262</v>
+        <v>7.998</v>
       </c>
     </row>
     <row r="264">
@@ -13001,10 +13001,10 @@
         <v>0.87</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.3248</v>
+        <v>-0.1909</v>
       </c>
       <c r="J264" t="n">
-        <v>-9.744</v>
+        <v>-5.727</v>
       </c>
     </row>
     <row r="265">
@@ -13041,10 +13041,10 @@
         <v>1.77</v>
       </c>
       <c r="I265" t="n">
-        <v>0.9852</v>
+        <v>1.1576</v>
       </c>
       <c r="J265" t="n">
-        <v>29.556</v>
+        <v>34.728</v>
       </c>
     </row>
     <row r="266">
@@ -13081,10 +13081,10 @@
         <v>1.22</v>
       </c>
       <c r="I266" t="n">
-        <v>0.3164</v>
+        <v>0.4257</v>
       </c>
       <c r="J266" t="n">
-        <v>9.492000000000001</v>
+        <v>12.771</v>
       </c>
     </row>
     <row r="267">
@@ -13121,10 +13121,10 @@
         <v>0.6</v>
       </c>
       <c r="I267" t="n">
-        <v>-1.0537</v>
+        <v>-1.0487</v>
       </c>
       <c r="J267" t="n">
-        <v>-31.611</v>
+        <v>-31.461</v>
       </c>
     </row>
     <row r="268">
@@ -13161,10 +13161,10 @@
         <v>0.6</v>
       </c>
       <c r="I268" t="n">
-        <v>-1.0537</v>
+        <v>-1.0487</v>
       </c>
       <c r="J268" t="n">
-        <v>-31.611</v>
+        <v>-31.461</v>
       </c>
     </row>
     <row r="269">
@@ -13201,10 +13201,10 @@
         <v>0.36</v>
       </c>
       <c r="I269" t="n">
-        <v>-1.5646</v>
+        <v>-1.6225</v>
       </c>
       <c r="J269" t="n">
-        <v>-46.938</v>
+        <v>-48.675</v>
       </c>
     </row>
     <row r="270">
@@ -13241,10 +13241,10 @@
         <v>1.28</v>
       </c>
       <c r="I270" t="n">
-        <v>0.9963</v>
+        <v>0.9719</v>
       </c>
       <c r="J270" t="n">
-        <v>29.889</v>
+        <v>29.157</v>
       </c>
     </row>
     <row r="271">
@@ -13281,10 +13281,10 @@
         <v>1.12</v>
       </c>
       <c r="I271" t="n">
-        <v>0.5947</v>
+        <v>0.5239</v>
       </c>
       <c r="J271" t="n">
-        <v>17.841</v>
+        <v>15.717</v>
       </c>
     </row>
     <row r="272">
@@ -13321,10 +13321,10 @@
         <v>0.8</v>
       </c>
       <c r="I272" t="n">
-        <v>-0.6657999999999999</v>
+        <v>-0.6199</v>
       </c>
       <c r="J272" t="n">
-        <v>-16.645</v>
+        <v>-15.4975</v>
       </c>
     </row>
     <row r="273">
@@ -13361,10 +13361,10 @@
         <v>0.72</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.8582</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="J273" t="n">
-        <v>-21.455</v>
+        <v>-20.5775</v>
       </c>
     </row>
     <row r="274">
@@ -13401,10 +13401,10 @@
         <v>0.64</v>
       </c>
       <c r="I274" t="n">
-        <v>-1.0371</v>
+        <v>-1.0187</v>
       </c>
       <c r="J274" t="n">
-        <v>-25.9275</v>
+        <v>-25.4675</v>
       </c>
     </row>
     <row r="275">
@@ -13441,10 +13441,10 @@
         <v>1.55</v>
       </c>
       <c r="I275" t="n">
-        <v>1.43</v>
+        <v>1.2756</v>
       </c>
       <c r="J275" t="n">
-        <v>35.75</v>
+        <v>31.89</v>
       </c>
     </row>
     <row r="276">
@@ -13481,10 +13481,10 @@
         <v>1.27</v>
       </c>
       <c r="I276" t="n">
-        <v>0.8387</v>
+        <v>0.8015</v>
       </c>
       <c r="J276" t="n">
-        <v>20.9675</v>
+        <v>20.0375</v>
       </c>
     </row>
     <row r="277">
@@ -13521,10 +13521,10 @@
         <v>1.14</v>
       </c>
       <c r="I277" t="n">
-        <v>0.2971</v>
+        <v>0.3286</v>
       </c>
       <c r="J277" t="n">
-        <v>7.4275</v>
+        <v>8.215</v>
       </c>
     </row>
     <row r="278">
@@ -13561,10 +13561,10 @@
         <v>1</v>
       </c>
       <c r="I278" t="n">
-        <v>0.0094</v>
+        <v>0.0011</v>
       </c>
       <c r="J278" t="n">
-        <v>0.235</v>
+        <v>0.0275</v>
       </c>
     </row>
     <row r="279">
@@ -13601,10 +13601,10 @@
         <v>0.97</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.0871</v>
+        <v>-0.0492</v>
       </c>
       <c r="J279" t="n">
-        <v>-2.1775</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="280">
@@ -13641,10 +13641,10 @@
         <v>0.96</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.1099</v>
+        <v>-0.0623</v>
       </c>
       <c r="J280" t="n">
-        <v>-2.7475</v>
+        <v>-1.5575</v>
       </c>
     </row>
     <row r="281">
@@ -13681,10 +13681,10 @@
         <v>0.88</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.2583</v>
+        <v>-0.155</v>
       </c>
       <c r="J281" t="n">
-        <v>-6.4575</v>
+        <v>-3.875</v>
       </c>
     </row>
     <row r="282">
@@ -13721,10 +13721,10 @@
         <v>0.98</v>
       </c>
       <c r="I282" t="n">
-        <v>-0.1775</v>
+        <v>-0.1161</v>
       </c>
       <c r="J282" t="n">
-        <v>-4.26</v>
+        <v>-2.7864</v>
       </c>
     </row>
     <row r="283">
@@ -13761,10 +13761,10 @@
         <v>0.85</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.5741000000000001</v>
+        <v>-0.5145</v>
       </c>
       <c r="J283" t="n">
-        <v>-13.7784</v>
+        <v>-12.348</v>
       </c>
     </row>
     <row r="284">
@@ -13801,10 +13801,10 @@
         <v>0.62</v>
       </c>
       <c r="I284" t="n">
-        <v>-1.1025</v>
+        <v>-1.0907</v>
       </c>
       <c r="J284" t="n">
-        <v>-26.46</v>
+        <v>-26.1768</v>
       </c>
     </row>
     <row r="285">
@@ -13841,10 +13841,10 @@
         <v>1.84</v>
       </c>
       <c r="I285" t="n">
-        <v>1.9016</v>
+        <v>1.6087</v>
       </c>
       <c r="J285" t="n">
-        <v>45.6384</v>
+        <v>38.6088</v>
       </c>
     </row>
     <row r="286">
@@ -13881,10 +13881,10 @@
         <v>1.16</v>
       </c>
       <c r="I286" t="n">
-        <v>0.5068</v>
+        <v>0.4841</v>
       </c>
       <c r="J286" t="n">
-        <v>12.1632</v>
+        <v>11.6184</v>
       </c>
     </row>
     <row r="287">
@@ -13921,10 +13921,10 @@
         <v>0.89</v>
       </c>
       <c r="I287" t="n">
-        <v>-0.1852</v>
+        <v>-0.1337</v>
       </c>
       <c r="J287" t="n">
-        <v>-4.4448</v>
+        <v>-3.2088</v>
       </c>
     </row>
     <row r="288">
@@ -13961,10 +13961,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.3344</v>
+        <v>-0.2149</v>
       </c>
       <c r="J288" t="n">
-        <v>-8.025600000000001</v>
+        <v>-5.1576</v>
       </c>
     </row>
     <row r="289">
@@ -14001,10 +14001,10 @@
         <v>0.52</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.7248</v>
+        <v>-0.4895</v>
       </c>
       <c r="J289" t="n">
-        <v>-17.3952</v>
+        <v>-11.748</v>
       </c>
     </row>
     <row r="290">
@@ -14041,10 +14041,10 @@
         <v>1.27</v>
       </c>
       <c r="I290" t="n">
-        <v>0.5221</v>
+        <v>0.6156</v>
       </c>
       <c r="J290" t="n">
-        <v>12.5304</v>
+        <v>14.7744</v>
       </c>
     </row>
     <row r="291">
@@ -14081,10 +14081,10 @@
         <v>0.93</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.1057</v>
+        <v>-0.0892</v>
       </c>
       <c r="J291" t="n">
-        <v>-2.5368</v>
+        <v>-2.1408</v>
       </c>
     </row>
     <row r="292">
@@ -14121,10 +14121,10 @@
         <v>1.33</v>
       </c>
       <c r="I292" t="n">
-        <v>0.916</v>
+        <v>0.898</v>
       </c>
       <c r="J292" t="n">
-        <v>25.648</v>
+        <v>25.144</v>
       </c>
     </row>
     <row r="293">
@@ -14161,10 +14161,10 @@
         <v>1.26</v>
       </c>
       <c r="I293" t="n">
-        <v>0.7549</v>
+        <v>0.731</v>
       </c>
       <c r="J293" t="n">
-        <v>21.1372</v>
+        <v>20.468</v>
       </c>
     </row>
     <row r="294">
@@ -14201,10 +14201,10 @@
         <v>1.13</v>
       </c>
       <c r="I294" t="n">
-        <v>0.4133</v>
+        <v>0.403</v>
       </c>
       <c r="J294" t="n">
-        <v>11.5724</v>
+        <v>11.284</v>
       </c>
     </row>
     <row r="295">
@@ -14241,10 +14241,10 @@
         <v>1.1</v>
       </c>
       <c r="I295" t="n">
-        <v>0.3111</v>
+        <v>0.3231</v>
       </c>
       <c r="J295" t="n">
-        <v>8.710800000000001</v>
+        <v>9.046799999999999</v>
       </c>
     </row>
     <row r="296">
@@ -14281,10 +14281,10 @@
         <v>0.68</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.9769</v>
+        <v>-0.9496</v>
       </c>
       <c r="J296" t="n">
-        <v>-27.3532</v>
+        <v>-26.5888</v>
       </c>
     </row>
     <row r="297">
@@ -14321,10 +14321,10 @@
         <v>1.13</v>
       </c>
       <c r="I297" t="n">
-        <v>0.2893</v>
+        <v>0.3155</v>
       </c>
       <c r="J297" t="n">
-        <v>8.1004</v>
+        <v>8.834</v>
       </c>
     </row>
     <row r="298">
@@ -14361,10 +14361,10 @@
         <v>1.06</v>
       </c>
       <c r="I298" t="n">
-        <v>0.1686</v>
+        <v>0.1692</v>
       </c>
       <c r="J298" t="n">
-        <v>4.7208</v>
+        <v>4.7376</v>
       </c>
     </row>
     <row r="299">
@@ -14401,10 +14401,10 @@
         <v>0.97</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.06859999999999999</v>
+        <v>-0.0477</v>
       </c>
       <c r="J299" t="n">
-        <v>-1.9208</v>
+        <v>-1.3356</v>
       </c>
     </row>
     <row r="300">
@@ -14441,10 +14441,10 @@
         <v>0.92</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.1805</v>
+        <v>-0.1083</v>
       </c>
       <c r="J300" t="n">
-        <v>-5.054</v>
+        <v>-3.0324</v>
       </c>
     </row>
     <row r="301">
@@ -14481,10 +14481,10 @@
         <v>0.76</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.4329</v>
+        <v>-0.2748</v>
       </c>
       <c r="J301" t="n">
-        <v>-12.1212</v>
+        <v>-7.6944</v>
       </c>
     </row>
     <row r="302">
@@ -14521,10 +14521,10 @@
         <v>1.22</v>
       </c>
       <c r="I302" t="n">
-        <v>0.4073</v>
+        <v>0.3601</v>
       </c>
       <c r="J302" t="n">
-        <v>12.219</v>
+        <v>10.803</v>
       </c>
     </row>
     <row r="303">
@@ -14561,10 +14561,10 @@
         <v>1.12</v>
       </c>
       <c r="I303" t="n">
-        <v>0.2561</v>
+        <v>0.2165</v>
       </c>
       <c r="J303" t="n">
-        <v>7.683</v>
+        <v>6.495</v>
       </c>
     </row>
     <row r="304">
@@ -14601,10 +14601,10 @@
         <v>0.99</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.0485</v>
+        <v>-0.0216</v>
       </c>
       <c r="J304" t="n">
-        <v>-1.455</v>
+        <v>-0.648</v>
       </c>
     </row>
     <row r="305">
@@ -14641,10 +14641,10 @@
         <v>0.89</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.249</v>
+        <v>-0.1468</v>
       </c>
       <c r="J305" t="n">
-        <v>-7.47</v>
+        <v>-4.404</v>
       </c>
     </row>
     <row r="306">
@@ -14681,10 +14681,10 @@
         <v>0.85</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.3127</v>
+        <v>-0.1896</v>
       </c>
       <c r="J306" t="n">
-        <v>-9.381</v>
+        <v>-5.688</v>
       </c>
     </row>
     <row r="307">
@@ -14721,10 +14721,10 @@
         <v>1.44</v>
       </c>
       <c r="I307" t="n">
-        <v>0.6768</v>
+        <v>0.5924</v>
       </c>
       <c r="J307" t="n">
-        <v>20.304</v>
+        <v>17.772</v>
       </c>
     </row>
     <row r="308">
@@ -14761,10 +14761,10 @@
         <v>1.14</v>
       </c>
       <c r="I308" t="n">
-        <v>0.2741</v>
+        <v>0.2226</v>
       </c>
       <c r="J308" t="n">
-        <v>8.223000000000001</v>
+        <v>6.678</v>
       </c>
     </row>
     <row r="309">
@@ -14801,10 +14801,10 @@
         <v>1.13</v>
       </c>
       <c r="I309" t="n">
-        <v>0.2578</v>
+        <v>0.209</v>
       </c>
       <c r="J309" t="n">
-        <v>7.734</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="310">
@@ -14841,10 +14841,10 @@
         <v>0.79</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.4089</v>
+        <v>-0.2549</v>
       </c>
       <c r="J310" t="n">
-        <v>-12.267</v>
+        <v>-7.647</v>
       </c>
     </row>
     <row r="311">
@@ -14881,10 +14881,10 @@
         <v>0.76</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.4501</v>
+        <v>-0.2844</v>
       </c>
       <c r="J311" t="n">
-        <v>-13.503</v>
+        <v>-8.532</v>
       </c>
     </row>
     <row r="312">
@@ -14921,10 +14921,10 @@
         <v>1.43</v>
       </c>
       <c r="I312" t="n">
-        <v>1.0759</v>
+        <v>1.0492</v>
       </c>
       <c r="J312" t="n">
-        <v>27.9734</v>
+        <v>27.2792</v>
       </c>
     </row>
     <row r="313">
@@ -14961,10 +14961,10 @@
         <v>1.34</v>
       </c>
       <c r="I313" t="n">
-        <v>0.8807</v>
+        <v>0.8831</v>
       </c>
       <c r="J313" t="n">
-        <v>22.8982</v>
+        <v>22.9606</v>
       </c>
     </row>
     <row r="314">
@@ -15001,10 +15001,10 @@
         <v>1.22</v>
       </c>
       <c r="I314" t="n">
-        <v>0.5846</v>
+        <v>0.606</v>
       </c>
       <c r="J314" t="n">
-        <v>15.1996</v>
+        <v>15.756</v>
       </c>
     </row>
     <row r="315">
@@ -15041,10 +15041,10 @@
         <v>1.07</v>
       </c>
       <c r="I315" t="n">
-        <v>0.1441</v>
+        <v>0.2135</v>
       </c>
       <c r="J315" t="n">
-        <v>3.7466</v>
+        <v>5.551</v>
       </c>
     </row>
     <row r="316">
@@ -15081,10 +15081,10 @@
         <v>0.97</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.263</v>
+        <v>-0.1835</v>
       </c>
       <c r="J316" t="n">
-        <v>-6.838</v>
+        <v>-4.771</v>
       </c>
     </row>
     <row r="317">
@@ -15121,10 +15121,10 @@
         <v>1.39</v>
       </c>
       <c r="I317" t="n">
-        <v>0.6854</v>
+        <v>0.8478</v>
       </c>
       <c r="J317" t="n">
-        <v>17.8204</v>
+        <v>22.0428</v>
       </c>
     </row>
     <row r="318">
@@ -15161,10 +15161,10 @@
         <v>0.91</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.1308</v>
+        <v>-0.109</v>
       </c>
       <c r="J318" t="n">
-        <v>-3.4008</v>
+        <v>-2.834</v>
       </c>
     </row>
     <row r="319">
@@ -15201,10 +15201,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.3235</v>
+        <v>-0.2118</v>
       </c>
       <c r="J319" t="n">
-        <v>-8.411</v>
+        <v>-5.5068</v>
       </c>
     </row>
     <row r="320">
@@ -15241,10 +15241,10 @@
         <v>0.68</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.5158</v>
+        <v>-0.3376</v>
       </c>
       <c r="J320" t="n">
-        <v>-13.4108</v>
+        <v>-8.7776</v>
       </c>
     </row>
     <row r="321">
@@ -15281,10 +15281,10 @@
         <v>0.5</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.7447</v>
+        <v>-0.5047</v>
       </c>
       <c r="J321" t="n">
-        <v>-19.3622</v>
+        <v>-13.1222</v>
       </c>
     </row>
     <row r="322">
@@ -15321,10 +15321,10 @@
         <v>1.14</v>
       </c>
       <c r="I322" t="n">
-        <v>0.2978</v>
+        <v>0.2519</v>
       </c>
       <c r="J322" t="n">
-        <v>8.933999999999999</v>
+        <v>7.557</v>
       </c>
     </row>
     <row r="323">
@@ -15361,10 +15361,10 @@
         <v>1.06</v>
       </c>
       <c r="I323" t="n">
-        <v>0.1604</v>
+        <v>0.1258</v>
       </c>
       <c r="J323" t="n">
-        <v>4.812</v>
+        <v>3.774</v>
       </c>
     </row>
     <row r="324">
@@ -15401,10 +15401,10 @@
         <v>0.99</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.0281</v>
+        <v>-0.0199</v>
       </c>
       <c r="J324" t="n">
-        <v>-0.843</v>
+        <v>-0.597</v>
       </c>
     </row>
     <row r="325">
@@ -15441,10 +15441,10 @@
         <v>0.89</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.241</v>
+        <v>-0.1439</v>
       </c>
       <c r="J325" t="n">
-        <v>-7.23</v>
+        <v>-4.317</v>
       </c>
     </row>
     <row r="326">
@@ -15481,10 +15481,10 @@
         <v>0.86</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.29</v>
+        <v>-0.1761</v>
       </c>
       <c r="J326" t="n">
-        <v>-8.699999999999999</v>
+        <v>-5.283</v>
       </c>
     </row>
     <row r="327">
@@ -15521,10 +15521,10 @@
         <v>1.38</v>
       </c>
       <c r="I327" t="n">
-        <v>0.5937</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="J327" t="n">
-        <v>17.811</v>
+        <v>15.408</v>
       </c>
     </row>
     <row r="328">
@@ -15561,10 +15561,10 @@
         <v>1.31</v>
       </c>
       <c r="I328" t="n">
-        <v>0.5051</v>
+        <v>0.4308</v>
       </c>
       <c r="J328" t="n">
-        <v>15.153</v>
+        <v>12.924</v>
       </c>
     </row>
     <row r="329">
@@ -15601,10 +15601,10 @@
         <v>1.02</v>
       </c>
       <c r="I329" t="n">
-        <v>0.0183</v>
+        <v>0.0383</v>
       </c>
       <c r="J329" t="n">
-        <v>0.549</v>
+        <v>1.149</v>
       </c>
     </row>
     <row r="330">
@@ -15641,10 +15641,10 @@
         <v>0.91</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.2345</v>
+        <v>-0.1324</v>
       </c>
       <c r="J330" t="n">
-        <v>-7.035</v>
+        <v>-3.972</v>
       </c>
     </row>
     <row r="331">
@@ -15681,10 +15681,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.3872</v>
+        <v>-0.2385</v>
       </c>
       <c r="J331" t="n">
-        <v>-11.616</v>
+        <v>-7.155</v>
       </c>
     </row>
     <row r="332">
@@ -15721,10 +15721,10 @@
         <v>1.65</v>
       </c>
       <c r="I332" t="n">
-        <v>1.4519</v>
+        <v>1.2979</v>
       </c>
       <c r="J332" t="n">
-        <v>34.8456</v>
+        <v>31.1496</v>
       </c>
     </row>
     <row r="333">
@@ -15761,10 +15761,10 @@
         <v>1.51</v>
       </c>
       <c r="I333" t="n">
-        <v>1.1803</v>
+        <v>1.1274</v>
       </c>
       <c r="J333" t="n">
-        <v>28.3272</v>
+        <v>27.0576</v>
       </c>
     </row>
     <row r="334">
@@ -15801,10 +15801,10 @@
         <v>1.37</v>
       </c>
       <c r="I334" t="n">
-        <v>0.8782</v>
+        <v>0.9185</v>
       </c>
       <c r="J334" t="n">
-        <v>21.0768</v>
+        <v>22.044</v>
       </c>
     </row>
     <row r="335">
@@ -15841,10 +15841,10 @@
         <v>1.15</v>
       </c>
       <c r="I335" t="n">
-        <v>0.318</v>
+        <v>0.4087</v>
       </c>
       <c r="J335" t="n">
-        <v>7.632</v>
+        <v>9.8088</v>
       </c>
     </row>
     <row r="336">
@@ -15881,10 +15881,10 @@
         <v>0.96</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.3328</v>
+        <v>-0.2474</v>
       </c>
       <c r="J336" t="n">
-        <v>-7.9872</v>
+        <v>-5.9376</v>
       </c>
     </row>
     <row r="337">
@@ -15921,10 +15921,10 @@
         <v>0.97</v>
       </c>
       <c r="I337" t="n">
-        <v>0.0439</v>
+        <v>-0.0043</v>
       </c>
       <c r="J337" t="n">
-        <v>1.0536</v>
+        <v>-0.1032</v>
       </c>
     </row>
     <row r="338">
@@ -15961,10 +15961,10 @@
         <v>0.83</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.2061</v>
+        <v>-0.1748</v>
       </c>
       <c r="J338" t="n">
-        <v>-4.9464</v>
+        <v>-4.1952</v>
       </c>
     </row>
     <row r="339">
@@ -16001,10 +16001,10 @@
         <v>0.63</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.5448</v>
+        <v>-0.366</v>
       </c>
       <c r="J339" t="n">
-        <v>-13.0752</v>
+        <v>-8.784000000000001</v>
       </c>
     </row>
     <row r="340">
@@ -16041,10 +16041,10 @@
         <v>0.62</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.5591</v>
+        <v>-0.3754</v>
       </c>
       <c r="J340" t="n">
-        <v>-13.4184</v>
+        <v>-9.009600000000001</v>
       </c>
     </row>
     <row r="341">
@@ -16081,10 +16081,10 @@
         <v>0.6</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.5871</v>
+        <v>-0.3941</v>
       </c>
       <c r="J341" t="n">
-        <v>-14.0904</v>
+        <v>-9.458399999999999</v>
       </c>
     </row>
     <row r="342">
@@ -16121,10 +16121,10 @@
         <v>1.57</v>
       </c>
       <c r="I342" t="n">
-        <v>1.303</v>
+        <v>1.2025</v>
       </c>
       <c r="J342" t="n">
-        <v>28.666</v>
+        <v>26.455</v>
       </c>
     </row>
     <row r="343">
@@ -16161,10 +16161,10 @@
         <v>1.52</v>
       </c>
       <c r="I343" t="n">
-        <v>1.2042</v>
+        <v>1.1411</v>
       </c>
       <c r="J343" t="n">
-        <v>26.4924</v>
+        <v>25.1042</v>
       </c>
     </row>
     <row r="344">
@@ -16201,10 +16201,10 @@
         <v>1.45</v>
       </c>
       <c r="I344" t="n">
-        <v>1.0602</v>
+        <v>1.0538</v>
       </c>
       <c r="J344" t="n">
-        <v>23.3244</v>
+        <v>23.1836</v>
       </c>
     </row>
     <row r="345">
@@ -16241,10 +16241,10 @@
         <v>1.18</v>
       </c>
       <c r="I345" t="n">
-        <v>0.3972</v>
+        <v>0.4875</v>
       </c>
       <c r="J345" t="n">
-        <v>8.7384</v>
+        <v>10.725</v>
       </c>
     </row>
     <row r="346">
@@ -16281,10 +16281,10 @@
         <v>0.88</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.5604</v>
+        <v>-0.4883</v>
       </c>
       <c r="J346" t="n">
-        <v>-12.3288</v>
+        <v>-10.7426</v>
       </c>
     </row>
     <row r="347">
@@ -16321,10 +16321,10 @@
         <v>0.93</v>
       </c>
       <c r="I347" t="n">
-        <v>-0.0424</v>
+        <v>-0.06320000000000001</v>
       </c>
       <c r="J347" t="n">
-        <v>-0.9328</v>
+        <v>-1.3904</v>
       </c>
     </row>
     <row r="348">
@@ -16361,10 +16361,10 @@
         <v>0.91</v>
       </c>
       <c r="I348" t="n">
-        <v>-0.0786</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="J348" t="n">
-        <v>-1.7292</v>
+        <v>-1.936</v>
       </c>
     </row>
     <row r="349">
@@ -16401,10 +16401,10 @@
         <v>0.67</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.4928</v>
+        <v>-0.331</v>
       </c>
       <c r="J349" t="n">
-        <v>-10.8416</v>
+        <v>-7.282</v>
       </c>
     </row>
     <row r="350">
@@ -16441,10 +16441,10 @@
         <v>0.65</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.5221</v>
+        <v>-0.3497</v>
       </c>
       <c r="J350" t="n">
-        <v>-11.4862</v>
+        <v>-7.6934</v>
       </c>
     </row>
     <row r="351">
@@ -16481,10 +16481,10 @@
         <v>0.57</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.6328</v>
+        <v>-0.4247</v>
       </c>
       <c r="J351" t="n">
-        <v>-13.9216</v>
+        <v>-9.343400000000001</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/5206/event_5206_evp_summary.xlsx
+++ b/database/event/5206/event_5206_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.9573</v>
+        <v>5.0578</v>
       </c>
       <c r="C2" t="n">
-        <v>2.0598</v>
+        <v>2.1016</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6</v>
+        <v>1.6782</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9573</v>
+        <v>5.0578</v>
       </c>
       <c r="F2" t="n">
-        <v>4.9573</v>
+        <v>5.0578</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>7.5254</v>
+        <v>8.344900000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>10.8159</v>
+        <v>10.4922</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>10.8159</v>
+        <v>10.4922</v>
       </c>
       <c r="N2" t="n">
         <v>347</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.9122</v>
+        <v>3.7367</v>
       </c>
       <c r="C3" t="n">
-        <v>1.6256</v>
+        <v>1.5526</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1281</v>
+        <v>1.0768</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9122</v>
+        <v>3.7367</v>
       </c>
       <c r="F3" t="n">
-        <v>3.9122</v>
+        <v>3.7367</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>5.2307</v>
+        <v>5.4536</v>
       </c>
       <c r="I3" t="n">
-        <v>6.1457</v>
+        <v>6.0378</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>6.1457</v>
+        <v>6.0378</v>
       </c>
       <c r="N3" t="n">
         <v>246</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.8052</v>
+        <v>3.5886</v>
       </c>
       <c r="C4" t="n">
-        <v>1.5811</v>
+        <v>1.4911</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0798</v>
+        <v>1.0094</v>
       </c>
       <c r="E4" t="n">
-        <v>3.8052</v>
+        <v>3.5886</v>
       </c>
       <c r="F4" t="n">
-        <v>3.8052</v>
+        <v>3.5886</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>4.9957</v>
+        <v>5.1293</v>
       </c>
       <c r="I4" t="n">
-        <v>5.8696</v>
+        <v>5.6788</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>5.8696</v>
+        <v>5.6788</v>
       </c>
       <c r="N4" t="n">
         <v>164</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.3751</v>
+        <v>3.2307</v>
       </c>
       <c r="C5" t="n">
-        <v>1.4024</v>
+        <v>1.3424</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8857</v>
+        <v>0.8465</v>
       </c>
       <c r="E5" t="n">
-        <v>3.3751</v>
+        <v>3.2307</v>
       </c>
       <c r="F5" t="n">
-        <v>3.3751</v>
+        <v>3.2307</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4.0513</v>
+        <v>4.346</v>
       </c>
       <c r="I5" t="n">
-        <v>5.1596</v>
+        <v>5.0627</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>5.1596</v>
+        <v>5.0627</v>
       </c>
       <c r="N5" t="n">
         <v>286</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.6512</v>
+        <v>2.4766</v>
       </c>
       <c r="C6" t="n">
-        <v>1.1016</v>
+        <v>1.029</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5589</v>
+        <v>0.5032</v>
       </c>
       <c r="E6" t="n">
-        <v>2.6512</v>
+        <v>2.4766</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6512</v>
+        <v>2.4766</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2.6512</v>
+        <v>2.6956</v>
       </c>
       <c r="I6" t="n">
-        <v>3.3765</v>
+        <v>3.1402</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3765</v>
+        <v>3.1402</v>
       </c>
       <c r="N6" t="n">
         <v>402</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.5527</v>
+        <v>2.4652</v>
       </c>
       <c r="C7" t="n">
-        <v>1.0607</v>
+        <v>1.0243</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5144</v>
+        <v>0.498</v>
       </c>
       <c r="E7" t="n">
-        <v>2.5527</v>
+        <v>2.4652</v>
       </c>
       <c r="F7" t="n">
-        <v>2.5527</v>
+        <v>2.4652</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2.5527</v>
+        <v>2.6706</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9993</v>
+        <v>2.9567</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9993</v>
+        <v>2.9567</v>
       </c>
       <c r="N7" t="n">
         <v>356</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.4352</v>
+        <v>2.3955</v>
       </c>
       <c r="C8" t="n">
-        <v>1.0118</v>
+        <v>0.9954</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4614</v>
+        <v>0.4663</v>
       </c>
       <c r="E8" t="n">
-        <v>2.4352</v>
+        <v>2.3955</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4352</v>
+        <v>2.3955</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.4352</v>
+        <v>2.5181</v>
       </c>
       <c r="I8" t="n">
-        <v>2.7482</v>
+        <v>3.2477</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>214</v>
+        <v>335</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.7482</v>
+        <v>3.2477</v>
       </c>
       <c r="N8" t="n">
-        <v>214</v>
+        <v>335</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.2565</v>
+        <v>2.3414</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9376</v>
+        <v>0.9729</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3807</v>
+        <v>0.4417</v>
       </c>
       <c r="E9" t="n">
-        <v>2.2565</v>
+        <v>2.3414</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2565</v>
+        <v>2.3414</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.2565</v>
+        <v>2.3998</v>
       </c>
       <c r="I9" t="n">
-        <v>3.3766</v>
+        <v>2.5901</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>335</v>
+        <v>214</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3766</v>
+        <v>2.5901</v>
       </c>
       <c r="N9" t="n">
-        <v>335</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10">
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.1894</v>
+        <v>2.1786</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9097</v>
+        <v>0.9052</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3504</v>
+        <v>0.3675</v>
       </c>
       <c r="E10" t="n">
-        <v>2.1894</v>
+        <v>2.1786</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1894</v>
+        <v>2.1786</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.1894</v>
+        <v>2.1786</v>
       </c>
       <c r="I10" t="n">
-        <v>2.3732</v>
+        <v>2.2923</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.3732</v>
+        <v>2.2923</v>
       </c>
       <c r="N10" t="n">
         <v>161</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.6792</v>
+        <v>1.7129</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6977</v>
+        <v>0.7117</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1201</v>
+        <v>0.1555</v>
       </c>
       <c r="E11" t="n">
-        <v>1.6792</v>
+        <v>1.7129</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6792</v>
+        <v>1.7129</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.6792</v>
+        <v>1.7129</v>
       </c>
       <c r="I11" t="n">
-        <v>1.973</v>
+        <v>1.8964</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.973</v>
+        <v>1.8964</v>
       </c>
       <c r="N11" t="n">
         <v>248</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.4996</v>
+        <v>1.5197</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6231</v>
+        <v>0.6314</v>
       </c>
       <c r="D12" t="n">
-        <v>0.039</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>1.4996</v>
+        <v>1.5197</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4996</v>
+        <v>1.5197</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.4996</v>
+        <v>1.5197</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6255</v>
+        <v>1.599</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.6255</v>
+        <v>1.599</v>
       </c>
       <c r="N12" t="n">
         <v>161</v>
@@ -998,185 +998,185 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.3042</v>
+        <v>1.2837</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5419</v>
+        <v>0.5334</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0492</v>
+        <v>-0.0398</v>
       </c>
       <c r="E13" t="n">
-        <v>1.3042</v>
+        <v>1.2837</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3042</v>
+        <v>1.2837</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.3042</v>
+        <v>1.2837</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4718</v>
+        <v>1.5339</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>214</v>
+        <v>333</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.4718</v>
+        <v>1.5339</v>
       </c>
       <c r="N13" t="n">
-        <v>214</v>
+        <v>333</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.1886</v>
+        <v>1.2103</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4939</v>
+        <v>0.5029</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1014</v>
+        <v>-0.0732</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1886</v>
+        <v>1.2103</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1886</v>
+        <v>1.2103</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1886</v>
+        <v>1.2103</v>
       </c>
       <c r="I14" t="n">
-        <v>1.576</v>
+        <v>1.3063</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>333</v>
+        <v>214</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.576</v>
+        <v>1.3063</v>
       </c>
       <c r="N14" t="n">
-        <v>333</v>
+        <v>214</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.1595</v>
+        <v>1.1676</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4818</v>
+        <v>0.4851</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1146</v>
+        <v>-0.0927</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1595</v>
+        <v>1.1676</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1595</v>
+        <v>1.1676</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1595</v>
+        <v>1.1676</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3085</v>
+        <v>1.326</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>205</v>
+        <v>300</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.3085</v>
+        <v>1.326</v>
       </c>
       <c r="N15" t="n">
-        <v>205</v>
+        <v>300</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.109</v>
+        <v>1.0819</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4608</v>
+        <v>0.4495</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1374</v>
+        <v>-0.1317</v>
       </c>
       <c r="E16" t="n">
-        <v>1.109</v>
+        <v>1.0819</v>
       </c>
       <c r="F16" t="n">
-        <v>1.109</v>
+        <v>1.0819</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.109</v>
+        <v>1.0819</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3566</v>
+        <v>1.1677</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>300</v>
+        <v>205</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.3566</v>
+        <v>1.1677</v>
       </c>
       <c r="N16" t="n">
-        <v>300</v>
+        <v>205</v>
       </c>
     </row>
     <row r="17">
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9748</v>
+        <v>0.9956</v>
       </c>
       <c r="C17" t="n">
-        <v>0.405</v>
+        <v>0.4137</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1979</v>
+        <v>-0.171</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9748</v>
+        <v>0.9956</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9748</v>
+        <v>0.9956</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9748</v>
+        <v>0.9956</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0149</v>
+        <v>1.0213</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.0149</v>
+        <v>1.0213</v>
       </c>
       <c r="N17" t="n">
         <v>172</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8933</v>
+        <v>0.9746</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3712</v>
+        <v>0.405</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2347</v>
+        <v>-0.1805</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8933</v>
+        <v>0.9746</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8933</v>
+        <v>0.9746</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8933</v>
+        <v>0.9746</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0927</v>
+        <v>1.1068</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0927</v>
+        <v>1.1068</v>
       </c>
       <c r="N18" t="n">
         <v>171</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8719</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3623</v>
+        <v>0.373</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2444</v>
+        <v>-0.2156</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8719</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8719</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8719</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1561</v>
+        <v>1.0727</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1561</v>
+        <v>1.0727</v>
       </c>
       <c r="N19" t="n">
         <v>298</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7873</v>
+        <v>0.8501</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3271</v>
+        <v>0.3532</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2826</v>
+        <v>-0.2372</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7873</v>
+        <v>0.8501</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7873</v>
+        <v>0.8501</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7873</v>
+        <v>0.8501</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0439</v>
+        <v>1.0158</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.0439</v>
+        <v>1.0158</v>
       </c>
       <c r="N20" t="n">
         <v>261</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7426</v>
+        <v>0.7491</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3086</v>
+        <v>0.3113</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3028</v>
+        <v>-0.2832</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7426</v>
+        <v>0.7491</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7426</v>
+        <v>0.7491</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7426</v>
+        <v>0.7491</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7731</v>
+        <v>0.7684</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7731</v>
+        <v>0.7684</v>
       </c>
       <c r="N21" t="n">
         <v>160</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6433</v>
+        <v>0.7237</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2673</v>
+        <v>0.3007</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3476</v>
+        <v>-0.2948</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6433</v>
+        <v>0.7237</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6433</v>
+        <v>0.7237</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6433</v>
+        <v>0.7237</v>
       </c>
       <c r="I22" t="n">
-        <v>0.853</v>
+        <v>0.8648</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.853</v>
+        <v>0.8648</v>
       </c>
       <c r="N22" t="n">
         <v>286</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.552</v>
+        <v>0.6153</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2294</v>
+        <v>0.2557</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3888</v>
+        <v>-0.3441</v>
       </c>
       <c r="E23" t="n">
-        <v>0.552</v>
+        <v>0.6153</v>
       </c>
       <c r="F23" t="n">
-        <v>0.552</v>
+        <v>0.6153</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.552</v>
+        <v>0.6153</v>
       </c>
       <c r="I23" t="n">
-        <v>0.703</v>
+        <v>0.7168</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.703</v>
+        <v>0.7168</v>
       </c>
       <c r="N23" t="n">
         <v>298</v>
@@ -1504,78 +1504,78 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5159</v>
+        <v>0.5225</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2144</v>
+        <v>0.2171</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4051</v>
+        <v>-0.3864</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5159</v>
+        <v>0.5225</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5159</v>
+        <v>0.5225</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5159</v>
+        <v>0.5225</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.6244</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>205</v>
+        <v>262</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.6244</v>
       </c>
       <c r="N24" t="n">
-        <v>205</v>
+        <v>262</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4116</v>
+        <v>0.4666</v>
       </c>
       <c r="C25" t="n">
-        <v>0.171</v>
+        <v>0.1939</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4522</v>
+        <v>-0.4118</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4116</v>
+        <v>0.4666</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4116</v>
+        <v>0.4666</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4116</v>
+        <v>0.4666</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4645</v>
+        <v>0.5036</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4645</v>
+        <v>0.5036</v>
       </c>
       <c r="N25" t="n">
         <v>205</v>
@@ -1596,139 +1596,139 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4096</v>
+        <v>0.3769</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1702</v>
+        <v>0.1566</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4531</v>
+        <v>-0.4526</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4096</v>
+        <v>0.3769</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4096</v>
+        <v>0.3769</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4096</v>
+        <v>0.3769</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5431</v>
+        <v>0.4068</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>262</v>
+        <v>205</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.5431</v>
+        <v>0.4068</v>
       </c>
       <c r="N26" t="n">
-        <v>262</v>
+        <v>205</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3515</v>
+        <v>0.3421</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1461</v>
+        <v>0.1421</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4793</v>
+        <v>-0.4685</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3515</v>
+        <v>0.3421</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3515</v>
+        <v>0.3421</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3515</v>
+        <v>0.3421</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3967</v>
+        <v>0.3985</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>214</v>
+        <v>332</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3967</v>
+        <v>0.3985</v>
       </c>
       <c r="N27" t="n">
-        <v>214</v>
+        <v>332</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.3193</v>
+        <v>0.3196</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1327</v>
+        <v>0.1328</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4939</v>
+        <v>-0.4787</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3193</v>
+        <v>0.3196</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3193</v>
+        <v>0.3196</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3193</v>
+        <v>0.3196</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4066</v>
+        <v>0.345</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>332</v>
+        <v>214</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.4066</v>
+        <v>0.345</v>
       </c>
       <c r="N28" t="n">
-        <v>332</v>
+        <v>214</v>
       </c>
     </row>
     <row r="29">
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.2059</v>
+        <v>-0.1986</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0856</v>
+        <v>-0.0825</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.731</v>
+        <v>-0.7146</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.2059</v>
+        <v>-0.1986</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.2059</v>
+        <v>-0.1986</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.2059</v>
+        <v>-0.1986</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2232</v>
+        <v>-0.209</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.2232</v>
+        <v>-0.209</v>
       </c>
       <c r="N29" t="n">
         <v>161</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.2849</v>
+        <v>-0.2023</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1184</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7665999999999999</v>
+        <v>-0.7163</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.2849</v>
+        <v>-0.2023</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.2849</v>
+        <v>-0.2023</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.2849</v>
+        <v>-0.2023</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3629</v>
+        <v>-0.2357</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.3629</v>
+        <v>-0.2357</v>
       </c>
       <c r="N30" t="n">
         <v>250</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3529</v>
+        <v>-0.419</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1466</v>
+        <v>-0.1741</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7973</v>
+        <v>-0.8149</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3529</v>
+        <v>-0.419</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.3529</v>
+        <v>-0.419</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.3529</v>
+        <v>-0.419</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3983</v>
+        <v>-0.4522</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.3983</v>
+        <v>-0.4522</v>
       </c>
       <c r="N31" t="n">
         <v>205</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.3649</v>
+        <v>-0.447</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1516</v>
+        <v>-0.1857</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8027</v>
+        <v>-0.8277</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.3649</v>
+        <v>-0.447</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.3649</v>
+        <v>-0.447</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.3649</v>
+        <v>-0.447</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.3955</v>
+        <v>-0.4703</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.3955</v>
+        <v>-0.4703</v>
       </c>
       <c r="N32" t="n">
         <v>161</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.7511</v>
+        <v>-0.842</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.3121</v>
+        <v>-0.3499</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9771</v>
+        <v>-1.0075</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.7511</v>
+        <v>-0.842</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.7511</v>
+        <v>-0.842</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.7511</v>
+        <v>-0.842</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.8476</v>
+        <v>-0.9088000000000001</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.8476</v>
+        <v>-0.9088000000000001</v>
       </c>
       <c r="N33" t="n">
         <v>214</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.0179</v>
+        <v>-0.9885</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.4229</v>
+        <v>-0.4107</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.0975</v>
+        <v>-1.0742</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.0179</v>
+        <v>-0.9885</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.0179</v>
+        <v>-0.9885</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.0179</v>
+        <v>-0.9885</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.1487</v>
+        <v>-1.0669</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.1487</v>
+        <v>-1.0669</v>
       </c>
       <c r="N34" t="n">
         <v>106</v>
@@ -2010,139 +2010,139 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Nivera</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.1239</v>
+        <v>-1.0812</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.467</v>
+        <v>-0.4492</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.1454</v>
+        <v>-1.1164</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.1239</v>
+        <v>-1.0812</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.1239</v>
+        <v>-1.0812</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.1239</v>
+        <v>-1.0812</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.2182</v>
+        <v>-1.2279</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.2182</v>
+        <v>-1.2279</v>
       </c>
       <c r="N35" t="n">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>Nivera</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.1886</v>
+        <v>-1.1558</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.4939</v>
+        <v>-0.4802</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.1746</v>
+        <v>-1.1503</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.1886</v>
+        <v>-1.1558</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.1886</v>
+        <v>-1.1558</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.1886</v>
+        <v>-1.1558</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.3965</v>
+        <v>-1.2161</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>217</v>
+        <v>167</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.3965</v>
+        <v>-1.2161</v>
       </c>
       <c r="N36" t="n">
-        <v>217</v>
+        <v>167</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.2109</v>
+        <v>-1.1869</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.5031</v>
+        <v>-0.4932</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1847</v>
+        <v>-1.1645</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.2109</v>
+        <v>-1.1869</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.2109</v>
+        <v>-1.1869</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.2109</v>
+        <v>-1.1869</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.4813</v>
+        <v>-1.314</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>172</v>
+        <v>217</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.4813</v>
+        <v>-1.314</v>
       </c>
       <c r="N37" t="n">
-        <v>172</v>
+        <v>217</v>
       </c>
     </row>
     <row r="38">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2197</v>
+        <v>-1.3261</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.5068</v>
+        <v>-0.551</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1886</v>
+        <v>-1.2279</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2197</v>
+        <v>-1.3261</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.2197</v>
+        <v>-1.3261</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.2197</v>
+        <v>-1.3261</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.3765</v>
+        <v>-1.4313</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.3765</v>
+        <v>-1.4313</v>
       </c>
       <c r="N38" t="n">
         <v>205</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.294</v>
+        <v>-1.3763</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.5377</v>
+        <v>-0.5719</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2222</v>
+        <v>-1.2507</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.294</v>
+        <v>-1.3763</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.294</v>
+        <v>-1.3763</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.294</v>
+        <v>-1.3763</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.4026</v>
+        <v>-1.4481</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.4026</v>
+        <v>-1.4481</v>
       </c>
       <c r="N39" t="n">
         <v>161</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.5798</v>
+        <v>-1.6048</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.6564</v>
+        <v>-0.6667999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3512</v>
+        <v>-1.3547</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.5798</v>
+        <v>-1.6048</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.5798</v>
+        <v>-1.6048</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.5798</v>
+        <v>-1.6048</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.7828</v>
+        <v>-1.7321</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.7828</v>
+        <v>-1.7321</v>
       </c>
       <c r="N40" t="n">
         <v>214</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.8815</v>
+        <v>-1.8055</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.7818000000000001</v>
+        <v>-0.7502</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4874</v>
+        <v>-1.4461</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.8815</v>
+        <v>-1.8055</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.8815</v>
+        <v>-1.8055</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.8815</v>
+        <v>-1.8055</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.0394</v>
+        <v>-1.8997</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.0394</v>
+        <v>-1.8997</v>
       </c>
       <c r="N41" t="n">
         <v>145</v>
@@ -2336,28 +2336,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-2.1218</v>
+        <v>-2.0483</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.8816000000000001</v>
+        <v>-0.8511</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.5959</v>
+        <v>-1.5566</v>
       </c>
       <c r="E42" t="n">
-        <v>-2.1218</v>
+        <v>-2.0483</v>
       </c>
       <c r="F42" t="n">
-        <v>-2.1218</v>
+        <v>-2.0483</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>-2.1218</v>
+        <v>-2.0483</v>
       </c>
       <c r="I42" t="n">
-        <v>-2.3945</v>
+        <v>-2.2108</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>-2.3945</v>
+        <v>-2.2108</v>
       </c>
       <c r="N42" t="n">
         <v>76</v>
@@ -2382,28 +2382,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-2.8636</v>
+        <v>-2.8097</v>
       </c>
       <c r="C43" t="n">
-        <v>-1.1899</v>
+        <v>-1.1675</v>
       </c>
       <c r="D43" t="n">
-        <v>-1.9308</v>
+        <v>-1.9032</v>
       </c>
       <c r="E43" t="n">
-        <v>-2.8636</v>
+        <v>-2.8097</v>
       </c>
       <c r="F43" t="n">
-        <v>-2.8636</v>
+        <v>-2.8097</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-2.8636</v>
+        <v>-2.8097</v>
       </c>
       <c r="I43" t="n">
-        <v>-3.3646</v>
+        <v>-3.1107</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>-3.3646</v>
+        <v>-3.1107</v>
       </c>
       <c r="N43" t="n">
         <v>100</v>
@@ -2521,10 +2521,10 @@
         <v>1.53</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9169</v>
+        <v>0.8792</v>
       </c>
       <c r="J2" t="n">
-        <v>25.6732</v>
+        <v>24.6176</v>
       </c>
     </row>
     <row r="3">
@@ -2561,10 +2561,10 @@
         <v>1.4</v>
       </c>
       <c r="I3" t="n">
-        <v>0.717</v>
+        <v>0.6992</v>
       </c>
       <c r="J3" t="n">
-        <v>20.076</v>
+        <v>19.5776</v>
       </c>
     </row>
     <row r="4">
@@ -2601,10 +2601,10 @@
         <v>1.28</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5254</v>
+        <v>0.5241</v>
       </c>
       <c r="J4" t="n">
-        <v>14.7112</v>
+        <v>14.6748</v>
       </c>
     </row>
     <row r="5">
@@ -2641,10 +2641,10 @@
         <v>1.01</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002</v>
+        <v>0.0176</v>
       </c>
       <c r="J5" t="n">
-        <v>0.056</v>
+        <v>0.4928</v>
       </c>
     </row>
     <row r="6">
@@ -2681,10 +2681,10 @@
         <v>0.85</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2103</v>
+        <v>-0.219</v>
       </c>
       <c r="J6" t="n">
-        <v>-5.8884</v>
+        <v>-6.132</v>
       </c>
     </row>
     <row r="7">
@@ -2721,10 +2721,10 @@
         <v>0.83</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5034</v>
+        <v>-0.4902</v>
       </c>
       <c r="J7" t="n">
-        <v>-14.0952</v>
+        <v>-13.7256</v>
       </c>
     </row>
     <row r="8">
@@ -2761,10 +2761,10 @@
         <v>1.06</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2812</v>
+        <v>0.2667</v>
       </c>
       <c r="J8" t="n">
-        <v>7.8736</v>
+        <v>7.4676</v>
       </c>
     </row>
     <row r="9">
@@ -2801,10 +2801,10 @@
         <v>1.02</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1388</v>
+        <v>0.1307</v>
       </c>
       <c r="J9" t="n">
-        <v>3.8864</v>
+        <v>3.6596</v>
       </c>
     </row>
     <row r="10">
@@ -2841,10 +2841,10 @@
         <v>0.95</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1646</v>
+        <v>-0.178</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.6088</v>
+        <v>-4.984</v>
       </c>
     </row>
     <row r="11">
@@ -2881,10 +2881,10 @@
         <v>0.51</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.2927</v>
+        <v>-1.1733</v>
       </c>
       <c r="J11" t="n">
-        <v>-36.1956</v>
+        <v>-32.8524</v>
       </c>
     </row>
     <row r="12">
@@ -2921,10 +2921,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4606</v>
+        <v>-0.468</v>
       </c>
       <c r="J12" t="n">
-        <v>-9.672599999999999</v>
+        <v>-9.827999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -2961,10 +2961,10 @@
         <v>1.35</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7245</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>15.2145</v>
+        <v>14.511</v>
       </c>
     </row>
     <row r="14">
@@ -3001,10 +3001,10 @@
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0078</v>
+        <v>0.0055</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1638</v>
+        <v>0.1155</v>
       </c>
     </row>
     <row r="15">
@@ -3041,10 +3041,10 @@
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0078</v>
+        <v>0.0055</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1638</v>
+        <v>0.1155</v>
       </c>
     </row>
     <row r="16">
@@ -3081,10 +3081,10 @@
         <v>0.85</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1824</v>
+        <v>-0.1971</v>
       </c>
       <c r="J16" t="n">
-        <v>-3.8304</v>
+        <v>-4.1391</v>
       </c>
     </row>
     <row r="17">
@@ -3121,10 +3121,10 @@
         <v>0.16</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.0714</v>
+        <v>-1.825</v>
       </c>
       <c r="J17" t="n">
-        <v>-43.4994</v>
+        <v>-38.325</v>
       </c>
     </row>
     <row r="18">
@@ -3161,10 +3161,10 @@
         <v>1.05</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4064</v>
+        <v>0.3474</v>
       </c>
       <c r="J18" t="n">
-        <v>8.5344</v>
+        <v>7.2954</v>
       </c>
     </row>
     <row r="19">
@@ -3201,10 +3201,10 @@
         <v>0.98</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0806</v>
+        <v>0.0225</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6926</v>
+        <v>0.4725</v>
       </c>
     </row>
     <row r="20">
@@ -3241,10 +3241,10 @@
         <v>0.6</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9994</v>
+        <v>-0.9360000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>-20.9874</v>
+        <v>-19.656</v>
       </c>
     </row>
     <row r="21">
@@ -3281,10 +3281,10 @@
         <v>0.57</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.072</v>
+        <v>-0.9976</v>
       </c>
       <c r="J21" t="n">
-        <v>-22.512</v>
+        <v>-20.9496</v>
       </c>
     </row>
     <row r="22">
@@ -3321,10 +3321,10 @@
         <v>1.15</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3364</v>
+        <v>0.3399</v>
       </c>
       <c r="J22" t="n">
-        <v>12.1104</v>
+        <v>12.2364</v>
       </c>
     </row>
     <row r="23">
@@ -3361,10 +3361,10 @@
         <v>1.09</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2188</v>
+        <v>0.2276</v>
       </c>
       <c r="J23" t="n">
-        <v>7.8768</v>
+        <v>8.1936</v>
       </c>
     </row>
     <row r="24">
@@ -3401,10 +3401,10 @@
         <v>0.89</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1488</v>
+        <v>-0.161</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.3568</v>
+        <v>-5.796</v>
       </c>
     </row>
     <row r="25">
@@ -3441,10 +3441,10 @@
         <v>1.21</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4471</v>
+        <v>0.4434</v>
       </c>
       <c r="J25" t="n">
-        <v>16.0956</v>
+        <v>15.9624</v>
       </c>
     </row>
     <row r="26">
@@ -3481,10 +3481,10 @@
         <v>0.82</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2225</v>
+        <v>-0.2353</v>
       </c>
       <c r="J26" t="n">
-        <v>-8.01</v>
+        <v>-8.470800000000001</v>
       </c>
     </row>
     <row r="27">
@@ -3521,10 +3521,10 @@
         <v>0.83</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.5286999999999999</v>
+        <v>-0.5077</v>
       </c>
       <c r="J27" t="n">
-        <v>-19.0332</v>
+        <v>-18.2772</v>
       </c>
     </row>
     <row r="28">
@@ -3561,10 +3561,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.8852</v>
+        <v>-0.8212</v>
       </c>
       <c r="J28" t="n">
-        <v>-31.8672</v>
+        <v>-29.5632</v>
       </c>
     </row>
     <row r="29">
@@ -3601,10 +3601,10 @@
         <v>0.65</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.9829</v>
+        <v>-0.9056</v>
       </c>
       <c r="J29" t="n">
-        <v>-35.3844</v>
+        <v>-32.6016</v>
       </c>
     </row>
     <row r="30">
@@ -3641,10 +3641,10 @@
         <v>1.37</v>
       </c>
       <c r="I30" t="n">
-        <v>1.0414</v>
+        <v>0.9727</v>
       </c>
       <c r="J30" t="n">
-        <v>37.4904</v>
+        <v>35.0172</v>
       </c>
     </row>
     <row r="31">
@@ -3681,10 +3681,10 @@
         <v>1.24</v>
       </c>
       <c r="I31" t="n">
-        <v>0.7471</v>
+        <v>0.6944</v>
       </c>
       <c r="J31" t="n">
-        <v>26.8956</v>
+        <v>24.9984</v>
       </c>
     </row>
     <row r="32">
@@ -3721,10 +3721,10 @@
         <v>1.17</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2473</v>
+        <v>0.2646</v>
       </c>
       <c r="J32" t="n">
-        <v>6.9244</v>
+        <v>7.4088</v>
       </c>
     </row>
     <row r="33">
@@ -3761,10 +3761,10 @@
         <v>0.97</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.0677</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.8956</v>
+        <v>-2.0132</v>
       </c>
     </row>
     <row r="34">
@@ -3801,10 +3801,10 @@
         <v>0.95</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.094</v>
+        <v>-0.1001</v>
       </c>
       <c r="J34" t="n">
-        <v>-2.632</v>
+        <v>-2.8028</v>
       </c>
     </row>
     <row r="35">
@@ -3841,10 +3841,10 @@
         <v>1.6</v>
       </c>
       <c r="I35" t="n">
-        <v>0.7377</v>
+        <v>0.7301</v>
       </c>
       <c r="J35" t="n">
-        <v>20.6556</v>
+        <v>20.4428</v>
       </c>
     </row>
     <row r="36">
@@ -3881,10 +3881,10 @@
         <v>1.19</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2714</v>
+        <v>0.2885</v>
       </c>
       <c r="J36" t="n">
-        <v>7.5992</v>
+        <v>8.077999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -3921,10 +3921,10 @@
         <v>1.01</v>
       </c>
       <c r="I37" t="n">
-        <v>0.0289</v>
+        <v>0.0339</v>
       </c>
       <c r="J37" t="n">
-        <v>0.8092</v>
+        <v>0.9492</v>
       </c>
     </row>
     <row r="38">
@@ -3961,10 +3961,10 @@
         <v>0.9</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1342</v>
+        <v>-0.1469</v>
       </c>
       <c r="J38" t="n">
-        <v>-3.7576</v>
+        <v>-4.1132</v>
       </c>
     </row>
     <row r="39">
@@ -4001,10 +4001,10 @@
         <v>0.7</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.3362</v>
+        <v>-0.3477</v>
       </c>
       <c r="J39" t="n">
-        <v>-9.413600000000001</v>
+        <v>-9.7356</v>
       </c>
     </row>
     <row r="40">
@@ -4041,10 +4041,10 @@
         <v>1.35</v>
       </c>
       <c r="I40" t="n">
-        <v>0.5381</v>
+        <v>0.5289</v>
       </c>
       <c r="J40" t="n">
-        <v>15.0668</v>
+        <v>14.8092</v>
       </c>
     </row>
     <row r="41">
@@ -4081,10 +4081,10 @@
         <v>1.04</v>
       </c>
       <c r="I41" t="n">
-        <v>0.0888</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="J41" t="n">
-        <v>2.4864</v>
+        <v>2.7328</v>
       </c>
     </row>
     <row r="42">
@@ -4121,10 +4121,10 @@
         <v>0.82</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.1975</v>
+        <v>-0.216</v>
       </c>
       <c r="J42" t="n">
-        <v>-5.135</v>
+        <v>-5.616</v>
       </c>
     </row>
     <row r="43">
@@ -4161,10 +4161,10 @@
         <v>0.75</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.2642</v>
+        <v>-0.2822</v>
       </c>
       <c r="J43" t="n">
-        <v>-6.8692</v>
+        <v>-7.3372</v>
       </c>
     </row>
     <row r="44">
@@ -4201,10 +4201,10 @@
         <v>0.65</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.3593</v>
+        <v>-0.3743</v>
       </c>
       <c r="J44" t="n">
-        <v>-9.341799999999999</v>
+        <v>-9.7318</v>
       </c>
     </row>
     <row r="45">
@@ -4241,10 +4241,10 @@
         <v>0.95</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0521</v>
+        <v>-0.0678</v>
       </c>
       <c r="J45" t="n">
-        <v>-1.3546</v>
+        <v>-1.7628</v>
       </c>
     </row>
     <row r="46">
@@ -4281,10 +4281,10 @@
         <v>0.88</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1354</v>
+        <v>-0.1534</v>
       </c>
       <c r="J46" t="n">
-        <v>-3.5204</v>
+        <v>-3.9884</v>
       </c>
     </row>
     <row r="47">
@@ -4321,10 +4321,10 @@
         <v>1.18</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5209</v>
+        <v>0.5077</v>
       </c>
       <c r="J47" t="n">
-        <v>13.5434</v>
+        <v>13.2002</v>
       </c>
     </row>
     <row r="48">
@@ -4361,10 +4361,10 @@
         <v>0.85</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.5295</v>
+        <v>-0.4976</v>
       </c>
       <c r="J48" t="n">
-        <v>-13.767</v>
+        <v>-12.9376</v>
       </c>
     </row>
     <row r="49">
@@ -4401,10 +4401,10 @@
         <v>0.64</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.0563</v>
+        <v>-0.9612000000000001</v>
       </c>
       <c r="J49" t="n">
-        <v>-27.4638</v>
+        <v>-24.9912</v>
       </c>
     </row>
     <row r="50">
@@ -4441,10 +4441,10 @@
         <v>1.74</v>
       </c>
       <c r="I50" t="n">
-        <v>1.4606</v>
+        <v>1.4399</v>
       </c>
       <c r="J50" t="n">
-        <v>37.9756</v>
+        <v>37.4374</v>
       </c>
     </row>
     <row r="51">
@@ -4481,10 +4481,10 @@
         <v>1.32</v>
       </c>
       <c r="I51" t="n">
-        <v>0.8569</v>
+        <v>0.8054</v>
       </c>
       <c r="J51" t="n">
-        <v>22.2794</v>
+        <v>20.9404</v>
       </c>
     </row>
     <row r="52">
@@ -4521,10 +4521,10 @@
         <v>0.89</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.1351</v>
+        <v>-0.1504</v>
       </c>
       <c r="J52" t="n">
-        <v>-3.9179</v>
+        <v>-4.3616</v>
       </c>
     </row>
     <row r="53">
@@ -4561,10 +4561,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.3342</v>
+        <v>-0.3478</v>
       </c>
       <c r="J53" t="n">
-        <v>-9.691800000000001</v>
+        <v>-10.0862</v>
       </c>
     </row>
     <row r="54">
@@ -4601,10 +4601,10 @@
         <v>0.68</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.3437</v>
+        <v>-0.357</v>
       </c>
       <c r="J54" t="n">
-        <v>-9.9673</v>
+        <v>-10.353</v>
       </c>
     </row>
     <row r="55">
@@ -4641,10 +4641,10 @@
         <v>1.17</v>
       </c>
       <c r="I55" t="n">
-        <v>0.4173</v>
+        <v>0.407</v>
       </c>
       <c r="J55" t="n">
-        <v>12.1017</v>
+        <v>11.803</v>
       </c>
     </row>
     <row r="56">
@@ -4681,10 +4681,10 @@
         <v>1.09</v>
       </c>
       <c r="I56" t="n">
-        <v>0.2545</v>
+        <v>0.2535</v>
       </c>
       <c r="J56" t="n">
-        <v>7.3805</v>
+        <v>7.3515</v>
       </c>
     </row>
     <row r="57">
@@ -4721,10 +4721,10 @@
         <v>0.91</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.3198</v>
+        <v>-0.3151</v>
       </c>
       <c r="J57" t="n">
-        <v>-9.2742</v>
+        <v>-9.1379</v>
       </c>
     </row>
     <row r="58">
@@ -4761,10 +4761,10 @@
         <v>0.67</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.9472</v>
+        <v>-0.8727</v>
       </c>
       <c r="J58" t="n">
-        <v>-27.4688</v>
+        <v>-25.3083</v>
       </c>
     </row>
     <row r="59">
@@ -4801,10 +4801,10 @@
         <v>0.67</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.9472</v>
+        <v>-0.8727</v>
       </c>
       <c r="J59" t="n">
-        <v>-27.4688</v>
+        <v>-25.3083</v>
       </c>
     </row>
     <row r="60">
@@ -4841,10 +4841,10 @@
         <v>1.62</v>
       </c>
       <c r="I60" t="n">
-        <v>1.3676</v>
+        <v>1.3323</v>
       </c>
       <c r="J60" t="n">
-        <v>39.6604</v>
+        <v>38.6367</v>
       </c>
     </row>
     <row r="61">
@@ -4881,10 +4881,10 @@
         <v>1.13</v>
       </c>
       <c r="I61" t="n">
-        <v>0.4336</v>
+        <v>0.4193</v>
       </c>
       <c r="J61" t="n">
-        <v>12.5744</v>
+        <v>12.1597</v>
       </c>
     </row>
     <row r="62">
@@ -4921,10 +4921,10 @@
         <v>0.79</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.2376</v>
+        <v>-0.2534</v>
       </c>
       <c r="J62" t="n">
-        <v>-7.128</v>
+        <v>-7.602</v>
       </c>
     </row>
     <row r="63">
@@ -4961,10 +4961,10 @@
         <v>0.68</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.3439</v>
+        <v>-0.3572</v>
       </c>
       <c r="J63" t="n">
-        <v>-10.317</v>
+        <v>-10.716</v>
       </c>
     </row>
     <row r="64">
@@ -5001,10 +5001,10 @@
         <v>0.67</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.3534</v>
+        <v>-0.3663</v>
       </c>
       <c r="J64" t="n">
-        <v>-10.602</v>
+        <v>-10.989</v>
       </c>
     </row>
     <row r="65">
@@ -5041,10 +5041,10 @@
         <v>1.27</v>
       </c>
       <c r="I65" t="n">
-        <v>0.6045</v>
+        <v>0.5789</v>
       </c>
       <c r="J65" t="n">
-        <v>18.135</v>
+        <v>17.367</v>
       </c>
     </row>
     <row r="66">
@@ -5081,10 +5081,10 @@
         <v>1.12</v>
       </c>
       <c r="I66" t="n">
-        <v>0.3167</v>
+        <v>0.3129</v>
       </c>
       <c r="J66" t="n">
-        <v>9.500999999999999</v>
+        <v>9.387</v>
       </c>
     </row>
     <row r="67">
@@ -5121,10 +5121,10 @@
         <v>0.95</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.1895</v>
+        <v>-0.195</v>
       </c>
       <c r="J67" t="n">
-        <v>-5.685</v>
+        <v>-5.85</v>
       </c>
     </row>
     <row r="68">
@@ -5161,10 +5161,10 @@
         <v>0.9</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.3397</v>
+        <v>-0.3356</v>
       </c>
       <c r="J68" t="n">
-        <v>-10.191</v>
+        <v>-10.068</v>
       </c>
     </row>
     <row r="69">
@@ -5201,10 +5201,10 @@
         <v>0.68</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.9134</v>
+        <v>-0.845</v>
       </c>
       <c r="J69" t="n">
-        <v>-27.402</v>
+        <v>-25.35</v>
       </c>
     </row>
     <row r="70">
@@ -5241,10 +5241,10 @@
         <v>1.22</v>
       </c>
       <c r="I70" t="n">
-        <v>0.6888</v>
+        <v>0.6444</v>
       </c>
       <c r="J70" t="n">
-        <v>20.664</v>
+        <v>19.332</v>
       </c>
     </row>
     <row r="71">
@@ -5281,10 +5281,10 @@
         <v>1.09</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3315</v>
+        <v>0.3233</v>
       </c>
       <c r="J71" t="n">
-        <v>9.945</v>
+        <v>9.699</v>
       </c>
     </row>
     <row r="72">
@@ -5321,10 +5321,10 @@
         <v>0.84</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.5063</v>
+        <v>-0.4868</v>
       </c>
       <c r="J72" t="n">
-        <v>-15.189</v>
+        <v>-14.604</v>
       </c>
     </row>
     <row r="73">
@@ -5361,10 +5361,10 @@
         <v>0.75</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.74</v>
+        <v>-0.6939</v>
       </c>
       <c r="J73" t="n">
-        <v>-22.2</v>
+        <v>-20.817</v>
       </c>
     </row>
     <row r="74">
@@ -5401,10 +5401,10 @@
         <v>0.73</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.7903</v>
+        <v>-0.7379</v>
       </c>
       <c r="J74" t="n">
-        <v>-23.709</v>
+        <v>-22.137</v>
       </c>
     </row>
     <row r="75">
@@ -5441,10 +5441,10 @@
         <v>1.32</v>
       </c>
       <c r="I75" t="n">
-        <v>0.9385</v>
+        <v>0.864</v>
       </c>
       <c r="J75" t="n">
-        <v>28.155</v>
+        <v>25.92</v>
       </c>
     </row>
     <row r="76">
@@ -5481,10 +5481,10 @@
         <v>1.21</v>
       </c>
       <c r="I76" t="n">
-        <v>0.6617</v>
+        <v>0.6207</v>
       </c>
       <c r="J76" t="n">
-        <v>19.851</v>
+        <v>18.621</v>
       </c>
     </row>
     <row r="77">
@@ -5521,10 +5521,10 @@
         <v>1.14</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2987</v>
+        <v>0.3086</v>
       </c>
       <c r="J77" t="n">
-        <v>8.961</v>
+        <v>9.257999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -5561,10 +5561,10 @@
         <v>0.99</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.0331</v>
+        <v>-0.0349</v>
       </c>
       <c r="J78" t="n">
-        <v>-0.993</v>
+        <v>-1.047</v>
       </c>
     </row>
     <row r="79">
@@ -5601,10 +5601,10 @@
         <v>0.73</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.3214</v>
+        <v>-0.3307</v>
       </c>
       <c r="J79" t="n">
-        <v>-9.641999999999999</v>
+        <v>-9.920999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -5641,10 +5641,10 @@
         <v>1.7</v>
       </c>
       <c r="I80" t="n">
-        <v>1.1207</v>
+        <v>1.0961</v>
       </c>
       <c r="J80" t="n">
-        <v>33.621</v>
+        <v>32.883</v>
       </c>
     </row>
     <row r="81">
@@ -5681,10 +5681,10 @@
         <v>1.1</v>
       </c>
       <c r="I81" t="n">
-        <v>0.2244</v>
+        <v>0.2368</v>
       </c>
       <c r="J81" t="n">
-        <v>6.732</v>
+        <v>7.104</v>
       </c>
     </row>
     <row r="82">
@@ -5721,10 +5721,10 @@
         <v>1.09</v>
       </c>
       <c r="I82" t="n">
-        <v>0.1674</v>
+        <v>0.1783</v>
       </c>
       <c r="J82" t="n">
-        <v>4.3524</v>
+        <v>4.6358</v>
       </c>
     </row>
     <row r="83">
@@ -5761,10 +5761,10 @@
         <v>1.06</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1191</v>
+        <v>0.1299</v>
       </c>
       <c r="J83" t="n">
-        <v>3.0966</v>
+        <v>3.3774</v>
       </c>
     </row>
     <row r="84">
@@ -5801,10 +5801,10 @@
         <v>0.96</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.0664</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="J84" t="n">
-        <v>-1.7264</v>
+        <v>-1.9474</v>
       </c>
     </row>
     <row r="85">
@@ -5841,10 +5841,10 @@
         <v>1.17</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2861</v>
+        <v>0.2939</v>
       </c>
       <c r="J85" t="n">
-        <v>7.4386</v>
+        <v>7.6414</v>
       </c>
     </row>
     <row r="86">
@@ -5881,10 +5881,10 @@
         <v>0.88</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.1597</v>
+        <v>-0.1721</v>
       </c>
       <c r="J86" t="n">
-        <v>-4.1522</v>
+        <v>-4.4746</v>
       </c>
     </row>
     <row r="87">
@@ -5921,10 +5921,10 @@
         <v>0.95</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.0859</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="J87" t="n">
-        <v>-2.2334</v>
+        <v>-2.4388</v>
       </c>
     </row>
     <row r="88">
@@ -5961,10 +5961,10 @@
         <v>0.83</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.2193</v>
+        <v>-0.2305</v>
       </c>
       <c r="J88" t="n">
-        <v>-5.7018</v>
+        <v>-5.993</v>
       </c>
     </row>
     <row r="89">
@@ -6001,10 +6001,10 @@
         <v>0.63</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.4112</v>
+        <v>-0.4183</v>
       </c>
       <c r="J89" t="n">
-        <v>-10.6912</v>
+        <v>-10.8758</v>
       </c>
     </row>
     <row r="90">
@@ -6041,10 +6041,10 @@
         <v>1.67</v>
       </c>
       <c r="I90" t="n">
-        <v>0.837</v>
+        <v>0.8179</v>
       </c>
       <c r="J90" t="n">
-        <v>21.762</v>
+        <v>21.2654</v>
       </c>
     </row>
     <row r="91">
@@ -6081,10 +6081,10 @@
         <v>1.4</v>
       </c>
       <c r="I91" t="n">
-        <v>0.5345</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="J91" t="n">
-        <v>13.897</v>
+        <v>13.9828</v>
       </c>
     </row>
     <row r="92">
@@ -6121,10 +6121,10 @@
         <v>1.22</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5783</v>
+        <v>0.5679</v>
       </c>
       <c r="J92" t="n">
-        <v>12.1443</v>
+        <v>11.9259</v>
       </c>
     </row>
     <row r="93">
@@ -6161,10 +6161,10 @@
         <v>1.22</v>
       </c>
       <c r="I93" t="n">
-        <v>0.5783</v>
+        <v>0.5679</v>
       </c>
       <c r="J93" t="n">
-        <v>12.1443</v>
+        <v>11.9259</v>
       </c>
     </row>
     <row r="94">
@@ -6201,10 +6201,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.319</v>
+        <v>-0.2933</v>
       </c>
       <c r="J94" t="n">
-        <v>-6.699</v>
+        <v>-6.1593</v>
       </c>
     </row>
     <row r="95">
@@ -6241,10 +6241,10 @@
         <v>1.78</v>
       </c>
       <c r="I95" t="n">
-        <v>1.4459</v>
+        <v>1.4347</v>
       </c>
       <c r="J95" t="n">
-        <v>30.3639</v>
+        <v>30.1287</v>
       </c>
     </row>
     <row r="96">
@@ -6281,10 +6281,10 @@
         <v>1.62</v>
       </c>
       <c r="I96" t="n">
-        <v>1.256</v>
+        <v>1.2333</v>
       </c>
       <c r="J96" t="n">
-        <v>26.376</v>
+        <v>25.8993</v>
       </c>
     </row>
     <row r="97">
@@ -6321,10 +6321,10 @@
         <v>1.74</v>
       </c>
       <c r="I97" t="n">
-        <v>1.1336</v>
+        <v>1.1141</v>
       </c>
       <c r="J97" t="n">
-        <v>23.8056</v>
+        <v>23.3961</v>
       </c>
     </row>
     <row r="98">
@@ -6361,10 +6361,10 @@
         <v>1.47</v>
       </c>
       <c r="I98" t="n">
-        <v>0.8231000000000001</v>
+        <v>0.7952</v>
       </c>
       <c r="J98" t="n">
-        <v>17.2851</v>
+        <v>16.6992</v>
       </c>
     </row>
     <row r="99">
@@ -6401,10 +6401,10 @@
         <v>0.95</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.0987</v>
+        <v>-0.1038</v>
       </c>
       <c r="J99" t="n">
-        <v>-2.0727</v>
+        <v>-2.1798</v>
       </c>
     </row>
     <row r="100">
@@ -6441,10 +6441,10 @@
         <v>1.3</v>
       </c>
       <c r="I100" t="n">
-        <v>0.556</v>
+        <v>0.5527</v>
       </c>
       <c r="J100" t="n">
-        <v>11.676</v>
+        <v>11.6067</v>
       </c>
     </row>
     <row r="101">
@@ -6481,10 +6481,10 @@
         <v>0.66</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3946</v>
+        <v>-0.4004</v>
       </c>
       <c r="J101" t="n">
-        <v>-8.2866</v>
+        <v>-8.4084</v>
       </c>
     </row>
     <row r="102">
@@ -6521,10 +6521,10 @@
         <v>1.65</v>
       </c>
       <c r="I102" t="n">
-        <v>1.2988</v>
+        <v>1.2776</v>
       </c>
       <c r="J102" t="n">
-        <v>28.5736</v>
+        <v>28.1072</v>
       </c>
     </row>
     <row r="103">
@@ -6561,10 +6561,10 @@
         <v>1.47</v>
       </c>
       <c r="I103" t="n">
-        <v>1.0785</v>
+        <v>1.0397</v>
       </c>
       <c r="J103" t="n">
-        <v>23.727</v>
+        <v>22.8734</v>
       </c>
     </row>
     <row r="104">
@@ -6601,10 +6601,10 @@
         <v>1.21</v>
       </c>
       <c r="I104" t="n">
-        <v>0.5609</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="J104" t="n">
-        <v>12.3398</v>
+        <v>12.1198</v>
       </c>
     </row>
     <row r="105">
@@ -6641,10 +6641,10 @@
         <v>1.15</v>
       </c>
       <c r="I105" t="n">
-        <v>0.4096</v>
+        <v>0.4146</v>
       </c>
       <c r="J105" t="n">
-        <v>9.011200000000001</v>
+        <v>9.1212</v>
       </c>
     </row>
     <row r="106">
@@ -6681,10 +6681,10 @@
         <v>1.14</v>
       </c>
       <c r="I106" t="n">
-        <v>0.3832</v>
+        <v>0.3906</v>
       </c>
       <c r="J106" t="n">
-        <v>8.430400000000001</v>
+        <v>8.5932</v>
       </c>
     </row>
     <row r="107">
@@ -6721,10 +6721,10 @@
         <v>0.98</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.007</v>
+        <v>-0.0203</v>
       </c>
       <c r="J107" t="n">
-        <v>-0.154</v>
+        <v>-0.4466</v>
       </c>
     </row>
     <row r="108">
@@ -6761,10 +6761,10 @@
         <v>0.86</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.1551</v>
+        <v>-0.1738</v>
       </c>
       <c r="J108" t="n">
-        <v>-3.4122</v>
+        <v>-3.8236</v>
       </c>
     </row>
     <row r="109">
@@ -6801,10 +6801,10 @@
         <v>0.77</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2436</v>
+        <v>-0.2622</v>
       </c>
       <c r="J109" t="n">
-        <v>-5.3592</v>
+        <v>-5.7684</v>
       </c>
     </row>
     <row r="110">
@@ -6841,10 +6841,10 @@
         <v>0.72</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2912</v>
+        <v>-0.3089</v>
       </c>
       <c r="J110" t="n">
-        <v>-6.4064</v>
+        <v>-6.7958</v>
       </c>
     </row>
     <row r="111">
@@ -6881,10 +6881,10 @@
         <v>0.66</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3481</v>
+        <v>-0.3638</v>
       </c>
       <c r="J111" t="n">
-        <v>-7.6582</v>
+        <v>-8.0036</v>
       </c>
     </row>
     <row r="112">
@@ -6921,10 +6921,10 @@
         <v>1.49</v>
       </c>
       <c r="I112" t="n">
-        <v>1.1047</v>
+        <v>1.0692</v>
       </c>
       <c r="J112" t="n">
-        <v>26.5128</v>
+        <v>25.6608</v>
       </c>
     </row>
     <row r="113">
@@ -6961,10 +6961,10 @@
         <v>1.46</v>
       </c>
       <c r="I113" t="n">
-        <v>1.0673</v>
+        <v>1.0262</v>
       </c>
       <c r="J113" t="n">
-        <v>25.6152</v>
+        <v>24.6288</v>
       </c>
     </row>
     <row r="114">
@@ -7001,10 +7001,10 @@
         <v>1.26</v>
       </c>
       <c r="I114" t="n">
-        <v>0.681</v>
+        <v>0.6577</v>
       </c>
       <c r="J114" t="n">
-        <v>16.344</v>
+        <v>15.7848</v>
       </c>
     </row>
     <row r="115">
@@ -7041,10 +7041,10 @@
         <v>1.22</v>
       </c>
       <c r="I115" t="n">
-        <v>0.5868</v>
+        <v>0.5737</v>
       </c>
       <c r="J115" t="n">
-        <v>14.0832</v>
+        <v>13.7688</v>
       </c>
     </row>
     <row r="116">
@@ -7081,10 +7081,10 @@
         <v>1.15</v>
       </c>
       <c r="I116" t="n">
-        <v>0.4114</v>
+        <v>0.4158</v>
       </c>
       <c r="J116" t="n">
-        <v>9.8736</v>
+        <v>9.979200000000001</v>
       </c>
     </row>
     <row r="117">
@@ -7121,10 +7121,10 @@
         <v>1.16</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4828</v>
+        <v>0.4517</v>
       </c>
       <c r="J117" t="n">
-        <v>11.5872</v>
+        <v>10.8408</v>
       </c>
     </row>
     <row r="118">
@@ -7161,10 +7161,10 @@
         <v>0.91</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.08840000000000001</v>
+        <v>-0.1087</v>
       </c>
       <c r="J118" t="n">
-        <v>-2.1216</v>
+        <v>-2.6088</v>
       </c>
     </row>
     <row r="119">
@@ -7201,10 +7201,10 @@
         <v>0.77</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2387</v>
+        <v>-0.2585</v>
       </c>
       <c r="J119" t="n">
-        <v>-5.7288</v>
+        <v>-6.204</v>
       </c>
     </row>
     <row r="120">
@@ -7241,10 +7241,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.4343</v>
+        <v>-0.4473</v>
       </c>
       <c r="J120" t="n">
-        <v>-10.4232</v>
+        <v>-10.7352</v>
       </c>
     </row>
     <row r="121">
@@ -7281,10 +7281,10 @@
         <v>0.34</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.6378</v>
+        <v>-0.6373</v>
       </c>
       <c r="J121" t="n">
-        <v>-15.3072</v>
+        <v>-15.2952</v>
       </c>
     </row>
     <row r="122">
@@ -7321,10 +7321,10 @@
         <v>1.28</v>
       </c>
       <c r="I122" t="n">
-        <v>0.5676</v>
+        <v>0.5548999999999999</v>
       </c>
       <c r="J122" t="n">
-        <v>15.8928</v>
+        <v>15.5372</v>
       </c>
     </row>
     <row r="123">
@@ -7361,10 +7361,10 @@
         <v>1.14</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3149</v>
+        <v>0.3202</v>
       </c>
       <c r="J123" t="n">
-        <v>8.8172</v>
+        <v>8.9656</v>
       </c>
     </row>
     <row r="124">
@@ -7401,10 +7401,10 @@
         <v>1.09</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2168</v>
+        <v>0.2262</v>
       </c>
       <c r="J124" t="n">
-        <v>6.0704</v>
+        <v>6.3336</v>
       </c>
     </row>
     <row r="125">
@@ -7441,10 +7441,10 @@
         <v>1.04</v>
       </c>
       <c r="I125" t="n">
-        <v>0.1101</v>
+        <v>0.1204</v>
       </c>
       <c r="J125" t="n">
-        <v>3.0828</v>
+        <v>3.3712</v>
       </c>
     </row>
     <row r="126">
@@ -7481,10 +7481,10 @@
         <v>0.66</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3783</v>
+        <v>-0.3875</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.5924</v>
+        <v>-10.85</v>
       </c>
     </row>
     <row r="127">
@@ -7521,10 +7521,10 @@
         <v>1.3</v>
       </c>
       <c r="I127" t="n">
-        <v>0.8552999999999999</v>
+        <v>0.7961</v>
       </c>
       <c r="J127" t="n">
-        <v>23.9484</v>
+        <v>22.2908</v>
       </c>
     </row>
     <row r="128">
@@ -7561,10 +7561,10 @@
         <v>1.05</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1885</v>
+        <v>0.1943</v>
       </c>
       <c r="J128" t="n">
-        <v>5.278</v>
+        <v>5.4404</v>
       </c>
     </row>
     <row r="129">
@@ -7601,10 +7601,10 @@
         <v>1.02</v>
       </c>
       <c r="I129" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.0954</v>
       </c>
       <c r="J129" t="n">
-        <v>2.45</v>
+        <v>2.6712</v>
       </c>
     </row>
     <row r="130">
@@ -7641,10 +7641,10 @@
         <v>0.93</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2699</v>
+        <v>-0.2664</v>
       </c>
       <c r="J130" t="n">
-        <v>-7.5572</v>
+        <v>-7.4592</v>
       </c>
     </row>
     <row r="131">
@@ -7681,10 +7681,10 @@
         <v>0.88</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4163</v>
+        <v>-0.4013</v>
       </c>
       <c r="J131" t="n">
-        <v>-11.6564</v>
+        <v>-11.2364</v>
       </c>
     </row>
     <row r="132">
@@ -7721,10 +7721,10 @@
         <v>0.82</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.1739</v>
+        <v>-0.1977</v>
       </c>
       <c r="J132" t="n">
-        <v>-4.1736</v>
+        <v>-4.7448</v>
       </c>
     </row>
     <row r="133">
@@ -7761,10 +7761,10 @@
         <v>0.72</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.2764</v>
+        <v>-0.2976</v>
       </c>
       <c r="J133" t="n">
-        <v>-6.6336</v>
+        <v>-7.1424</v>
       </c>
     </row>
     <row r="134">
@@ -7801,10 +7801,10 @@
         <v>0.65</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.3398</v>
+        <v>-0.3591</v>
       </c>
       <c r="J134" t="n">
-        <v>-8.155200000000001</v>
+        <v>-8.618399999999999</v>
       </c>
     </row>
     <row r="135">
@@ -7841,10 +7841,10 @@
         <v>0.65</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3398</v>
+        <v>-0.3591</v>
       </c>
       <c r="J135" t="n">
-        <v>-8.155200000000001</v>
+        <v>-8.618399999999999</v>
       </c>
     </row>
     <row r="136">
@@ -7881,10 +7881,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4232</v>
+        <v>-0.4386</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.1568</v>
+        <v>-10.5264</v>
       </c>
     </row>
     <row r="137">
@@ -7921,10 +7921,10 @@
         <v>2.07</v>
       </c>
       <c r="I137" t="n">
-        <v>1.7509</v>
+        <v>1.7583</v>
       </c>
       <c r="J137" t="n">
-        <v>42.0216</v>
+        <v>42.1992</v>
       </c>
     </row>
     <row r="138">
@@ -7961,10 +7961,10 @@
         <v>1.46</v>
       </c>
       <c r="I138" t="n">
-        <v>1.0499</v>
+        <v>1.0098</v>
       </c>
       <c r="J138" t="n">
-        <v>25.1976</v>
+        <v>24.2352</v>
       </c>
     </row>
     <row r="139">
@@ -8001,10 +8001,10 @@
         <v>1.38</v>
       </c>
       <c r="I139" t="n">
-        <v>0.9199000000000001</v>
+        <v>0.8741</v>
       </c>
       <c r="J139" t="n">
-        <v>22.0776</v>
+        <v>20.9784</v>
       </c>
     </row>
     <row r="140">
@@ -8041,10 +8041,10 @@
         <v>1.38</v>
       </c>
       <c r="I140" t="n">
-        <v>0.9199000000000001</v>
+        <v>0.8741</v>
       </c>
       <c r="J140" t="n">
-        <v>22.0776</v>
+        <v>20.9784</v>
       </c>
     </row>
     <row r="141">
@@ -8081,10 +8081,10 @@
         <v>1</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.1068</v>
+        <v>-0.07439999999999999</v>
       </c>
       <c r="J141" t="n">
-        <v>-2.5632</v>
+        <v>-1.7856</v>
       </c>
     </row>
     <row r="142">
@@ -8121,10 +8121,10 @@
         <v>1.04</v>
       </c>
       <c r="I142" t="n">
-        <v>0.141</v>
+        <v>0.1529</v>
       </c>
       <c r="J142" t="n">
-        <v>4.23</v>
+        <v>4.587</v>
       </c>
     </row>
     <row r="143">
@@ -8161,10 +8161,10 @@
         <v>1</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.026</v>
+        <v>-0.0178</v>
       </c>
       <c r="J143" t="n">
-        <v>-0.78</v>
+        <v>-0.534</v>
       </c>
     </row>
     <row r="144">
@@ -8201,10 +8201,10 @@
         <v>0.78</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.7045</v>
+        <v>-0.6554</v>
       </c>
       <c r="J144" t="n">
-        <v>-21.135</v>
+        <v>-19.662</v>
       </c>
     </row>
     <row r="145">
@@ -8241,10 +8241,10 @@
         <v>1.52</v>
       </c>
       <c r="I145" t="n">
-        <v>1.192</v>
+        <v>1.1537</v>
       </c>
       <c r="J145" t="n">
-        <v>35.76</v>
+        <v>34.611</v>
       </c>
     </row>
     <row r="146">
@@ -8281,10 +8281,10 @@
         <v>1.22</v>
       </c>
       <c r="I146" t="n">
-        <v>0.6291</v>
+        <v>0.6027</v>
       </c>
       <c r="J146" t="n">
-        <v>18.873</v>
+        <v>18.081</v>
       </c>
     </row>
     <row r="147">
@@ -8321,10 +8321,10 @@
         <v>1.25</v>
       </c>
       <c r="I147" t="n">
-        <v>0.4805</v>
+        <v>0.4816</v>
       </c>
       <c r="J147" t="n">
-        <v>14.415</v>
+        <v>14.448</v>
       </c>
     </row>
     <row r="148">
@@ -8361,10 +8361,10 @@
         <v>1.24</v>
       </c>
       <c r="I148" t="n">
-        <v>0.4638</v>
+        <v>0.4662</v>
       </c>
       <c r="J148" t="n">
-        <v>13.914</v>
+        <v>13.986</v>
       </c>
     </row>
     <row r="149">
@@ -8401,10 +8401,10 @@
         <v>1.23</v>
       </c>
       <c r="I149" t="n">
-        <v>0.4471</v>
+        <v>0.4506</v>
       </c>
       <c r="J149" t="n">
-        <v>13.413</v>
+        <v>13.518</v>
       </c>
     </row>
     <row r="150">
@@ -8441,10 +8441,10 @@
         <v>1.13</v>
       </c>
       <c r="I150" t="n">
-        <v>0.2736</v>
+        <v>0.2862</v>
       </c>
       <c r="J150" t="n">
-        <v>8.208</v>
+        <v>8.586</v>
       </c>
     </row>
     <row r="151">
@@ -8481,10 +8481,10 @@
         <v>1.09</v>
       </c>
       <c r="I151" t="n">
-        <v>0.1955</v>
+        <v>0.211</v>
       </c>
       <c r="J151" t="n">
-        <v>5.865</v>
+        <v>6.33</v>
       </c>
     </row>
     <row r="152">
@@ -8521,10 +8521,10 @@
         <v>0.95</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.2312</v>
+        <v>-0.2238</v>
       </c>
       <c r="J152" t="n">
-        <v>-6.2424</v>
+        <v>-6.0426</v>
       </c>
     </row>
     <row r="153">
@@ -8561,10 +8561,10 @@
         <v>0.88</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.4414</v>
+        <v>-0.4189</v>
       </c>
       <c r="J153" t="n">
-        <v>-11.9178</v>
+        <v>-11.3103</v>
       </c>
     </row>
     <row r="154">
@@ -8601,10 +8601,10 @@
         <v>0.85</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.5242</v>
+        <v>-0.4939</v>
       </c>
       <c r="J154" t="n">
-        <v>-14.1534</v>
+        <v>-13.3353</v>
       </c>
     </row>
     <row r="155">
@@ -8641,10 +8641,10 @@
         <v>1.61</v>
       </c>
       <c r="I155" t="n">
-        <v>1.3037</v>
+        <v>1.2733</v>
       </c>
       <c r="J155" t="n">
-        <v>35.1999</v>
+        <v>34.3791</v>
       </c>
     </row>
     <row r="156">
@@ -8681,10 +8681,10 @@
         <v>1.34</v>
       </c>
       <c r="I156" t="n">
-        <v>0.9105</v>
+        <v>0.8512</v>
       </c>
       <c r="J156" t="n">
-        <v>24.5835</v>
+        <v>22.9824</v>
       </c>
     </row>
     <row r="157">
@@ -8721,10 +8721,10 @@
         <v>0.89</v>
       </c>
       <c r="I157" t="n">
-        <v>-0.1393</v>
+        <v>-0.1536</v>
       </c>
       <c r="J157" t="n">
-        <v>-3.7611</v>
+        <v>-4.1472</v>
       </c>
     </row>
     <row r="158">
@@ -8761,10 +8761,10 @@
         <v>0.8</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.2326</v>
+        <v>-0.2474</v>
       </c>
       <c r="J158" t="n">
-        <v>-6.2802</v>
+        <v>-6.6798</v>
       </c>
     </row>
     <row r="159">
@@ -8801,10 +8801,10 @@
         <v>0.72</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.3108</v>
+        <v>-0.3242</v>
       </c>
       <c r="J159" t="n">
-        <v>-8.3916</v>
+        <v>-8.753399999999999</v>
       </c>
     </row>
     <row r="160">
@@ -8841,10 +8841,10 @@
         <v>1.27</v>
       </c>
       <c r="I160" t="n">
-        <v>0.5861</v>
+        <v>0.5653</v>
       </c>
       <c r="J160" t="n">
-        <v>15.8247</v>
+        <v>15.2631</v>
       </c>
     </row>
     <row r="161">
@@ -8881,10 +8881,10 @@
         <v>1.05</v>
       </c>
       <c r="I161" t="n">
-        <v>0.1521</v>
+        <v>0.1571</v>
       </c>
       <c r="J161" t="n">
-        <v>4.1067</v>
+        <v>4.2417</v>
       </c>
     </row>
     <row r="162">
@@ -8921,10 +8921,10 @@
         <v>1</v>
       </c>
       <c r="I162" t="n">
-        <v>0.005</v>
+        <v>0.0036</v>
       </c>
       <c r="J162" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="163">
@@ -8961,10 +8961,10 @@
         <v>0.99</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.0174</v>
+        <v>-0.0229</v>
       </c>
       <c r="J163" t="n">
-        <v>-0.522</v>
+        <v>-0.6870000000000001</v>
       </c>
     </row>
     <row r="164">
@@ -9001,10 +9001,10 @@
         <v>0.96</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.06</v>
+        <v>-0.0701</v>
       </c>
       <c r="J164" t="n">
-        <v>-1.8</v>
+        <v>-2.103</v>
       </c>
     </row>
     <row r="165">
@@ -9041,10 +9041,10 @@
         <v>0.92</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1073</v>
+        <v>-0.1203</v>
       </c>
       <c r="J165" t="n">
-        <v>-3.219</v>
+        <v>-3.609</v>
       </c>
     </row>
     <row r="166">
@@ -9081,10 +9081,10 @@
         <v>0.92</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.1073</v>
+        <v>-0.1203</v>
       </c>
       <c r="J166" t="n">
-        <v>-3.219</v>
+        <v>-3.609</v>
       </c>
     </row>
     <row r="167">
@@ -9121,10 +9121,10 @@
         <v>1.44</v>
       </c>
       <c r="I167" t="n">
-        <v>0.5953000000000001</v>
+        <v>0.5923</v>
       </c>
       <c r="J167" t="n">
-        <v>17.859</v>
+        <v>17.769</v>
       </c>
     </row>
     <row r="168">
@@ -9161,10 +9161,10 @@
         <v>1.03</v>
       </c>
       <c r="I168" t="n">
-        <v>0.0616</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="J168" t="n">
-        <v>1.848</v>
+        <v>2.145</v>
       </c>
     </row>
     <row r="169">
@@ -9201,10 +9201,10 @@
         <v>1.02</v>
       </c>
       <c r="I169" t="n">
-        <v>0.0434</v>
+        <v>0.0519</v>
       </c>
       <c r="J169" t="n">
-        <v>1.302</v>
+        <v>1.557</v>
       </c>
     </row>
     <row r="170">
@@ -9241,10 +9241,10 @@
         <v>0.95</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.08019999999999999</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="J170" t="n">
-        <v>-2.406</v>
+        <v>-2.682</v>
       </c>
     </row>
     <row r="171">
@@ -9281,10 +9281,10 @@
         <v>0.77</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2735</v>
+        <v>-0.2855</v>
       </c>
       <c r="J171" t="n">
-        <v>-8.205</v>
+        <v>-8.565</v>
       </c>
     </row>
     <row r="172">
@@ -9321,10 +9321,10 @@
         <v>1.48</v>
       </c>
       <c r="I172" t="n">
-        <v>1.1116</v>
+        <v>1.0728</v>
       </c>
       <c r="J172" t="n">
-        <v>26.6784</v>
+        <v>25.7472</v>
       </c>
     </row>
     <row r="173">
@@ -9361,10 +9361,10 @@
         <v>1.34</v>
       </c>
       <c r="I173" t="n">
-        <v>0.8796</v>
+        <v>0.8293</v>
       </c>
       <c r="J173" t="n">
-        <v>21.1104</v>
+        <v>19.9032</v>
       </c>
     </row>
     <row r="174">
@@ -9401,10 +9401,10 @@
         <v>1.19</v>
       </c>
       <c r="I174" t="n">
-        <v>0.5337</v>
+        <v>0.5219</v>
       </c>
       <c r="J174" t="n">
-        <v>12.8088</v>
+        <v>12.5256</v>
       </c>
     </row>
     <row r="175">
@@ -9441,10 +9441,10 @@
         <v>1.1</v>
       </c>
       <c r="I175" t="n">
-        <v>0.2983</v>
+        <v>0.3073</v>
       </c>
       <c r="J175" t="n">
-        <v>7.1592</v>
+        <v>7.3752</v>
       </c>
     </row>
     <row r="176">
@@ -9481,10 +9481,10 @@
         <v>0.98</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.1492</v>
+        <v>-0.138</v>
       </c>
       <c r="J176" t="n">
-        <v>-3.5808</v>
+        <v>-3.312</v>
       </c>
     </row>
     <row r="177">
@@ -9521,10 +9521,10 @@
         <v>1.03</v>
       </c>
       <c r="I177" t="n">
-        <v>0.1122</v>
+        <v>0.1147</v>
       </c>
       <c r="J177" t="n">
-        <v>2.6928</v>
+        <v>2.7528</v>
       </c>
     </row>
     <row r="178">
@@ -9561,10 +9561,10 @@
         <v>0.99</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.0121</v>
+        <v>-0.0188</v>
       </c>
       <c r="J178" t="n">
-        <v>-0.2904</v>
+        <v>-0.4512</v>
       </c>
     </row>
     <row r="179">
@@ -9601,10 +9601,10 @@
         <v>0.86</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1676</v>
+        <v>-0.1832</v>
       </c>
       <c r="J179" t="n">
-        <v>-4.0224</v>
+        <v>-4.3968</v>
       </c>
     </row>
     <row r="180">
@@ -9641,10 +9641,10 @@
         <v>0.85</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1779</v>
+        <v>-0.1937</v>
       </c>
       <c r="J180" t="n">
-        <v>-4.2696</v>
+        <v>-4.6488</v>
       </c>
     </row>
     <row r="181">
@@ -9681,10 +9681,10 @@
         <v>0.84</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1882</v>
+        <v>-0.204</v>
       </c>
       <c r="J181" t="n">
-        <v>-4.5168</v>
+        <v>-4.896</v>
       </c>
     </row>
     <row r="182">
@@ -9721,10 +9721,10 @@
         <v>1.57</v>
       </c>
       <c r="I182" t="n">
-        <v>1.2517</v>
+        <v>1.2183</v>
       </c>
       <c r="J182" t="n">
-        <v>37.551</v>
+        <v>36.549</v>
       </c>
     </row>
     <row r="183">
@@ -9761,10 +9761,10 @@
         <v>1.16</v>
       </c>
       <c r="I183" t="n">
-        <v>0.4746</v>
+        <v>0.4649</v>
       </c>
       <c r="J183" t="n">
-        <v>14.238</v>
+        <v>13.947</v>
       </c>
     </row>
     <row r="184">
@@ -9801,10 +9801,10 @@
         <v>1.06</v>
       </c>
       <c r="I184" t="n">
-        <v>0.2016</v>
+        <v>0.2118</v>
       </c>
       <c r="J184" t="n">
-        <v>6.048</v>
+        <v>6.354</v>
       </c>
     </row>
     <row r="185">
@@ -9841,10 +9841,10 @@
         <v>0.98</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1261</v>
+        <v>-0.1219</v>
       </c>
       <c r="J185" t="n">
-        <v>-3.783</v>
+        <v>-3.657</v>
       </c>
     </row>
     <row r="186">
@@ -9881,10 +9881,10 @@
         <v>0.87</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4699</v>
+        <v>-0.4447</v>
       </c>
       <c r="J186" t="n">
-        <v>-14.097</v>
+        <v>-13.341</v>
       </c>
     </row>
     <row r="187">
@@ -9921,10 +9921,10 @@
         <v>1.05</v>
       </c>
       <c r="I187" t="n">
-        <v>0.1494</v>
+        <v>0.1552</v>
       </c>
       <c r="J187" t="n">
-        <v>4.482</v>
+        <v>4.656</v>
       </c>
     </row>
     <row r="188">
@@ -9961,10 +9961,10 @@
         <v>1.01</v>
       </c>
       <c r="I188" t="n">
-        <v>0.0456</v>
+        <v>0.049</v>
       </c>
       <c r="J188" t="n">
-        <v>1.368</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="189">
@@ -10001,10 +10001,10 @@
         <v>0.97</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.0469</v>
+        <v>-0.0558</v>
       </c>
       <c r="J189" t="n">
-        <v>-1.407</v>
+        <v>-1.674</v>
       </c>
     </row>
     <row r="190">
@@ -10041,10 +10041,10 @@
         <v>0.95</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="J190" t="n">
-        <v>-2.16</v>
+        <v>-2.493</v>
       </c>
     </row>
     <row r="191">
@@ -10081,10 +10081,10 @@
         <v>0.8</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2338</v>
+        <v>-0.2483</v>
       </c>
       <c r="J191" t="n">
-        <v>-7.014</v>
+        <v>-7.449</v>
       </c>
     </row>
     <row r="192">
@@ -10121,10 +10121,10 @@
         <v>1.02</v>
       </c>
       <c r="I192" t="n">
-        <v>0.0485</v>
+        <v>0.0556</v>
       </c>
       <c r="J192" t="n">
-        <v>1.746</v>
+        <v>2.0016</v>
       </c>
     </row>
     <row r="193">
@@ -10161,10 +10161,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.08690000000000001</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="J193" t="n">
-        <v>-3.1284</v>
+        <v>-3.5316</v>
       </c>
     </row>
     <row r="194">
@@ -10201,10 +10201,10 @@
         <v>0.72</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.3158</v>
+        <v>-0.3281</v>
       </c>
       <c r="J194" t="n">
-        <v>-11.3688</v>
+        <v>-11.8116</v>
       </c>
     </row>
     <row r="195">
@@ -10241,10 +10241,10 @@
         <v>1.16</v>
       </c>
       <c r="I195" t="n">
-        <v>0.2618</v>
+        <v>0.2725</v>
       </c>
       <c r="J195" t="n">
-        <v>9.424799999999999</v>
+        <v>9.81</v>
       </c>
     </row>
     <row r="196">
@@ -10281,10 +10281,10 @@
         <v>1.1</v>
       </c>
       <c r="I196" t="n">
-        <v>0.1776</v>
+        <v>0.1893</v>
       </c>
       <c r="J196" t="n">
-        <v>6.3936</v>
+        <v>6.8148</v>
       </c>
     </row>
     <row r="197">
@@ -10321,10 +10321,10 @@
         <v>1.42</v>
       </c>
       <c r="I197" t="n">
-        <v>0.5558</v>
+        <v>0.5573</v>
       </c>
       <c r="J197" t="n">
-        <v>20.0088</v>
+        <v>20.0628</v>
       </c>
     </row>
     <row r="198">
@@ -10361,10 +10361,10 @@
         <v>1.39</v>
       </c>
       <c r="I198" t="n">
-        <v>0.5211</v>
+        <v>0.525</v>
       </c>
       <c r="J198" t="n">
-        <v>18.7596</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="199">
@@ -10401,10 +10401,10 @@
         <v>1.31</v>
       </c>
       <c r="I199" t="n">
-        <v>0.4283</v>
+        <v>0.4376</v>
       </c>
       <c r="J199" t="n">
-        <v>15.4188</v>
+        <v>15.7536</v>
       </c>
     </row>
     <row r="200">
@@ -10441,10 +10441,10 @@
         <v>1.29</v>
       </c>
       <c r="I200" t="n">
-        <v>0.4046</v>
+        <v>0.4151</v>
       </c>
       <c r="J200" t="n">
-        <v>14.5656</v>
+        <v>14.9436</v>
       </c>
     </row>
     <row r="201">
@@ -10481,10 +10481,10 @@
         <v>1.18</v>
       </c>
       <c r="I201" t="n">
-        <v>0.2637</v>
+        <v>0.2805</v>
       </c>
       <c r="J201" t="n">
-        <v>9.4932</v>
+        <v>10.098</v>
       </c>
     </row>
     <row r="202">
@@ -10521,10 +10521,10 @@
         <v>1.28</v>
       </c>
       <c r="I202" t="n">
-        <v>0.5548</v>
+        <v>0.5455</v>
       </c>
       <c r="J202" t="n">
-        <v>13.3152</v>
+        <v>13.092</v>
       </c>
     </row>
     <row r="203">
@@ -10561,10 +10561,10 @@
         <v>1.26</v>
       </c>
       <c r="I203" t="n">
-        <v>0.5205</v>
+        <v>0.514</v>
       </c>
       <c r="J203" t="n">
-        <v>12.492</v>
+        <v>12.336</v>
       </c>
     </row>
     <row r="204">
@@ -10601,10 +10601,10 @@
         <v>0.84</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2077</v>
+        <v>-0.2192</v>
       </c>
       <c r="J204" t="n">
-        <v>-4.9848</v>
+        <v>-5.2608</v>
       </c>
     </row>
     <row r="205">
@@ -10641,10 +10641,10 @@
         <v>1.09</v>
       </c>
       <c r="I205" t="n">
-        <v>0.2104</v>
+        <v>0.2216</v>
       </c>
       <c r="J205" t="n">
-        <v>5.0496</v>
+        <v>5.3184</v>
       </c>
     </row>
     <row r="206">
@@ -10681,10 +10681,10 @@
         <v>0.95</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.08459999999999999</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="J206" t="n">
-        <v>-2.0304</v>
+        <v>-2.2272</v>
       </c>
     </row>
     <row r="207">
@@ -10721,10 +10721,10 @@
         <v>0.83</v>
       </c>
       <c r="I207" t="n">
-        <v>-0.5206</v>
+        <v>-0.5021</v>
       </c>
       <c r="J207" t="n">
-        <v>-12.4944</v>
+        <v>-12.0504</v>
       </c>
     </row>
     <row r="208">
@@ -10761,10 +10761,10 @@
         <v>0.5</v>
       </c>
       <c r="I208" t="n">
-        <v>-1.3321</v>
+        <v>-1.2045</v>
       </c>
       <c r="J208" t="n">
-        <v>-31.9704</v>
+        <v>-28.908</v>
       </c>
     </row>
     <row r="209">
@@ -10801,10 +10801,10 @@
         <v>0.36</v>
       </c>
       <c r="I209" t="n">
-        <v>-1.6555</v>
+        <v>-1.4761</v>
       </c>
       <c r="J209" t="n">
-        <v>-39.732</v>
+        <v>-35.4264</v>
       </c>
     </row>
     <row r="210">
@@ -10841,10 +10841,10 @@
         <v>1.49</v>
       </c>
       <c r="I210" t="n">
-        <v>1.2243</v>
+        <v>1.1754</v>
       </c>
       <c r="J210" t="n">
-        <v>29.3832</v>
+        <v>28.2096</v>
       </c>
     </row>
     <row r="211">
@@ -10881,10 +10881,10 @@
         <v>1.47</v>
       </c>
       <c r="I211" t="n">
-        <v>1.1962</v>
+        <v>1.1456</v>
       </c>
       <c r="J211" t="n">
-        <v>28.7088</v>
+        <v>27.4944</v>
       </c>
     </row>
     <row r="212">
@@ -10921,10 +10921,10 @@
         <v>1.53</v>
       </c>
       <c r="I212" t="n">
-        <v>0.9383</v>
+        <v>0.8959</v>
       </c>
       <c r="J212" t="n">
-        <v>25.3341</v>
+        <v>24.1893</v>
       </c>
     </row>
     <row r="213">
@@ -10961,10 +10961,10 @@
         <v>1.07</v>
       </c>
       <c r="I213" t="n">
-        <v>0.1613</v>
+        <v>0.1757</v>
       </c>
       <c r="J213" t="n">
-        <v>4.3551</v>
+        <v>4.7439</v>
       </c>
     </row>
     <row r="214">
@@ -11001,10 +11001,10 @@
         <v>0.83</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.2242</v>
+        <v>-0.2344</v>
       </c>
       <c r="J214" t="n">
-        <v>-6.0534</v>
+        <v>-6.3288</v>
       </c>
     </row>
     <row r="215">
@@ -11041,10 +11041,10 @@
         <v>1.15</v>
       </c>
       <c r="I215" t="n">
-        <v>0.3153</v>
+        <v>0.3248</v>
       </c>
       <c r="J215" t="n">
-        <v>8.5131</v>
+        <v>8.769600000000001</v>
       </c>
     </row>
     <row r="216">
@@ -11081,10 +11081,10 @@
         <v>1.14</v>
       </c>
       <c r="I216" t="n">
-        <v>0.2978</v>
+        <v>0.3079</v>
       </c>
       <c r="J216" t="n">
-        <v>8.0406</v>
+        <v>8.3133</v>
       </c>
     </row>
     <row r="217">
@@ -11121,10 +11121,10 @@
         <v>1.14</v>
       </c>
       <c r="I217" t="n">
-        <v>0.4233</v>
+        <v>0.4182</v>
       </c>
       <c r="J217" t="n">
-        <v>11.4291</v>
+        <v>11.2914</v>
       </c>
     </row>
     <row r="218">
@@ -11161,10 +11161,10 @@
         <v>0.88</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.4425</v>
+        <v>-0.4197</v>
       </c>
       <c r="J218" t="n">
-        <v>-11.9475</v>
+        <v>-11.3319</v>
       </c>
     </row>
     <row r="219">
@@ -11201,10 +11201,10 @@
         <v>0.77</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.7346</v>
+        <v>-0.6812</v>
       </c>
       <c r="J219" t="n">
-        <v>-19.8342</v>
+        <v>-18.3924</v>
       </c>
     </row>
     <row r="220">
@@ -11241,10 +11241,10 @@
         <v>1.5</v>
       </c>
       <c r="I220" t="n">
-        <v>1.1603</v>
+        <v>1.1209</v>
       </c>
       <c r="J220" t="n">
-        <v>31.3281</v>
+        <v>30.2643</v>
       </c>
     </row>
     <row r="221">
@@ -11281,10 +11281,10 @@
         <v>1.36</v>
       </c>
       <c r="I221" t="n">
-        <v>0.9524</v>
+        <v>0.8902</v>
       </c>
       <c r="J221" t="n">
-        <v>25.7148</v>
+        <v>24.0354</v>
       </c>
     </row>
     <row r="222">
@@ -11321,10 +11321,10 @@
         <v>1.03</v>
       </c>
       <c r="I222" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.0968</v>
       </c>
       <c r="J222" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="223">
@@ -11361,10 +11361,10 @@
         <v>1.02</v>
       </c>
       <c r="I223" t="n">
-        <v>0.0745</v>
+        <v>0.0752</v>
       </c>
       <c r="J223" t="n">
-        <v>1.8625</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="224">
@@ -11401,10 +11401,10 @@
         <v>0.83</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.1939</v>
+        <v>-0.2108</v>
       </c>
       <c r="J224" t="n">
-        <v>-4.8475</v>
+        <v>-5.27</v>
       </c>
     </row>
     <row r="225">
@@ -11441,10 +11441,10 @@
         <v>0.77</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2534</v>
+        <v>-0.2698</v>
       </c>
       <c r="J225" t="n">
-        <v>-6.335</v>
+        <v>-6.745</v>
       </c>
     </row>
     <row r="226">
@@ -11481,10 +11481,10 @@
         <v>0.73</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.2923</v>
+        <v>-0.3078</v>
       </c>
       <c r="J226" t="n">
-        <v>-7.3075</v>
+        <v>-7.695</v>
       </c>
     </row>
     <row r="227">
@@ -11521,10 +11521,10 @@
         <v>1.66</v>
       </c>
       <c r="I227" t="n">
-        <v>0.7823</v>
+        <v>0.7741</v>
       </c>
       <c r="J227" t="n">
-        <v>19.5575</v>
+        <v>19.3525</v>
       </c>
     </row>
     <row r="228">
@@ -11561,10 +11561,10 @@
         <v>1.3</v>
       </c>
       <c r="I228" t="n">
-        <v>0.3922</v>
+        <v>0.408</v>
       </c>
       <c r="J228" t="n">
-        <v>9.805</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="229">
@@ -11601,10 +11601,10 @@
         <v>1.3</v>
       </c>
       <c r="I229" t="n">
-        <v>0.3922</v>
+        <v>0.408</v>
       </c>
       <c r="J229" t="n">
-        <v>9.805</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="230">
@@ -11641,10 +11641,10 @@
         <v>1.19</v>
       </c>
       <c r="I230" t="n">
-        <v>0.2646</v>
+        <v>0.2835</v>
       </c>
       <c r="J230" t="n">
-        <v>6.615</v>
+        <v>7.0875</v>
       </c>
     </row>
     <row r="231">
@@ -11681,10 +11681,10 @@
         <v>0.83</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.2347</v>
+        <v>-0.2426</v>
       </c>
       <c r="J231" t="n">
-        <v>-5.8675</v>
+        <v>-6.065</v>
       </c>
     </row>
     <row r="232">
@@ -11721,10 +11721,10 @@
         <v>1.26</v>
       </c>
       <c r="I232" t="n">
-        <v>0.7425</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="J232" t="n">
-        <v>22.275</v>
+        <v>21.003</v>
       </c>
     </row>
     <row r="233">
@@ -11761,10 +11761,10 @@
         <v>1.24</v>
       </c>
       <c r="I233" t="n">
-        <v>0.6933</v>
+        <v>0.6567</v>
       </c>
       <c r="J233" t="n">
-        <v>20.799</v>
+        <v>19.701</v>
       </c>
     </row>
     <row r="234">
@@ -11801,10 +11801,10 @@
         <v>1.01</v>
       </c>
       <c r="I234" t="n">
-        <v>0.0393</v>
+        <v>0.0492</v>
       </c>
       <c r="J234" t="n">
-        <v>1.179</v>
+        <v>1.476</v>
       </c>
     </row>
     <row r="235">
@@ -11841,10 +11841,10 @@
         <v>0.98</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1108</v>
+        <v>-0.1113</v>
       </c>
       <c r="J235" t="n">
-        <v>-3.324</v>
+        <v>-3.339</v>
       </c>
     </row>
     <row r="236">
@@ -11881,10 +11881,10 @@
         <v>0.86</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4816</v>
+        <v>-0.4585</v>
       </c>
       <c r="J236" t="n">
-        <v>-14.448</v>
+        <v>-13.755</v>
       </c>
     </row>
     <row r="237">
@@ -11921,10 +11921,10 @@
         <v>1.27</v>
       </c>
       <c r="I237" t="n">
-        <v>0.5589</v>
+        <v>0.5454</v>
       </c>
       <c r="J237" t="n">
-        <v>16.767</v>
+        <v>16.362</v>
       </c>
     </row>
     <row r="238">
@@ -11961,10 +11961,10 @@
         <v>1.07</v>
       </c>
       <c r="I238" t="n">
-        <v>0.1802</v>
+        <v>0.1892</v>
       </c>
       <c r="J238" t="n">
-        <v>5.406</v>
+        <v>5.676</v>
       </c>
     </row>
     <row r="239">
@@ -12001,10 +12001,10 @@
         <v>0.99</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.0218</v>
+        <v>-0.0262</v>
       </c>
       <c r="J239" t="n">
-        <v>-0.654</v>
+        <v>-0.786</v>
       </c>
     </row>
     <row r="240">
@@ -12041,10 +12041,10 @@
         <v>0.95</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.0775</v>
+        <v>-0.0873</v>
       </c>
       <c r="J240" t="n">
-        <v>-2.325</v>
+        <v>-2.619</v>
       </c>
     </row>
     <row r="241">
@@ -12081,10 +12081,10 @@
         <v>0.8</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.2409</v>
+        <v>-0.2539</v>
       </c>
       <c r="J241" t="n">
-        <v>-7.227</v>
+        <v>-7.617</v>
       </c>
     </row>
     <row r="242">
@@ -12121,10 +12121,10 @@
         <v>1.67</v>
       </c>
       <c r="I242" t="n">
-        <v>1.3411</v>
+        <v>1.3194</v>
       </c>
       <c r="J242" t="n">
-        <v>29.5042</v>
+        <v>29.0268</v>
       </c>
     </row>
     <row r="243">
@@ -12161,10 +12161,10 @@
         <v>1.24</v>
       </c>
       <c r="I243" t="n">
-        <v>0.6463</v>
+        <v>0.6243</v>
       </c>
       <c r="J243" t="n">
-        <v>14.2186</v>
+        <v>13.7346</v>
       </c>
     </row>
     <row r="244">
@@ -12201,10 +12201,10 @@
         <v>1.19</v>
       </c>
       <c r="I244" t="n">
-        <v>0.5275</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="J244" t="n">
-        <v>11.605</v>
+        <v>11.3872</v>
       </c>
     </row>
     <row r="245">
@@ -12241,10 +12241,10 @@
         <v>1.09</v>
       </c>
       <c r="I245" t="n">
-        <v>0.2621</v>
+        <v>0.2756</v>
       </c>
       <c r="J245" t="n">
-        <v>5.7662</v>
+        <v>6.0632</v>
       </c>
     </row>
     <row r="246">
@@ -12281,10 +12281,10 @@
         <v>1.06</v>
       </c>
       <c r="I246" t="n">
-        <v>0.172</v>
+        <v>0.1912</v>
       </c>
       <c r="J246" t="n">
-        <v>3.784</v>
+        <v>4.2064</v>
       </c>
     </row>
     <row r="247">
@@ -12321,10 +12321,10 @@
         <v>1.39</v>
       </c>
       <c r="I247" t="n">
-        <v>0.8387</v>
+        <v>0.7863</v>
       </c>
       <c r="J247" t="n">
-        <v>18.4514</v>
+        <v>17.2986</v>
       </c>
     </row>
     <row r="248">
@@ -12361,10 +12361,10 @@
         <v>0.98</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.0217</v>
+        <v>-0.0318</v>
       </c>
       <c r="J248" t="n">
-        <v>-0.4774</v>
+        <v>-0.6996</v>
       </c>
     </row>
     <row r="249">
@@ -12401,10 +12401,10 @@
         <v>0.82</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.2035</v>
+        <v>-0.2205</v>
       </c>
       <c r="J249" t="n">
-        <v>-4.477</v>
+        <v>-4.851</v>
       </c>
     </row>
     <row r="250">
@@ -12441,10 +12441,10 @@
         <v>0.68</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.3395</v>
+        <v>-0.3537</v>
       </c>
       <c r="J250" t="n">
-        <v>-7.469</v>
+        <v>-7.7814</v>
       </c>
     </row>
     <row r="251">
@@ -12481,10 +12481,10 @@
         <v>0.49</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.5154</v>
+        <v>-0.5211</v>
       </c>
       <c r="J251" t="n">
-        <v>-11.3388</v>
+        <v>-11.4642</v>
       </c>
     </row>
     <row r="252">
@@ -12521,10 +12521,10 @@
         <v>1.12</v>
       </c>
       <c r="I252" t="n">
-        <v>0.2987</v>
+        <v>0.2997</v>
       </c>
       <c r="J252" t="n">
-        <v>6.5714</v>
+        <v>6.5934</v>
       </c>
     </row>
     <row r="253">
@@ -12561,10 +12561,10 @@
         <v>0.84</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.1934</v>
+        <v>-0.2081</v>
       </c>
       <c r="J253" t="n">
-        <v>-4.2548</v>
+        <v>-4.5782</v>
       </c>
     </row>
     <row r="254">
@@ -12601,10 +12601,10 @@
         <v>0.65</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.3785</v>
+        <v>-0.3893</v>
       </c>
       <c r="J254" t="n">
-        <v>-8.327</v>
+        <v>-8.5646</v>
       </c>
     </row>
     <row r="255">
@@ -12641,10 +12641,10 @@
         <v>1.14</v>
       </c>
       <c r="I255" t="n">
-        <v>0.3385</v>
+        <v>0.3373</v>
       </c>
       <c r="J255" t="n">
-        <v>7.447</v>
+        <v>7.4206</v>
       </c>
     </row>
     <row r="256">
@@ -12681,10 +12681,10 @@
         <v>1.04</v>
       </c>
       <c r="I256" t="n">
-        <v>0.1252</v>
+        <v>0.1312</v>
       </c>
       <c r="J256" t="n">
-        <v>2.7544</v>
+        <v>2.8864</v>
       </c>
     </row>
     <row r="257">
@@ -12721,10 +12721,10 @@
         <v>0.9</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.3391</v>
+        <v>-0.3352</v>
       </c>
       <c r="J257" t="n">
-        <v>-7.4602</v>
+        <v>-7.3744</v>
       </c>
     </row>
     <row r="258">
@@ -12761,10 +12761,10 @@
         <v>0.61</v>
       </c>
       <c r="I258" t="n">
-        <v>-1.0822</v>
+        <v>-0.9903999999999999</v>
       </c>
       <c r="J258" t="n">
-        <v>-23.8084</v>
+        <v>-21.7888</v>
       </c>
     </row>
     <row r="259">
@@ -12801,10 +12801,10 @@
         <v>0.32</v>
       </c>
       <c r="I259" t="n">
-        <v>-1.753</v>
+        <v>-1.5566</v>
       </c>
       <c r="J259" t="n">
-        <v>-38.566</v>
+        <v>-34.2452</v>
       </c>
     </row>
     <row r="260">
@@ -12841,10 +12841,10 @@
         <v>1.7</v>
       </c>
       <c r="I260" t="n">
-        <v>1.4915</v>
+        <v>1.4596</v>
       </c>
       <c r="J260" t="n">
-        <v>32.813</v>
+        <v>32.1112</v>
       </c>
     </row>
     <row r="261">
@@ -12881,10 +12881,10 @@
         <v>1.3</v>
       </c>
       <c r="I261" t="n">
-        <v>0.8931</v>
+        <v>0.8228</v>
       </c>
       <c r="J261" t="n">
-        <v>19.6482</v>
+        <v>18.1016</v>
       </c>
     </row>
     <row r="262">
@@ -12921,10 +12921,10 @@
         <v>1.17</v>
       </c>
       <c r="I262" t="n">
-        <v>0.34</v>
+        <v>0.3509</v>
       </c>
       <c r="J262" t="n">
-        <v>10.2</v>
+        <v>10.527</v>
       </c>
     </row>
     <row r="263">
@@ -12961,10 +12961,10 @@
         <v>1.13</v>
       </c>
       <c r="I263" t="n">
-        <v>0.2666</v>
+        <v>0.2812</v>
       </c>
       <c r="J263" t="n">
-        <v>7.998</v>
+        <v>8.436</v>
       </c>
     </row>
     <row r="264">
@@ -13001,10 +13001,10 @@
         <v>0.87</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.1909</v>
+        <v>-0.199</v>
       </c>
       <c r="J264" t="n">
-        <v>-5.727</v>
+        <v>-5.97</v>
       </c>
     </row>
     <row r="265">
@@ -13041,10 +13041,10 @@
         <v>1.77</v>
       </c>
       <c r="I265" t="n">
-        <v>1.1576</v>
+        <v>1.1408</v>
       </c>
       <c r="J265" t="n">
-        <v>34.728</v>
+        <v>34.224</v>
       </c>
     </row>
     <row r="266">
@@ -13081,10 +13081,10 @@
         <v>1.22</v>
       </c>
       <c r="I266" t="n">
-        <v>0.4257</v>
+        <v>0.4317</v>
       </c>
       <c r="J266" t="n">
-        <v>12.771</v>
+        <v>12.951</v>
       </c>
     </row>
     <row r="267">
@@ -13121,10 +13121,10 @@
         <v>0.6</v>
       </c>
       <c r="I267" t="n">
-        <v>-1.0487</v>
+        <v>-0.9705</v>
       </c>
       <c r="J267" t="n">
-        <v>-31.461</v>
+        <v>-29.115</v>
       </c>
     </row>
     <row r="268">
@@ -13161,10 +13161,10 @@
         <v>0.6</v>
       </c>
       <c r="I268" t="n">
-        <v>-1.0487</v>
+        <v>-0.9705</v>
       </c>
       <c r="J268" t="n">
-        <v>-31.461</v>
+        <v>-29.115</v>
       </c>
     </row>
     <row r="269">
@@ -13201,10 +13201,10 @@
         <v>0.36</v>
       </c>
       <c r="I269" t="n">
-        <v>-1.6225</v>
+        <v>-1.4526</v>
       </c>
       <c r="J269" t="n">
-        <v>-48.675</v>
+        <v>-43.578</v>
       </c>
     </row>
     <row r="270">
@@ -13241,10 +13241,10 @@
         <v>1.28</v>
       </c>
       <c r="I270" t="n">
-        <v>0.9719</v>
+        <v>0.8749</v>
       </c>
       <c r="J270" t="n">
-        <v>29.157</v>
+        <v>26.247</v>
       </c>
     </row>
     <row r="271">
@@ -13281,10 +13281,10 @@
         <v>1.12</v>
       </c>
       <c r="I271" t="n">
-        <v>0.5239</v>
+        <v>0.477</v>
       </c>
       <c r="J271" t="n">
-        <v>15.717</v>
+        <v>14.31</v>
       </c>
     </row>
     <row r="272">
@@ -13321,10 +13321,10 @@
         <v>0.8</v>
       </c>
       <c r="I272" t="n">
-        <v>-0.6199</v>
+        <v>-0.5866</v>
       </c>
       <c r="J272" t="n">
-        <v>-15.4975</v>
+        <v>-14.665</v>
       </c>
     </row>
     <row r="273">
@@ -13361,10 +13361,10 @@
         <v>0.72</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-0.7652</v>
       </c>
       <c r="J273" t="n">
-        <v>-20.5775</v>
+        <v>-19.13</v>
       </c>
     </row>
     <row r="274">
@@ -13401,10 +13401,10 @@
         <v>0.64</v>
       </c>
       <c r="I274" t="n">
-        <v>-1.0187</v>
+        <v>-0.9346</v>
       </c>
       <c r="J274" t="n">
-        <v>-25.4675</v>
+        <v>-23.365</v>
       </c>
     </row>
     <row r="275">
@@ -13441,10 +13441,10 @@
         <v>1.55</v>
       </c>
       <c r="I275" t="n">
-        <v>1.2756</v>
+        <v>1.235</v>
       </c>
       <c r="J275" t="n">
-        <v>31.89</v>
+        <v>30.875</v>
       </c>
     </row>
     <row r="276">
@@ -13481,10 +13481,10 @@
         <v>1.27</v>
       </c>
       <c r="I276" t="n">
-        <v>0.8015</v>
+        <v>0.7458</v>
       </c>
       <c r="J276" t="n">
-        <v>20.0375</v>
+        <v>18.645</v>
       </c>
     </row>
     <row r="277">
@@ -13521,10 +13521,10 @@
         <v>1.14</v>
       </c>
       <c r="I277" t="n">
-        <v>0.3286</v>
+        <v>0.3301</v>
       </c>
       <c r="J277" t="n">
-        <v>8.215</v>
+        <v>8.2525</v>
       </c>
     </row>
     <row r="278">
@@ -13561,10 +13561,10 @@
         <v>1</v>
       </c>
       <c r="I278" t="n">
-        <v>0.0011</v>
+        <v>0.0007</v>
       </c>
       <c r="J278" t="n">
-        <v>0.0275</v>
+        <v>0.0175</v>
       </c>
     </row>
     <row r="279">
@@ -13601,10 +13601,10 @@
         <v>0.97</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.0492</v>
+        <v>-0.0575</v>
       </c>
       <c r="J279" t="n">
-        <v>-1.23</v>
+        <v>-1.4375</v>
       </c>
     </row>
     <row r="280">
@@ -13641,10 +13641,10 @@
         <v>0.96</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.0623</v>
+        <v>-0.0718</v>
       </c>
       <c r="J280" t="n">
-        <v>-1.5575</v>
+        <v>-1.795</v>
       </c>
     </row>
     <row r="281">
@@ -13681,10 +13681,10 @@
         <v>0.88</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.155</v>
+        <v>-0.1684</v>
       </c>
       <c r="J281" t="n">
-        <v>-3.875</v>
+        <v>-4.21</v>
       </c>
     </row>
     <row r="282">
@@ -13721,10 +13721,10 @@
         <v>0.98</v>
       </c>
       <c r="I282" t="n">
-        <v>-0.1161</v>
+        <v>-0.1149</v>
       </c>
       <c r="J282" t="n">
-        <v>-2.7864</v>
+        <v>-2.7576</v>
       </c>
     </row>
     <row r="283">
@@ -13761,10 +13761,10 @@
         <v>0.85</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.5145</v>
+        <v>-0.4871</v>
       </c>
       <c r="J283" t="n">
-        <v>-12.348</v>
+        <v>-11.6904</v>
       </c>
     </row>
     <row r="284">
@@ -13801,10 +13801,10 @@
         <v>0.62</v>
       </c>
       <c r="I284" t="n">
-        <v>-1.0907</v>
+        <v>-0.9928</v>
       </c>
       <c r="J284" t="n">
-        <v>-26.1768</v>
+        <v>-23.8272</v>
       </c>
     </row>
     <row r="285">
@@ -13841,10 +13841,10 @@
         <v>1.84</v>
       </c>
       <c r="I285" t="n">
-        <v>1.6087</v>
+        <v>1.5911</v>
       </c>
       <c r="J285" t="n">
-        <v>38.6088</v>
+        <v>38.1864</v>
       </c>
     </row>
     <row r="286">
@@ -13881,10 +13881,10 @@
         <v>1.16</v>
       </c>
       <c r="I286" t="n">
-        <v>0.4841</v>
+        <v>0.4714</v>
       </c>
       <c r="J286" t="n">
-        <v>11.6184</v>
+        <v>11.3136</v>
       </c>
     </row>
     <row r="287">
@@ -13921,10 +13921,10 @@
         <v>0.89</v>
       </c>
       <c r="I287" t="n">
-        <v>-0.1337</v>
+        <v>-0.1494</v>
       </c>
       <c r="J287" t="n">
-        <v>-3.2088</v>
+        <v>-3.5856</v>
       </c>
     </row>
     <row r="288">
@@ -13961,10 +13961,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.2149</v>
+        <v>-0.2315</v>
       </c>
       <c r="J288" t="n">
-        <v>-5.1576</v>
+        <v>-5.556</v>
       </c>
     </row>
     <row r="289">
@@ -14001,10 +14001,10 @@
         <v>0.52</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.4895</v>
+        <v>-0.4965</v>
       </c>
       <c r="J289" t="n">
-        <v>-11.748</v>
+        <v>-11.916</v>
       </c>
     </row>
     <row r="290">
@@ -14041,10 +14041,10 @@
         <v>1.27</v>
       </c>
       <c r="I290" t="n">
-        <v>0.6156</v>
+        <v>0.5872000000000001</v>
       </c>
       <c r="J290" t="n">
-        <v>14.7744</v>
+        <v>14.0928</v>
       </c>
     </row>
     <row r="291">
@@ -14081,10 +14081,10 @@
         <v>0.93</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.0892</v>
+        <v>-0.1033</v>
       </c>
       <c r="J291" t="n">
-        <v>-2.1408</v>
+        <v>-2.4792</v>
       </c>
     </row>
     <row r="292">
@@ -14121,10 +14121,10 @@
         <v>1.33</v>
       </c>
       <c r="I292" t="n">
-        <v>0.898</v>
+        <v>0.8381999999999999</v>
       </c>
       <c r="J292" t="n">
-        <v>25.144</v>
+        <v>23.4696</v>
       </c>
     </row>
     <row r="293">
@@ -14161,10 +14161,10 @@
         <v>1.26</v>
       </c>
       <c r="I293" t="n">
-        <v>0.731</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="J293" t="n">
-        <v>20.468</v>
+        <v>19.376</v>
       </c>
     </row>
     <row r="294">
@@ -14201,10 +14201,10 @@
         <v>1.13</v>
       </c>
       <c r="I294" t="n">
-        <v>0.403</v>
+        <v>0.3982</v>
       </c>
       <c r="J294" t="n">
-        <v>11.284</v>
+        <v>11.1496</v>
       </c>
     </row>
     <row r="295">
@@ -14241,10 +14241,10 @@
         <v>1.1</v>
       </c>
       <c r="I295" t="n">
-        <v>0.3231</v>
+        <v>0.3243</v>
       </c>
       <c r="J295" t="n">
-        <v>9.046799999999999</v>
+        <v>9.080399999999999</v>
       </c>
     </row>
     <row r="296">
@@ -14281,10 +14281,10 @@
         <v>0.68</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.9496</v>
+        <v>-0.8705000000000001</v>
       </c>
       <c r="J296" t="n">
-        <v>-26.5888</v>
+        <v>-24.374</v>
       </c>
     </row>
     <row r="297">
@@ -14321,10 +14321,10 @@
         <v>1.13</v>
       </c>
       <c r="I297" t="n">
-        <v>0.3155</v>
+        <v>0.3164</v>
       </c>
       <c r="J297" t="n">
-        <v>8.834</v>
+        <v>8.8592</v>
       </c>
     </row>
     <row r="298">
@@ -14361,10 +14361,10 @@
         <v>1.06</v>
       </c>
       <c r="I298" t="n">
-        <v>0.1692</v>
+        <v>0.1755</v>
       </c>
       <c r="J298" t="n">
-        <v>4.7376</v>
+        <v>4.914</v>
       </c>
     </row>
     <row r="299">
@@ -14401,10 +14401,10 @@
         <v>0.97</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.0477</v>
+        <v>-0.0565</v>
       </c>
       <c r="J299" t="n">
-        <v>-1.3356</v>
+        <v>-1.582</v>
       </c>
     </row>
     <row r="300">
@@ -14441,10 +14441,10 @@
         <v>0.92</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.1083</v>
+        <v>-0.121</v>
       </c>
       <c r="J300" t="n">
-        <v>-3.0324</v>
+        <v>-3.388</v>
       </c>
     </row>
     <row r="301">
@@ -14481,10 +14481,10 @@
         <v>0.76</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.2748</v>
+        <v>-0.2884</v>
       </c>
       <c r="J301" t="n">
-        <v>-7.6944</v>
+        <v>-8.075200000000001</v>
       </c>
     </row>
     <row r="302">
@@ -14521,10 +14521,10 @@
         <v>1.22</v>
       </c>
       <c r="I302" t="n">
-        <v>0.3601</v>
+        <v>0.3636</v>
       </c>
       <c r="J302" t="n">
-        <v>10.803</v>
+        <v>10.908</v>
       </c>
     </row>
     <row r="303">
@@ -14561,10 +14561,10 @@
         <v>1.12</v>
       </c>
       <c r="I303" t="n">
-        <v>0.2165</v>
+        <v>0.2258</v>
       </c>
       <c r="J303" t="n">
-        <v>6.495</v>
+        <v>6.774</v>
       </c>
     </row>
     <row r="304">
@@ -14601,10 +14601,10 @@
         <v>0.99</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.0216</v>
+        <v>-0.026</v>
       </c>
       <c r="J304" t="n">
-        <v>-0.648</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="305">
@@ -14641,10 +14641,10 @@
         <v>0.89</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.1468</v>
+        <v>-0.1594</v>
       </c>
       <c r="J305" t="n">
-        <v>-4.404</v>
+        <v>-4.782</v>
       </c>
     </row>
     <row r="306">
@@ -14681,10 +14681,10 @@
         <v>0.85</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.1896</v>
+        <v>-0.2027</v>
       </c>
       <c r="J306" t="n">
-        <v>-5.688</v>
+        <v>-6.081</v>
       </c>
     </row>
     <row r="307">
@@ -14721,10 +14721,10 @@
         <v>1.44</v>
       </c>
       <c r="I307" t="n">
-        <v>0.5924</v>
+        <v>0.5901</v>
       </c>
       <c r="J307" t="n">
-        <v>17.772</v>
+        <v>17.703</v>
       </c>
     </row>
     <row r="308">
@@ -14761,10 +14761,10 @@
         <v>1.14</v>
       </c>
       <c r="I308" t="n">
-        <v>0.2226</v>
+        <v>0.2367</v>
       </c>
       <c r="J308" t="n">
-        <v>6.678</v>
+        <v>7.101</v>
       </c>
     </row>
     <row r="309">
@@ -14801,10 +14801,10 @@
         <v>1.13</v>
       </c>
       <c r="I309" t="n">
-        <v>0.209</v>
+        <v>0.2232</v>
       </c>
       <c r="J309" t="n">
-        <v>6.27</v>
+        <v>6.696</v>
       </c>
     </row>
     <row r="310">
@@ -14841,10 +14841,10 @@
         <v>0.79</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.2549</v>
+        <v>-0.2669</v>
       </c>
       <c r="J310" t="n">
-        <v>-7.647</v>
+        <v>-8.007</v>
       </c>
     </row>
     <row r="311">
@@ -14881,10 +14881,10 @@
         <v>0.76</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.2844</v>
+        <v>-0.296</v>
       </c>
       <c r="J311" t="n">
-        <v>-8.532</v>
+        <v>-8.880000000000001</v>
       </c>
     </row>
     <row r="312">
@@ -14921,10 +14921,10 @@
         <v>1.43</v>
       </c>
       <c r="I312" t="n">
-        <v>1.0492</v>
+        <v>0.9996</v>
       </c>
       <c r="J312" t="n">
-        <v>27.2792</v>
+        <v>25.9896</v>
       </c>
     </row>
     <row r="313">
@@ -14961,10 +14961,10 @@
         <v>1.34</v>
       </c>
       <c r="I313" t="n">
-        <v>0.8831</v>
+        <v>0.8318</v>
       </c>
       <c r="J313" t="n">
-        <v>22.9606</v>
+        <v>21.6268</v>
       </c>
     </row>
     <row r="314">
@@ -15001,10 +15001,10 @@
         <v>1.22</v>
       </c>
       <c r="I314" t="n">
-        <v>0.606</v>
+        <v>0.5868</v>
       </c>
       <c r="J314" t="n">
-        <v>15.756</v>
+        <v>15.2568</v>
       </c>
     </row>
     <row r="315">
@@ -15041,10 +15041,10 @@
         <v>1.07</v>
       </c>
       <c r="I315" t="n">
-        <v>0.2135</v>
+        <v>0.2277</v>
       </c>
       <c r="J315" t="n">
-        <v>5.551</v>
+        <v>5.9202</v>
       </c>
     </row>
     <row r="316">
@@ -15081,10 +15081,10 @@
         <v>0.97</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.1835</v>
+        <v>-0.1726</v>
       </c>
       <c r="J316" t="n">
-        <v>-4.771</v>
+        <v>-4.4876</v>
       </c>
     </row>
     <row r="317">
@@ -15121,10 +15121,10 @@
         <v>1.39</v>
       </c>
       <c r="I317" t="n">
-        <v>0.8478</v>
+        <v>0.7931</v>
       </c>
       <c r="J317" t="n">
-        <v>22.0428</v>
+        <v>20.6206</v>
       </c>
     </row>
     <row r="318">
@@ -15161,10 +15161,10 @@
         <v>0.91</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.109</v>
+        <v>-0.1247</v>
       </c>
       <c r="J318" t="n">
-        <v>-2.834</v>
+        <v>-3.2422</v>
       </c>
     </row>
     <row r="319">
@@ -15201,10 +15201,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.2118</v>
+        <v>-0.2291</v>
       </c>
       <c r="J319" t="n">
-        <v>-5.5068</v>
+        <v>-5.9566</v>
       </c>
     </row>
     <row r="320">
@@ -15241,10 +15241,10 @@
         <v>0.68</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.3376</v>
+        <v>-0.3522</v>
       </c>
       <c r="J320" t="n">
-        <v>-8.7776</v>
+        <v>-9.1572</v>
       </c>
     </row>
     <row r="321">
@@ -15281,10 +15281,10 @@
         <v>0.5</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.5047</v>
+        <v>-0.5113</v>
       </c>
       <c r="J321" t="n">
-        <v>-13.1222</v>
+        <v>-13.2938</v>
       </c>
     </row>
     <row r="322">
@@ -15321,10 +15321,10 @@
         <v>1.14</v>
       </c>
       <c r="I322" t="n">
-        <v>0.2519</v>
+        <v>0.2589</v>
       </c>
       <c r="J322" t="n">
-        <v>7.557</v>
+        <v>7.767</v>
       </c>
     </row>
     <row r="323">
@@ -15361,10 +15361,10 @@
         <v>1.06</v>
       </c>
       <c r="I323" t="n">
-        <v>0.1258</v>
+        <v>0.1347</v>
       </c>
       <c r="J323" t="n">
-        <v>3.774</v>
+        <v>4.041</v>
       </c>
     </row>
     <row r="324">
@@ -15401,10 +15401,10 @@
         <v>0.99</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.0199</v>
+        <v>-0.0247</v>
       </c>
       <c r="J324" t="n">
-        <v>-0.597</v>
+        <v>-0.741</v>
       </c>
     </row>
     <row r="325">
@@ -15441,10 +15441,10 @@
         <v>0.89</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.1439</v>
+        <v>-0.1572</v>
       </c>
       <c r="J325" t="n">
-        <v>-4.317</v>
+        <v>-4.716</v>
       </c>
     </row>
     <row r="326">
@@ -15481,10 +15481,10 @@
         <v>0.86</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.1761</v>
+        <v>-0.1898</v>
       </c>
       <c r="J326" t="n">
-        <v>-5.283</v>
+        <v>-5.694</v>
       </c>
     </row>
     <row r="327">
@@ -15521,10 +15521,10 @@
         <v>1.38</v>
       </c>
       <c r="I327" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.5178</v>
       </c>
       <c r="J327" t="n">
-        <v>15.408</v>
+        <v>15.534</v>
       </c>
     </row>
     <row r="328">
@@ -15561,10 +15561,10 @@
         <v>1.31</v>
       </c>
       <c r="I328" t="n">
-        <v>0.4308</v>
+        <v>0.4395</v>
       </c>
       <c r="J328" t="n">
-        <v>12.924</v>
+        <v>13.185</v>
       </c>
     </row>
     <row r="329">
@@ -15601,10 +15601,10 @@
         <v>1.02</v>
       </c>
       <c r="I329" t="n">
-        <v>0.0383</v>
+        <v>0.0481</v>
       </c>
       <c r="J329" t="n">
-        <v>1.149</v>
+        <v>1.443</v>
       </c>
     </row>
     <row r="330">
@@ -15641,10 +15641,10 @@
         <v>0.91</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.1324</v>
+        <v>-0.1427</v>
       </c>
       <c r="J330" t="n">
-        <v>-3.972</v>
+        <v>-4.281</v>
       </c>
     </row>
     <row r="331">
@@ -15681,10 +15681,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.2385</v>
+        <v>-0.2499</v>
       </c>
       <c r="J331" t="n">
-        <v>-7.155</v>
+        <v>-7.497</v>
       </c>
     </row>
     <row r="332">
@@ -15721,10 +15721,10 @@
         <v>1.65</v>
       </c>
       <c r="I332" t="n">
-        <v>1.2979</v>
+        <v>1.2769</v>
       </c>
       <c r="J332" t="n">
-        <v>31.1496</v>
+        <v>30.6456</v>
       </c>
     </row>
     <row r="333">
@@ -15761,10 +15761,10 @@
         <v>1.51</v>
       </c>
       <c r="I333" t="n">
-        <v>1.1274</v>
+        <v>1.0943</v>
       </c>
       <c r="J333" t="n">
-        <v>27.0576</v>
+        <v>26.2632</v>
       </c>
     </row>
     <row r="334">
@@ -15801,10 +15801,10 @@
         <v>1.37</v>
       </c>
       <c r="I334" t="n">
-        <v>0.9185</v>
+        <v>0.8689</v>
       </c>
       <c r="J334" t="n">
-        <v>22.044</v>
+        <v>20.8536</v>
       </c>
     </row>
     <row r="335">
@@ -15841,10 +15841,10 @@
         <v>1.15</v>
       </c>
       <c r="I335" t="n">
-        <v>0.4087</v>
+        <v>0.4139</v>
       </c>
       <c r="J335" t="n">
-        <v>9.8088</v>
+        <v>9.9336</v>
       </c>
     </row>
     <row r="336">
@@ -15881,10 +15881,10 @@
         <v>0.96</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.2474</v>
+        <v>-0.2267</v>
       </c>
       <c r="J336" t="n">
-        <v>-5.9376</v>
+        <v>-5.4408</v>
       </c>
     </row>
     <row r="337">
@@ -15921,10 +15921,10 @@
         <v>0.97</v>
       </c>
       <c r="I337" t="n">
-        <v>-0.0043</v>
+        <v>-0.0227</v>
       </c>
       <c r="J337" t="n">
-        <v>-0.1032</v>
+        <v>-0.5448</v>
       </c>
     </row>
     <row r="338">
@@ -15961,10 +15961,10 @@
         <v>0.83</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.1748</v>
+        <v>-0.1961</v>
       </c>
       <c r="J338" t="n">
-        <v>-4.1952</v>
+        <v>-4.7064</v>
       </c>
     </row>
     <row r="339">
@@ -16001,10 +16001,10 @@
         <v>0.63</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.366</v>
+        <v>-0.3828</v>
       </c>
       <c r="J339" t="n">
-        <v>-8.784000000000001</v>
+        <v>-9.187200000000001</v>
       </c>
     </row>
     <row r="340">
@@ -16041,10 +16041,10 @@
         <v>0.62</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.3754</v>
+        <v>-0.3918</v>
       </c>
       <c r="J340" t="n">
-        <v>-9.009600000000001</v>
+        <v>-9.4032</v>
       </c>
     </row>
     <row r="341">
@@ -16081,10 +16081,10 @@
         <v>0.6</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.3941</v>
+        <v>-0.4096</v>
       </c>
       <c r="J341" t="n">
-        <v>-9.458399999999999</v>
+        <v>-9.830399999999999</v>
       </c>
     </row>
     <row r="342">
@@ -16121,10 +16121,10 @@
         <v>1.57</v>
       </c>
       <c r="I342" t="n">
-        <v>1.2025</v>
+        <v>1.1748</v>
       </c>
       <c r="J342" t="n">
-        <v>26.455</v>
+        <v>25.8456</v>
       </c>
     </row>
     <row r="343">
@@ -16161,10 +16161,10 @@
         <v>1.52</v>
       </c>
       <c r="I343" t="n">
-        <v>1.1411</v>
+        <v>1.1089</v>
       </c>
       <c r="J343" t="n">
-        <v>25.1042</v>
+        <v>24.3958</v>
       </c>
     </row>
     <row r="344">
@@ -16201,10 +16201,10 @@
         <v>1.45</v>
       </c>
       <c r="I344" t="n">
-        <v>1.0538</v>
+        <v>1.0103</v>
       </c>
       <c r="J344" t="n">
-        <v>23.1836</v>
+        <v>22.2266</v>
       </c>
     </row>
     <row r="345">
@@ -16241,10 +16241,10 @@
         <v>1.18</v>
       </c>
       <c r="I345" t="n">
-        <v>0.4875</v>
+        <v>0.4848</v>
       </c>
       <c r="J345" t="n">
-        <v>10.725</v>
+        <v>10.6656</v>
       </c>
     </row>
     <row r="346">
@@ -16281,10 +16281,10 @@
         <v>0.88</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.4883</v>
+        <v>-0.4519</v>
       </c>
       <c r="J346" t="n">
-        <v>-10.7426</v>
+        <v>-9.941800000000001</v>
       </c>
     </row>
     <row r="347">
@@ -16321,10 +16321,10 @@
         <v>0.93</v>
       </c>
       <c r="I347" t="n">
-        <v>-0.06320000000000001</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="J347" t="n">
-        <v>-1.3904</v>
+        <v>-1.8282</v>
       </c>
     </row>
     <row r="348">
@@ -16361,10 +16361,10 @@
         <v>0.91</v>
       </c>
       <c r="I348" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.1083</v>
       </c>
       <c r="J348" t="n">
-        <v>-1.936</v>
+        <v>-2.3826</v>
       </c>
     </row>
     <row r="349">
@@ -16401,10 +16401,10 @@
         <v>0.67</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.331</v>
+        <v>-0.3488</v>
       </c>
       <c r="J349" t="n">
-        <v>-7.282</v>
+        <v>-7.6736</v>
       </c>
     </row>
     <row r="350">
@@ -16441,10 +16441,10 @@
         <v>0.65</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.3497</v>
+        <v>-0.3668</v>
       </c>
       <c r="J350" t="n">
-        <v>-7.6934</v>
+        <v>-8.069599999999999</v>
       </c>
     </row>
     <row r="351">
@@ -16481,10 +16481,10 @@
         <v>0.57</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.4247</v>
+        <v>-0.4382</v>
       </c>
       <c r="J351" t="n">
-        <v>-9.343400000000001</v>
+        <v>-9.6404</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/5206/event_5206_evp_summary.xlsx
+++ b/database/event/5206/event_5206_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.0578</v>
+        <v>4.876</v>
       </c>
       <c r="C2" t="n">
-        <v>2.1016</v>
+        <v>2.026</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6782</v>
+        <v>1.6155</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0578</v>
+        <v>4.876</v>
       </c>
       <c r="F2" t="n">
-        <v>5.0578</v>
+        <v>4.876</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>8.344900000000001</v>
+        <v>8.224299999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>10.4922</v>
+        <v>10.4274</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>10.4922</v>
+        <v>10.4274</v>
       </c>
       <c r="N2" t="n">
         <v>347</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.7367</v>
+        <v>3.5699</v>
       </c>
       <c r="C3" t="n">
-        <v>1.5526</v>
+        <v>1.4833</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0768</v>
+        <v>1.0205</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7367</v>
+        <v>3.5699</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7367</v>
+        <v>3.5699</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>5.4536</v>
+        <v>5.231</v>
       </c>
       <c r="I3" t="n">
-        <v>6.0378</v>
+        <v>5.813</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>6.0378</v>
+        <v>5.813</v>
       </c>
       <c r="N3" t="n">
         <v>246</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.5886</v>
+        <v>3.5125</v>
       </c>
       <c r="C4" t="n">
-        <v>1.4911</v>
+        <v>1.4595</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0094</v>
+        <v>0.9943</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5886</v>
+        <v>3.5125</v>
       </c>
       <c r="F4" t="n">
-        <v>3.5886</v>
+        <v>3.5125</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>5.1293</v>
+        <v>5.0994</v>
       </c>
       <c r="I4" t="n">
-        <v>5.6788</v>
+        <v>5.6667</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>5.6788</v>
+        <v>5.6667</v>
       </c>
       <c r="N4" t="n">
         <v>164</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.2307</v>
+        <v>3.1198</v>
       </c>
       <c r="C5" t="n">
-        <v>1.3424</v>
+        <v>1.2963</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8465</v>
+        <v>0.8154</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2307</v>
+        <v>3.1198</v>
       </c>
       <c r="F5" t="n">
-        <v>3.2307</v>
+        <v>3.1198</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4.346</v>
+        <v>4.1996</v>
       </c>
       <c r="I5" t="n">
-        <v>5.0627</v>
+        <v>4.9195</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>5.0627</v>
+        <v>4.9195</v>
       </c>
       <c r="N5" t="n">
         <v>286</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.4766</v>
+        <v>2.4333</v>
       </c>
       <c r="C6" t="n">
-        <v>1.029</v>
+        <v>1.0111</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5032</v>
+        <v>0.5027</v>
       </c>
       <c r="E6" t="n">
-        <v>2.4766</v>
+        <v>2.4333</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4766</v>
+        <v>2.4333</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2.6956</v>
+        <v>2.6262</v>
       </c>
       <c r="I6" t="n">
-        <v>3.1402</v>
+        <v>3.0764</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1402</v>
+        <v>3.0764</v>
       </c>
       <c r="N6" t="n">
         <v>402</v>
@@ -722,93 +722,93 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.4652</v>
+        <v>2.4217</v>
       </c>
       <c r="C7" t="n">
-        <v>1.0243</v>
+        <v>1.0062</v>
       </c>
       <c r="D7" t="n">
-        <v>0.498</v>
+        <v>0.4974</v>
       </c>
       <c r="E7" t="n">
-        <v>2.4652</v>
+        <v>2.4217</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4652</v>
+        <v>2.4217</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6706</v>
+        <v>2.5997</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9567</v>
+        <v>3.3842</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>356</v>
+        <v>335</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9567</v>
+        <v>3.3842</v>
       </c>
       <c r="N7" t="n">
-        <v>356</v>
+        <v>335</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.3955</v>
+        <v>2.341</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9954</v>
+        <v>0.9727</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4663</v>
+        <v>0.4606</v>
       </c>
       <c r="E8" t="n">
-        <v>2.3955</v>
+        <v>2.341</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3955</v>
+        <v>2.341</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.5181</v>
+        <v>2.4147</v>
       </c>
       <c r="I8" t="n">
-        <v>3.2477</v>
+        <v>2.6834</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>335</v>
+        <v>356</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2477</v>
+        <v>2.6834</v>
       </c>
       <c r="N8" t="n">
-        <v>335</v>
+        <v>356</v>
       </c>
     </row>
     <row r="9">
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.3414</v>
+        <v>2.3043</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9729</v>
+        <v>0.9575</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4417</v>
+        <v>0.4439</v>
       </c>
       <c r="E9" t="n">
-        <v>2.3414</v>
+        <v>2.3043</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3414</v>
+        <v>2.3043</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.3998</v>
+        <v>2.3307</v>
       </c>
       <c r="I9" t="n">
-        <v>2.5901</v>
+        <v>2.5226</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.5901</v>
+        <v>2.5226</v>
       </c>
       <c r="N9" t="n">
         <v>214</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.1786</v>
+        <v>1.9588</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9052</v>
+        <v>0.8139</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3675</v>
+        <v>0.2865</v>
       </c>
       <c r="E10" t="n">
-        <v>2.1786</v>
+        <v>1.9588</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1786</v>
+        <v>1.9588</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.1786</v>
+        <v>1.9588</v>
       </c>
       <c r="I10" t="n">
-        <v>2.2923</v>
+        <v>2.0649</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.2923</v>
+        <v>2.0649</v>
       </c>
       <c r="N10" t="n">
         <v>161</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.7129</v>
+        <v>1.5907</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7117</v>
+        <v>0.6609</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1555</v>
+        <v>0.1189</v>
       </c>
       <c r="E11" t="n">
-        <v>1.7129</v>
+        <v>1.5907</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7129</v>
+        <v>1.5907</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.7129</v>
+        <v>1.5907</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8964</v>
+        <v>1.7676</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.8964</v>
+        <v>1.7676</v>
       </c>
       <c r="N11" t="n">
         <v>248</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.5197</v>
+        <v>1.303</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6314</v>
+        <v>0.5414</v>
       </c>
       <c r="D12" t="n">
-        <v>0.06759999999999999</v>
+        <v>-0.0122</v>
       </c>
       <c r="E12" t="n">
-        <v>1.5197</v>
+        <v>1.303</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5197</v>
+        <v>1.303</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.5197</v>
+        <v>1.303</v>
       </c>
       <c r="I12" t="n">
-        <v>1.599</v>
+        <v>1.3735</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.599</v>
+        <v>1.3735</v>
       </c>
       <c r="N12" t="n">
         <v>161</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.2837</v>
+        <v>1.2559</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5334</v>
+        <v>0.5218</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0398</v>
+        <v>-0.0337</v>
       </c>
       <c r="E13" t="n">
-        <v>1.2837</v>
+        <v>1.2559</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2837</v>
+        <v>1.2559</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.2837</v>
+        <v>1.2559</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5339</v>
+        <v>1.5105</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.5339</v>
+        <v>1.5105</v>
       </c>
       <c r="N13" t="n">
         <v>333</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.2103</v>
+        <v>1.141</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5029</v>
+        <v>0.4741</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0732</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>1.2103</v>
+        <v>1.141</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2103</v>
+        <v>1.141</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2103</v>
+        <v>1.141</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3063</v>
+        <v>1.2349</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.3063</v>
+        <v>1.2349</v>
       </c>
       <c r="N14" t="n">
         <v>214</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.1676</v>
+        <v>1.1369</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4851</v>
+        <v>0.4724</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0927</v>
+        <v>-0.08790000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1676</v>
+        <v>1.1369</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1676</v>
+        <v>1.1369</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1676</v>
+        <v>1.1369</v>
       </c>
       <c r="I15" t="n">
-        <v>1.326</v>
+        <v>1.2971</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.326</v>
+        <v>1.2971</v>
       </c>
       <c r="N15" t="n">
         <v>300</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.0819</v>
+        <v>1.101</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4495</v>
+        <v>0.4575</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1317</v>
+        <v>-0.1042</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0819</v>
+        <v>1.101</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0819</v>
+        <v>1.101</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0819</v>
+        <v>1.101</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1677</v>
+        <v>1.1917</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1677</v>
+        <v>1.1917</v>
       </c>
       <c r="N16" t="n">
         <v>205</v>
@@ -1182,185 +1182,185 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9956</v>
+        <v>0.9147</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4137</v>
+        <v>0.3801</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.171</v>
+        <v>-0.1891</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9956</v>
+        <v>0.9147</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9956</v>
+        <v>0.9147</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9956</v>
+        <v>0.9147</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0213</v>
+        <v>1.1001</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>172</v>
+        <v>298</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.0213</v>
+        <v>1.1001</v>
       </c>
       <c r="N17" t="n">
-        <v>172</v>
+        <v>298</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9746</v>
+        <v>0.9106</v>
       </c>
       <c r="C18" t="n">
-        <v>0.405</v>
+        <v>0.3784</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1805</v>
+        <v>-0.191</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9746</v>
+        <v>0.9106</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9746</v>
+        <v>0.9106</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9746</v>
+        <v>0.9106</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1068</v>
+        <v>0.9349</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1068</v>
+        <v>0.9349</v>
       </c>
       <c r="N18" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.8976</v>
       </c>
       <c r="C19" t="n">
         <v>0.373</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2156</v>
+        <v>-0.1969</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.8976</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.8976</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.8976</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0727</v>
+        <v>1.0796</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>298</v>
+        <v>261</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0727</v>
+        <v>1.0796</v>
       </c>
       <c r="N19" t="n">
-        <v>298</v>
+        <v>261</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8501</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3532</v>
+        <v>0.3575</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2372</v>
+        <v>-0.2138</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8501</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8501</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8501</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0158</v>
+        <v>0.9817</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>261</v>
+        <v>171</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.0158</v>
+        <v>0.9817</v>
       </c>
       <c r="N20" t="n">
-        <v>261</v>
+        <v>171</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7491</v>
+        <v>0.7359</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3113</v>
+        <v>0.3058</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2832</v>
+        <v>-0.2706</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7491</v>
+        <v>0.7359</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7491</v>
+        <v>0.7359</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7491</v>
+        <v>0.7359</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7684</v>
+        <v>0.7556</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7684</v>
+        <v>0.7556</v>
       </c>
       <c r="N21" t="n">
         <v>160</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7237</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3007</v>
+        <v>0.2649</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2948</v>
+        <v>-0.3153</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7237</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7237</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7237</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8648</v>
+        <v>0.7668</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8648</v>
+        <v>0.7668</v>
       </c>
       <c r="N22" t="n">
         <v>286</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6153</v>
+        <v>0.4927</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2557</v>
+        <v>0.2047</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3441</v>
+        <v>-0.3813</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6153</v>
+        <v>0.4927</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6153</v>
+        <v>0.4927</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6153</v>
+        <v>0.4927</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7168</v>
+        <v>0.5772</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7168</v>
+        <v>0.5772</v>
       </c>
       <c r="N23" t="n">
         <v>298</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5225</v>
+        <v>0.4807</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2171</v>
+        <v>0.1997</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3864</v>
+        <v>-0.3868</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5225</v>
+        <v>0.4807</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5225</v>
+        <v>0.4807</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5225</v>
+        <v>0.4807</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6244</v>
+        <v>0.5782</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6244</v>
+        <v>0.5782</v>
       </c>
       <c r="N24" t="n">
         <v>262</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4666</v>
+        <v>0.3586</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1939</v>
+        <v>0.149</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4118</v>
+        <v>-0.4424</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4666</v>
+        <v>0.3586</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4666</v>
+        <v>0.3586</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4666</v>
+        <v>0.3586</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5036</v>
+        <v>0.3881</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5036</v>
+        <v>0.3881</v>
       </c>
       <c r="N25" t="n">
         <v>205</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3769</v>
+        <v>0.2935</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1566</v>
+        <v>0.122</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4526</v>
+        <v>-0.4721</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3769</v>
+        <v>0.2935</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3769</v>
+        <v>0.2935</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3769</v>
+        <v>0.2935</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4068</v>
+        <v>0.3177</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4068</v>
+        <v>0.3177</v>
       </c>
       <c r="N26" t="n">
         <v>205</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3421</v>
+        <v>0.2422</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1421</v>
+        <v>0.1006</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4685</v>
+        <v>-0.4955</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3421</v>
+        <v>0.2422</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3421</v>
+        <v>0.2422</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3421</v>
+        <v>0.2422</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3985</v>
+        <v>0.2838</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3985</v>
+        <v>0.2838</v>
       </c>
       <c r="N27" t="n">
         <v>332</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.3196</v>
+        <v>0.242</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1328</v>
+        <v>0.1006</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4787</v>
+        <v>-0.4955</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3196</v>
+        <v>0.242</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3196</v>
+        <v>0.242</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3196</v>
+        <v>0.242</v>
       </c>
       <c r="I28" t="n">
-        <v>0.345</v>
+        <v>0.2619</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.345</v>
+        <v>0.2619</v>
       </c>
       <c r="N28" t="n">
         <v>214</v>
@@ -1734,185 +1734,185 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>VINI</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1986</v>
+        <v>-0.2412</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0825</v>
+        <v>-0.1002</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7146</v>
+        <v>-0.7157</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1986</v>
+        <v>-0.2412</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1986</v>
+        <v>-0.2412</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1986</v>
+        <v>-0.2412</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.209</v>
+        <v>-0.2825</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>161</v>
+        <v>250</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.209</v>
+        <v>-0.2825</v>
       </c>
       <c r="N29" t="n">
-        <v>161</v>
+        <v>250</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>VINI</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.2023</v>
+        <v>-0.3059</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-0.1271</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7163</v>
+        <v>-0.7451</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.2023</v>
+        <v>-0.3059</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.2023</v>
+        <v>-0.3059</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.2023</v>
+        <v>-0.3059</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2357</v>
+        <v>-0.3225</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>250</v>
+        <v>161</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.2357</v>
+        <v>-0.3225</v>
       </c>
       <c r="N30" t="n">
-        <v>250</v>
+        <v>161</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.419</v>
+        <v>-0.4345</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1741</v>
+        <v>-0.1805</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8149</v>
+        <v>-0.8037</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.419</v>
+        <v>-0.4345</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.419</v>
+        <v>-0.4345</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.419</v>
+        <v>-0.4345</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4522</v>
+        <v>-0.4581</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>205</v>
+        <v>161</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.4522</v>
+        <v>-0.4581</v>
       </c>
       <c r="N31" t="n">
-        <v>205</v>
+        <v>161</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.447</v>
+        <v>-0.4681</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1857</v>
+        <v>-0.1945</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8277</v>
+        <v>-0.819</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.447</v>
+        <v>-0.4681</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.447</v>
+        <v>-0.4681</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.447</v>
+        <v>-0.4681</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4703</v>
+        <v>-0.5066000000000001</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>161</v>
+        <v>205</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4703</v>
+        <v>-0.5066000000000001</v>
       </c>
       <c r="N32" t="n">
-        <v>161</v>
+        <v>205</v>
       </c>
     </row>
     <row r="33">
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.842</v>
+        <v>-0.8362000000000001</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.3499</v>
+        <v>-0.3474</v>
       </c>
       <c r="D33" t="n">
-        <v>-1.0075</v>
+        <v>-0.9867</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.842</v>
+        <v>-0.8362000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.842</v>
+        <v>-0.8362000000000001</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.842</v>
+        <v>-0.8362000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.9088000000000001</v>
+        <v>-0.905</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.9088000000000001</v>
+        <v>-0.905</v>
       </c>
       <c r="N33" t="n">
         <v>214</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.9885</v>
+        <v>-0.9593</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.4107</v>
+        <v>-0.3986</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.0742</v>
+        <v>-1.0428</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.9885</v>
+        <v>-0.9593</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.9885</v>
+        <v>-0.9593</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.9885</v>
+        <v>-0.9593</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.0669</v>
+        <v>-1.0382</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.0669</v>
+        <v>-1.0382</v>
       </c>
       <c r="N34" t="n">
         <v>106</v>
@@ -2010,139 +2010,139 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>Nivera</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.0812</v>
+        <v>-1.0911</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.4492</v>
+        <v>-0.4534</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.1164</v>
+        <v>-1.1028</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.0812</v>
+        <v>-1.0911</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.0812</v>
+        <v>-1.0911</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.0812</v>
+        <v>-1.0911</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.2279</v>
+        <v>-1.1502</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.2279</v>
+        <v>-1.1502</v>
       </c>
       <c r="N35" t="n">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Nivera</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.1558</v>
+        <v>-1.1556</v>
       </c>
       <c r="C36" t="n">
         <v>-0.4802</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.1503</v>
+        <v>-1.1322</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.1558</v>
+        <v>-1.1556</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.1558</v>
+        <v>-1.1556</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.1558</v>
+        <v>-1.1556</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.2161</v>
+        <v>-1.2842</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>167</v>
+        <v>217</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.2161</v>
+        <v>-1.2842</v>
       </c>
       <c r="N36" t="n">
-        <v>167</v>
+        <v>217</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.1869</v>
+        <v>-1.1653</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.4932</v>
+        <v>-0.4842</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1645</v>
+        <v>-1.1366</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.1869</v>
+        <v>-1.1653</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.1869</v>
+        <v>-1.1653</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.1869</v>
+        <v>-1.1653</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.314</v>
+        <v>-1.3295</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>217</v>
+        <v>172</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.314</v>
+        <v>-1.3295</v>
       </c>
       <c r="N37" t="n">
-        <v>217</v>
+        <v>172</v>
       </c>
     </row>
     <row r="38">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.3261</v>
+        <v>-1.2724</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.551</v>
+        <v>-0.5286999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.2279</v>
+        <v>-1.1854</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.3261</v>
+        <v>-1.2724</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.3261</v>
+        <v>-1.2724</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.3261</v>
+        <v>-1.2724</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.4313</v>
+        <v>-1.3771</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.4313</v>
+        <v>-1.3771</v>
       </c>
       <c r="N38" t="n">
         <v>205</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.3763</v>
+        <v>-1.3131</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.5719</v>
+        <v>-0.5456</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2507</v>
+        <v>-1.204</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.3763</v>
+        <v>-1.3131</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.3763</v>
+        <v>-1.3131</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.3763</v>
+        <v>-1.3131</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.4481</v>
+        <v>-1.3842</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.4481</v>
+        <v>-1.3842</v>
       </c>
       <c r="N39" t="n">
         <v>161</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.6048</v>
+        <v>-1.5357</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.6667999999999999</v>
+        <v>-0.6381</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3547</v>
+        <v>-1.3054</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.6048</v>
+        <v>-1.5357</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.6048</v>
+        <v>-1.5357</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.6048</v>
+        <v>-1.5357</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.7321</v>
+        <v>-1.6621</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.7321</v>
+        <v>-1.6621</v>
       </c>
       <c r="N40" t="n">
         <v>214</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.8055</v>
+        <v>-1.903</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.7502</v>
+        <v>-0.7907</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4461</v>
+        <v>-1.4727</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.8055</v>
+        <v>-1.903</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.8055</v>
+        <v>-1.903</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.8055</v>
+        <v>-1.903</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.8997</v>
+        <v>-2.006</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.8997</v>
+        <v>-2.006</v>
       </c>
       <c r="N41" t="n">
         <v>145</v>
@@ -2336,28 +2336,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-2.0483</v>
+        <v>-1.9882</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.8511</v>
+        <v>-0.8260999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.5566</v>
+        <v>-1.5115</v>
       </c>
       <c r="E42" t="n">
-        <v>-2.0483</v>
+        <v>-1.9882</v>
       </c>
       <c r="F42" t="n">
-        <v>-2.0483</v>
+        <v>-1.9882</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>-2.0483</v>
+        <v>-1.9882</v>
       </c>
       <c r="I42" t="n">
-        <v>-2.2108</v>
+        <v>-2.1519</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>-2.2108</v>
+        <v>-2.1519</v>
       </c>
       <c r="N42" t="n">
         <v>76</v>
@@ -2382,28 +2382,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-2.8097</v>
+        <v>-2.7207</v>
       </c>
       <c r="C43" t="n">
-        <v>-1.1675</v>
+        <v>-1.1305</v>
       </c>
       <c r="D43" t="n">
-        <v>-1.9032</v>
+        <v>-1.8452</v>
       </c>
       <c r="E43" t="n">
-        <v>-2.8097</v>
+        <v>-2.7207</v>
       </c>
       <c r="F43" t="n">
-        <v>-2.8097</v>
+        <v>-2.7207</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-2.8097</v>
+        <v>-2.7207</v>
       </c>
       <c r="I43" t="n">
-        <v>-3.1107</v>
+        <v>-3.0234</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>-3.1107</v>
+        <v>-3.0234</v>
       </c>
       <c r="N43" t="n">
         <v>100</v>
@@ -2521,10 +2521,10 @@
         <v>1.53</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8792</v>
+        <v>0.8268</v>
       </c>
       <c r="J2" t="n">
-        <v>24.6176</v>
+        <v>23.1504</v>
       </c>
     </row>
     <row r="3">
@@ -2561,10 +2561,10 @@
         <v>1.4</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6992</v>
+        <v>0.6412</v>
       </c>
       <c r="J3" t="n">
-        <v>19.5776</v>
+        <v>17.9536</v>
       </c>
     </row>
     <row r="4">
@@ -2601,10 +2601,10 @@
         <v>1.28</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5241</v>
+        <v>0.4676</v>
       </c>
       <c r="J4" t="n">
-        <v>14.6748</v>
+        <v>13.0928</v>
       </c>
     </row>
     <row r="5">
@@ -2641,10 +2641,10 @@
         <v>1.01</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0176</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4928</v>
+        <v>0.2688</v>
       </c>
     </row>
     <row r="6">
@@ -2681,10 +2681,10 @@
         <v>0.85</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.219</v>
+        <v>-0.1998</v>
       </c>
       <c r="J6" t="n">
-        <v>-6.132</v>
+        <v>-5.5944</v>
       </c>
     </row>
     <row r="7">
@@ -2721,10 +2721,10 @@
         <v>0.83</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4902</v>
+        <v>-0.451</v>
       </c>
       <c r="J7" t="n">
-        <v>-13.7256</v>
+        <v>-12.628</v>
       </c>
     </row>
     <row r="8">
@@ -2761,10 +2761,10 @@
         <v>1.06</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2667</v>
+        <v>0.2284</v>
       </c>
       <c r="J8" t="n">
-        <v>7.4676</v>
+        <v>6.3952</v>
       </c>
     </row>
     <row r="9">
@@ -2801,10 +2801,10 @@
         <v>1.02</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1307</v>
+        <v>0.1034</v>
       </c>
       <c r="J9" t="n">
-        <v>3.6596</v>
+        <v>2.8952</v>
       </c>
     </row>
     <row r="10">
@@ -2841,10 +2841,10 @@
         <v>0.95</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.178</v>
+        <v>-0.151</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.984</v>
+        <v>-4.228</v>
       </c>
     </row>
     <row r="11">
@@ -2881,10 +2881,10 @@
         <v>0.51</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.1733</v>
+        <v>-1.1897</v>
       </c>
       <c r="J11" t="n">
-        <v>-32.8524</v>
+        <v>-33.3116</v>
       </c>
     </row>
     <row r="12">
@@ -2921,10 +2921,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.468</v>
+        <v>-0.4648</v>
       </c>
       <c r="J12" t="n">
-        <v>-9.827999999999999</v>
+        <v>-9.7608</v>
       </c>
     </row>
     <row r="13">
@@ -2961,10 +2961,10 @@
         <v>1.35</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>14.511</v>
+        <v>13.3686</v>
       </c>
     </row>
     <row r="14">
@@ -3001,10 +3001,10 @@
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0055</v>
+        <v>0.0031</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1155</v>
+        <v>0.06510000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -3041,10 +3041,10 @@
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0055</v>
+        <v>0.0031</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1155</v>
+        <v>0.06510000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -3081,10 +3081,10 @@
         <v>0.85</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1971</v>
+        <v>-0.1768</v>
       </c>
       <c r="J16" t="n">
-        <v>-4.1391</v>
+        <v>-3.7128</v>
       </c>
     </row>
     <row r="17">
@@ -3121,10 +3121,10 @@
         <v>0.16</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.825</v>
+        <v>-1.9688</v>
       </c>
       <c r="J17" t="n">
-        <v>-38.325</v>
+        <v>-41.3448</v>
       </c>
     </row>
     <row r="18">
@@ -3161,10 +3161,10 @@
         <v>1.05</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3474</v>
+        <v>0.3398</v>
       </c>
       <c r="J18" t="n">
-        <v>7.2954</v>
+        <v>7.1358</v>
       </c>
     </row>
     <row r="19">
@@ -3201,10 +3201,10 @@
         <v>0.98</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0225</v>
+        <v>0.0553</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4725</v>
+        <v>1.1613</v>
       </c>
     </row>
     <row r="20">
@@ -3241,10 +3241,10 @@
         <v>0.6</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.9239000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>-19.656</v>
+        <v>-19.4019</v>
       </c>
     </row>
     <row r="21">
@@ -3281,10 +3281,10 @@
         <v>0.57</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9976</v>
+        <v>-0.9902</v>
       </c>
       <c r="J21" t="n">
-        <v>-20.9496</v>
+        <v>-20.7942</v>
       </c>
     </row>
     <row r="22">
@@ -3321,10 +3321,10 @@
         <v>1.15</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3399</v>
+        <v>0.287</v>
       </c>
       <c r="J22" t="n">
-        <v>12.2364</v>
+        <v>10.332</v>
       </c>
     </row>
     <row r="23">
@@ -3361,10 +3361,10 @@
         <v>1.09</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2276</v>
+        <v>0.1843</v>
       </c>
       <c r="J23" t="n">
-        <v>8.1936</v>
+        <v>6.6348</v>
       </c>
     </row>
     <row r="24">
@@ -3401,10 +3401,10 @@
         <v>0.89</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.161</v>
+        <v>-0.1408</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.796</v>
+        <v>-5.0688</v>
       </c>
     </row>
     <row r="25">
@@ -3441,10 +3441,10 @@
         <v>1.21</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4434</v>
+        <v>0.3856</v>
       </c>
       <c r="J25" t="n">
-        <v>15.9624</v>
+        <v>13.8816</v>
       </c>
     </row>
     <row r="26">
@@ -3481,10 +3481,10 @@
         <v>0.82</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2353</v>
+        <v>-0.215</v>
       </c>
       <c r="J26" t="n">
-        <v>-8.470800000000001</v>
+        <v>-7.74</v>
       </c>
     </row>
     <row r="27">
@@ -3521,10 +3521,10 @@
         <v>0.83</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.5077</v>
+        <v>-0.4661</v>
       </c>
       <c r="J27" t="n">
-        <v>-18.2772</v>
+        <v>-16.7796</v>
       </c>
     </row>
     <row r="28">
@@ -3561,10 +3561,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.8212</v>
+        <v>-0.7969000000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>-29.5632</v>
+        <v>-28.6884</v>
       </c>
     </row>
     <row r="29">
@@ -3601,10 +3601,10 @@
         <v>0.65</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.9056</v>
+        <v>-0.8895999999999999</v>
       </c>
       <c r="J29" t="n">
-        <v>-32.6016</v>
+        <v>-32.0256</v>
       </c>
     </row>
     <row r="30">
@@ -3641,10 +3641,10 @@
         <v>1.37</v>
       </c>
       <c r="I30" t="n">
-        <v>0.9727</v>
+        <v>0.9715</v>
       </c>
       <c r="J30" t="n">
-        <v>35.0172</v>
+        <v>34.974</v>
       </c>
     </row>
     <row r="31">
@@ -3681,10 +3681,10 @@
         <v>1.24</v>
       </c>
       <c r="I31" t="n">
-        <v>0.6944</v>
+        <v>0.6623</v>
       </c>
       <c r="J31" t="n">
-        <v>24.9984</v>
+        <v>23.8428</v>
       </c>
     </row>
     <row r="32">
@@ -3721,10 +3721,10 @@
         <v>1.17</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2646</v>
+        <v>0.2154</v>
       </c>
       <c r="J32" t="n">
-        <v>7.4088</v>
+        <v>6.0312</v>
       </c>
     </row>
     <row r="33">
@@ -3761,10 +3761,10 @@
         <v>0.97</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.07190000000000001</v>
+        <v>-0.0576</v>
       </c>
       <c r="J33" t="n">
-        <v>-2.0132</v>
+        <v>-1.6128</v>
       </c>
     </row>
     <row r="34">
@@ -3801,10 +3801,10 @@
         <v>0.95</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1001</v>
+        <v>-0.0832</v>
       </c>
       <c r="J34" t="n">
-        <v>-2.8028</v>
+        <v>-2.3296</v>
       </c>
     </row>
     <row r="35">
@@ -3841,10 +3841,10 @@
         <v>1.6</v>
       </c>
       <c r="I35" t="n">
-        <v>0.7301</v>
+        <v>0.6587</v>
       </c>
       <c r="J35" t="n">
-        <v>20.4428</v>
+        <v>18.4436</v>
       </c>
     </row>
     <row r="36">
@@ -3881,10 +3881,10 @@
         <v>1.19</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2885</v>
+        <v>0.2366</v>
       </c>
       <c r="J36" t="n">
-        <v>8.077999999999999</v>
+        <v>6.6248</v>
       </c>
     </row>
     <row r="37">
@@ -3921,10 +3921,10 @@
         <v>1.01</v>
       </c>
       <c r="I37" t="n">
-        <v>0.0339</v>
+        <v>0.0258</v>
       </c>
       <c r="J37" t="n">
-        <v>0.9492</v>
+        <v>0.7224</v>
       </c>
     </row>
     <row r="38">
@@ -3961,10 +3961,10 @@
         <v>0.9</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1469</v>
+        <v>-0.1273</v>
       </c>
       <c r="J38" t="n">
-        <v>-4.1132</v>
+        <v>-3.5644</v>
       </c>
     </row>
     <row r="39">
@@ -4001,10 +4001,10 @@
         <v>0.7</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.3477</v>
+        <v>-0.3329</v>
       </c>
       <c r="J39" t="n">
-        <v>-9.7356</v>
+        <v>-9.321199999999999</v>
       </c>
     </row>
     <row r="40">
@@ -4041,10 +4041,10 @@
         <v>1.35</v>
       </c>
       <c r="I40" t="n">
-        <v>0.5289</v>
+        <v>0.5435</v>
       </c>
       <c r="J40" t="n">
-        <v>14.8092</v>
+        <v>15.218</v>
       </c>
     </row>
     <row r="41">
@@ -4081,10 +4081,10 @@
         <v>1.04</v>
       </c>
       <c r="I41" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.0828</v>
       </c>
       <c r="J41" t="n">
-        <v>2.7328</v>
+        <v>2.3184</v>
       </c>
     </row>
     <row r="42">
@@ -4121,10 +4121,10 @@
         <v>0.82</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.216</v>
+        <v>-0.1984</v>
       </c>
       <c r="J42" t="n">
-        <v>-5.616</v>
+        <v>-5.1584</v>
       </c>
     </row>
     <row r="43">
@@ -4161,10 +4161,10 @@
         <v>0.75</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.2822</v>
+        <v>-0.2645</v>
       </c>
       <c r="J43" t="n">
-        <v>-7.3372</v>
+        <v>-6.877</v>
       </c>
     </row>
     <row r="44">
@@ -4201,10 +4201,10 @@
         <v>0.65</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.3743</v>
+        <v>-0.3607</v>
       </c>
       <c r="J44" t="n">
-        <v>-9.7318</v>
+        <v>-9.3782</v>
       </c>
     </row>
     <row r="45">
@@ -4241,10 +4241,10 @@
         <v>0.95</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0678</v>
+        <v>-0.0559</v>
       </c>
       <c r="J45" t="n">
-        <v>-1.7628</v>
+        <v>-1.4534</v>
       </c>
     </row>
     <row r="46">
@@ -4281,10 +4281,10 @@
         <v>0.88</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1534</v>
+        <v>-0.1374</v>
       </c>
       <c r="J46" t="n">
-        <v>-3.9884</v>
+        <v>-3.5724</v>
       </c>
     </row>
     <row r="47">
@@ -4321,10 +4321,10 @@
         <v>1.18</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5077</v>
+        <v>0.4703</v>
       </c>
       <c r="J47" t="n">
-        <v>13.2002</v>
+        <v>12.2278</v>
       </c>
     </row>
     <row r="48">
@@ -4361,10 +4361,10 @@
         <v>0.85</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.4976</v>
+        <v>-0.4569</v>
       </c>
       <c r="J48" t="n">
-        <v>-12.9376</v>
+        <v>-11.8794</v>
       </c>
     </row>
     <row r="49">
@@ -4401,10 +4401,10 @@
         <v>0.64</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9567</v>
       </c>
       <c r="J49" t="n">
-        <v>-24.9912</v>
+        <v>-24.8742</v>
       </c>
     </row>
     <row r="50">
@@ -4441,10 +4441,10 @@
         <v>1.74</v>
       </c>
       <c r="I50" t="n">
-        <v>1.4399</v>
+        <v>1.4731</v>
       </c>
       <c r="J50" t="n">
-        <v>37.4374</v>
+        <v>38.3006</v>
       </c>
     </row>
     <row r="51">
@@ -4481,10 +4481,10 @@
         <v>1.32</v>
       </c>
       <c r="I51" t="n">
-        <v>0.8054</v>
+        <v>0.7798</v>
       </c>
       <c r="J51" t="n">
-        <v>20.9404</v>
+        <v>20.2748</v>
       </c>
     </row>
     <row r="52">
@@ -4521,10 +4521,10 @@
         <v>0.89</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.1504</v>
+        <v>-0.1322</v>
       </c>
       <c r="J52" t="n">
-        <v>-4.3616</v>
+        <v>-3.8338</v>
       </c>
     </row>
     <row r="53">
@@ -4561,10 +4561,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.3478</v>
+        <v>-0.3325</v>
       </c>
       <c r="J53" t="n">
-        <v>-10.0862</v>
+        <v>-9.6425</v>
       </c>
     </row>
     <row r="54">
@@ -4601,10 +4601,10 @@
         <v>0.68</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.357</v>
+        <v>-0.3423</v>
       </c>
       <c r="J54" t="n">
-        <v>-10.353</v>
+        <v>-9.9267</v>
       </c>
     </row>
     <row r="55">
@@ -4641,10 +4641,10 @@
         <v>1.17</v>
       </c>
       <c r="I55" t="n">
-        <v>0.407</v>
+        <v>0.3521</v>
       </c>
       <c r="J55" t="n">
-        <v>11.803</v>
+        <v>10.2109</v>
       </c>
     </row>
     <row r="56">
@@ -4681,10 +4681,10 @@
         <v>1.09</v>
       </c>
       <c r="I56" t="n">
-        <v>0.2535</v>
+        <v>0.2071</v>
       </c>
       <c r="J56" t="n">
-        <v>7.3515</v>
+        <v>6.0059</v>
       </c>
     </row>
     <row r="57">
@@ -4721,10 +4721,10 @@
         <v>0.91</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.3151</v>
+        <v>-0.2741</v>
       </c>
       <c r="J57" t="n">
-        <v>-9.1379</v>
+        <v>-7.9489</v>
       </c>
     </row>
     <row r="58">
@@ -4761,10 +4761,10 @@
         <v>0.67</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.8727</v>
+        <v>-0.8542999999999999</v>
       </c>
       <c r="J58" t="n">
-        <v>-25.3083</v>
+        <v>-24.7747</v>
       </c>
     </row>
     <row r="59">
@@ -4801,10 +4801,10 @@
         <v>0.67</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.8727</v>
+        <v>-0.8542999999999999</v>
       </c>
       <c r="J59" t="n">
-        <v>-25.3083</v>
+        <v>-24.7747</v>
       </c>
     </row>
     <row r="60">
@@ -4841,10 +4841,10 @@
         <v>1.62</v>
       </c>
       <c r="I60" t="n">
-        <v>1.3323</v>
+        <v>1.366</v>
       </c>
       <c r="J60" t="n">
-        <v>38.6367</v>
+        <v>39.614</v>
       </c>
     </row>
     <row r="61">
@@ -4881,10 +4881,10 @@
         <v>1.13</v>
       </c>
       <c r="I61" t="n">
-        <v>0.4193</v>
+        <v>0.3764</v>
       </c>
       <c r="J61" t="n">
-        <v>12.1597</v>
+        <v>10.9156</v>
       </c>
     </row>
     <row r="62">
@@ -4921,10 +4921,10 @@
         <v>0.79</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.2534</v>
+        <v>-0.2338</v>
       </c>
       <c r="J62" t="n">
-        <v>-7.602</v>
+        <v>-7.014</v>
       </c>
     </row>
     <row r="63">
@@ -4961,10 +4961,10 @@
         <v>0.68</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.3572</v>
+        <v>-0.3425</v>
       </c>
       <c r="J63" t="n">
-        <v>-10.716</v>
+        <v>-10.275</v>
       </c>
     </row>
     <row r="64">
@@ -5001,10 +5001,10 @@
         <v>0.67</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.3663</v>
+        <v>-0.3523</v>
       </c>
       <c r="J64" t="n">
-        <v>-10.989</v>
+        <v>-10.569</v>
       </c>
     </row>
     <row r="65">
@@ -5041,10 +5041,10 @@
         <v>1.27</v>
       </c>
       <c r="I65" t="n">
-        <v>0.5789</v>
+        <v>0.5236</v>
       </c>
       <c r="J65" t="n">
-        <v>17.367</v>
+        <v>15.708</v>
       </c>
     </row>
     <row r="66">
@@ -5081,10 +5081,10 @@
         <v>1.12</v>
       </c>
       <c r="I66" t="n">
-        <v>0.3129</v>
+        <v>0.2621</v>
       </c>
       <c r="J66" t="n">
-        <v>9.387</v>
+        <v>7.863</v>
       </c>
     </row>
     <row r="67">
@@ -5121,10 +5121,10 @@
         <v>0.95</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.195</v>
+        <v>-0.1624</v>
       </c>
       <c r="J67" t="n">
-        <v>-5.85</v>
+        <v>-4.872</v>
       </c>
     </row>
     <row r="68">
@@ -5161,10 +5161,10 @@
         <v>0.9</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.3356</v>
+        <v>-0.2947</v>
       </c>
       <c r="J68" t="n">
-        <v>-10.068</v>
+        <v>-8.840999999999999</v>
       </c>
     </row>
     <row r="69">
@@ -5201,10 +5201,10 @@
         <v>0.68</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.845</v>
+        <v>-0.8232</v>
       </c>
       <c r="J69" t="n">
-        <v>-25.35</v>
+        <v>-24.696</v>
       </c>
     </row>
     <row r="70">
@@ -5241,10 +5241,10 @@
         <v>1.22</v>
       </c>
       <c r="I70" t="n">
-        <v>0.6444</v>
+        <v>0.6085</v>
       </c>
       <c r="J70" t="n">
-        <v>19.332</v>
+        <v>18.255</v>
       </c>
     </row>
     <row r="71">
@@ -5281,10 +5281,10 @@
         <v>1.09</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3233</v>
+        <v>0.2814</v>
       </c>
       <c r="J71" t="n">
-        <v>9.699</v>
+        <v>8.442</v>
       </c>
     </row>
     <row r="72">
@@ -5321,10 +5321,10 @@
         <v>0.84</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.4868</v>
+        <v>-0.4446</v>
       </c>
       <c r="J72" t="n">
-        <v>-14.604</v>
+        <v>-13.338</v>
       </c>
     </row>
     <row r="73">
@@ -5361,10 +5361,10 @@
         <v>0.75</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.6939</v>
+        <v>-0.6601</v>
       </c>
       <c r="J73" t="n">
-        <v>-20.817</v>
+        <v>-19.803</v>
       </c>
     </row>
     <row r="74">
@@ -5401,10 +5401,10 @@
         <v>0.73</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.7379</v>
+        <v>-0.7071</v>
       </c>
       <c r="J74" t="n">
-        <v>-22.137</v>
+        <v>-21.213</v>
       </c>
     </row>
     <row r="75">
@@ -5441,10 +5441,10 @@
         <v>1.32</v>
       </c>
       <c r="I75" t="n">
-        <v>0.864</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="J75" t="n">
-        <v>25.92</v>
+        <v>25.389</v>
       </c>
     </row>
     <row r="76">
@@ -5481,10 +5481,10 @@
         <v>1.21</v>
       </c>
       <c r="I76" t="n">
-        <v>0.6207</v>
+        <v>0.5834</v>
       </c>
       <c r="J76" t="n">
-        <v>18.621</v>
+        <v>17.502</v>
       </c>
     </row>
     <row r="77">
@@ -5521,10 +5521,10 @@
         <v>1.14</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3086</v>
+        <v>0.2609</v>
       </c>
       <c r="J77" t="n">
-        <v>9.257999999999999</v>
+        <v>7.827</v>
       </c>
     </row>
     <row r="78">
@@ -5561,10 +5561,10 @@
         <v>0.99</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.0349</v>
+        <v>-0.0257</v>
       </c>
       <c r="J78" t="n">
-        <v>-1.047</v>
+        <v>-0.771</v>
       </c>
     </row>
     <row r="79">
@@ -5601,10 +5601,10 @@
         <v>0.73</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.3307</v>
+        <v>-0.3159</v>
       </c>
       <c r="J79" t="n">
-        <v>-9.920999999999999</v>
+        <v>-9.477</v>
       </c>
     </row>
     <row r="80">
@@ -5641,10 +5641,10 @@
         <v>1.7</v>
       </c>
       <c r="I80" t="n">
-        <v>1.0961</v>
+        <v>1.0795</v>
       </c>
       <c r="J80" t="n">
-        <v>32.883</v>
+        <v>32.385</v>
       </c>
     </row>
     <row r="81">
@@ -5681,10 +5681,10 @@
         <v>1.1</v>
       </c>
       <c r="I81" t="n">
-        <v>0.2368</v>
+        <v>0.1958</v>
       </c>
       <c r="J81" t="n">
-        <v>7.104</v>
+        <v>5.874</v>
       </c>
     </row>
     <row r="82">
@@ -5721,10 +5721,10 @@
         <v>1.09</v>
       </c>
       <c r="I82" t="n">
-        <v>0.1783</v>
+        <v>0.162</v>
       </c>
       <c r="J82" t="n">
-        <v>4.6358</v>
+        <v>4.212</v>
       </c>
     </row>
     <row r="83">
@@ -5761,10 +5761,10 @@
         <v>1.06</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1299</v>
+        <v>0.1144</v>
       </c>
       <c r="J83" t="n">
-        <v>3.3774</v>
+        <v>2.9744</v>
       </c>
     </row>
     <row r="84">
@@ -5801,10 +5801,10 @@
         <v>0.96</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.07489999999999999</v>
+        <v>-0.06</v>
       </c>
       <c r="J84" t="n">
-        <v>-1.9474</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="85">
@@ -5841,10 +5841,10 @@
         <v>1.17</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2939</v>
+        <v>0.2815</v>
       </c>
       <c r="J85" t="n">
-        <v>7.6414</v>
+        <v>7.319</v>
       </c>
     </row>
     <row r="86">
@@ -5881,10 +5881,10 @@
         <v>0.88</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.1721</v>
+        <v>-0.1516</v>
       </c>
       <c r="J86" t="n">
-        <v>-4.4746</v>
+        <v>-3.9416</v>
       </c>
     </row>
     <row r="87">
@@ -5921,10 +5921,10 @@
         <v>0.95</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.0769</v>
       </c>
       <c r="J87" t="n">
-        <v>-2.4388</v>
+        <v>-1.9994</v>
       </c>
     </row>
     <row r="88">
@@ -5961,10 +5961,10 @@
         <v>0.83</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.2305</v>
+        <v>-0.2105</v>
       </c>
       <c r="J88" t="n">
-        <v>-5.993</v>
+        <v>-5.473</v>
       </c>
     </row>
     <row r="89">
@@ -6001,10 +6001,10 @@
         <v>0.63</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.4183</v>
+        <v>-0.4111</v>
       </c>
       <c r="J89" t="n">
-        <v>-10.8758</v>
+        <v>-10.6886</v>
       </c>
     </row>
     <row r="90">
@@ -6041,10 +6041,10 @@
         <v>1.67</v>
       </c>
       <c r="I90" t="n">
-        <v>0.8179</v>
+        <v>0.7513</v>
       </c>
       <c r="J90" t="n">
-        <v>21.2654</v>
+        <v>19.5338</v>
       </c>
     </row>
     <row r="91">
@@ -6081,10 +6081,10 @@
         <v>1.4</v>
       </c>
       <c r="I91" t="n">
-        <v>0.5377999999999999</v>
+        <v>0.4683</v>
       </c>
       <c r="J91" t="n">
-        <v>13.9828</v>
+        <v>12.1758</v>
       </c>
     </row>
     <row r="92">
@@ -6121,10 +6121,10 @@
         <v>1.22</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5679</v>
+        <v>0.5404</v>
       </c>
       <c r="J92" t="n">
-        <v>11.9259</v>
+        <v>11.3484</v>
       </c>
     </row>
     <row r="93">
@@ -6161,10 +6161,10 @@
         <v>1.22</v>
       </c>
       <c r="I93" t="n">
-        <v>0.5679</v>
+        <v>0.5404</v>
       </c>
       <c r="J93" t="n">
-        <v>11.9259</v>
+        <v>11.3484</v>
       </c>
     </row>
     <row r="94">
@@ -6201,10 +6201,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2933</v>
+        <v>-0.2587</v>
       </c>
       <c r="J94" t="n">
-        <v>-6.1593</v>
+        <v>-5.4327</v>
       </c>
     </row>
     <row r="95">
@@ -6241,10 +6241,10 @@
         <v>1.78</v>
       </c>
       <c r="I95" t="n">
-        <v>1.4347</v>
+        <v>1.4618</v>
       </c>
       <c r="J95" t="n">
-        <v>30.1287</v>
+        <v>30.6978</v>
       </c>
     </row>
     <row r="96">
@@ -6281,10 +6281,10 @@
         <v>1.62</v>
       </c>
       <c r="I96" t="n">
-        <v>1.2333</v>
+        <v>1.25</v>
       </c>
       <c r="J96" t="n">
-        <v>25.8993</v>
+        <v>26.25</v>
       </c>
     </row>
     <row r="97">
@@ -6321,10 +6321,10 @@
         <v>1.74</v>
       </c>
       <c r="I97" t="n">
-        <v>1.1141</v>
+        <v>1.0966</v>
       </c>
       <c r="J97" t="n">
-        <v>23.3961</v>
+        <v>23.0286</v>
       </c>
     </row>
     <row r="98">
@@ -6361,10 +6361,10 @@
         <v>1.47</v>
       </c>
       <c r="I98" t="n">
-        <v>0.7952</v>
+        <v>0.7393999999999999</v>
       </c>
       <c r="J98" t="n">
-        <v>16.6992</v>
+        <v>15.5274</v>
       </c>
     </row>
     <row r="99">
@@ -6401,10 +6401,10 @@
         <v>0.95</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1038</v>
+        <v>-0.0871</v>
       </c>
       <c r="J99" t="n">
-        <v>-2.1798</v>
+        <v>-1.8291</v>
       </c>
     </row>
     <row r="100">
@@ -6441,10 +6441,10 @@
         <v>1.3</v>
       </c>
       <c r="I100" t="n">
-        <v>0.5527</v>
+        <v>0.4957</v>
       </c>
       <c r="J100" t="n">
-        <v>11.6067</v>
+        <v>10.4097</v>
       </c>
     </row>
     <row r="101">
@@ -6481,10 +6481,10 @@
         <v>0.66</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4004</v>
+        <v>-0.393</v>
       </c>
       <c r="J101" t="n">
-        <v>-8.4084</v>
+        <v>-8.253</v>
       </c>
     </row>
     <row r="102">
@@ -6521,10 +6521,10 @@
         <v>1.65</v>
       </c>
       <c r="I102" t="n">
-        <v>1.2776</v>
+        <v>1.2958</v>
       </c>
       <c r="J102" t="n">
-        <v>28.1072</v>
+        <v>28.5076</v>
       </c>
     </row>
     <row r="103">
@@ -6561,10 +6561,10 @@
         <v>1.47</v>
       </c>
       <c r="I103" t="n">
-        <v>1.0397</v>
+        <v>1.046</v>
       </c>
       <c r="J103" t="n">
-        <v>22.8734</v>
+        <v>23.012</v>
       </c>
     </row>
     <row r="104">
@@ -6601,10 +6601,10 @@
         <v>1.21</v>
       </c>
       <c r="I104" t="n">
-        <v>0.5508999999999999</v>
+        <v>0.522</v>
       </c>
       <c r="J104" t="n">
-        <v>12.1198</v>
+        <v>11.484</v>
       </c>
     </row>
     <row r="105">
@@ -6641,10 +6641,10 @@
         <v>1.15</v>
       </c>
       <c r="I105" t="n">
-        <v>0.4146</v>
+        <v>0.3829</v>
       </c>
       <c r="J105" t="n">
-        <v>9.1212</v>
+        <v>8.4238</v>
       </c>
     </row>
     <row r="106">
@@ -6681,10 +6681,10 @@
         <v>1.14</v>
       </c>
       <c r="I106" t="n">
-        <v>0.3906</v>
+        <v>0.3587</v>
       </c>
       <c r="J106" t="n">
-        <v>8.5932</v>
+        <v>7.8914</v>
       </c>
     </row>
     <row r="107">
@@ -6721,10 +6721,10 @@
         <v>0.98</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.0203</v>
+        <v>-0.0128</v>
       </c>
       <c r="J107" t="n">
-        <v>-0.4466</v>
+        <v>-0.2816</v>
       </c>
     </row>
     <row r="108">
@@ -6761,10 +6761,10 @@
         <v>0.86</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.1738</v>
+        <v>-0.1575</v>
       </c>
       <c r="J108" t="n">
-        <v>-3.8236</v>
+        <v>-3.465</v>
       </c>
     </row>
     <row r="109">
@@ -6801,10 +6801,10 @@
         <v>0.77</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2622</v>
+        <v>-0.2447</v>
       </c>
       <c r="J109" t="n">
-        <v>-5.7684</v>
+        <v>-5.3834</v>
       </c>
     </row>
     <row r="110">
@@ -6841,10 +6841,10 @@
         <v>0.72</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3089</v>
+        <v>-0.2921</v>
       </c>
       <c r="J110" t="n">
-        <v>-6.7958</v>
+        <v>-6.4262</v>
       </c>
     </row>
     <row r="111">
@@ -6881,10 +6881,10 @@
         <v>0.66</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3638</v>
+        <v>-0.3497</v>
       </c>
       <c r="J111" t="n">
-        <v>-8.0036</v>
+        <v>-7.6934</v>
       </c>
     </row>
     <row r="112">
@@ -6921,10 +6921,10 @@
         <v>1.49</v>
       </c>
       <c r="I112" t="n">
-        <v>1.0692</v>
+        <v>1.0789</v>
       </c>
       <c r="J112" t="n">
-        <v>25.6608</v>
+        <v>25.8936</v>
       </c>
     </row>
     <row r="113">
@@ -6961,10 +6961,10 @@
         <v>1.46</v>
       </c>
       <c r="I113" t="n">
-        <v>1.0262</v>
+        <v>1.0302</v>
       </c>
       <c r="J113" t="n">
-        <v>24.6288</v>
+        <v>24.7248</v>
       </c>
     </row>
     <row r="114">
@@ -7001,10 +7001,10 @@
         <v>1.26</v>
       </c>
       <c r="I114" t="n">
-        <v>0.6577</v>
+        <v>0.6322</v>
       </c>
       <c r="J114" t="n">
-        <v>15.7848</v>
+        <v>15.1728</v>
       </c>
     </row>
     <row r="115">
@@ -7041,10 +7041,10 @@
         <v>1.22</v>
       </c>
       <c r="I115" t="n">
-        <v>0.5737</v>
+        <v>0.5453</v>
       </c>
       <c r="J115" t="n">
-        <v>13.7688</v>
+        <v>13.0872</v>
       </c>
     </row>
     <row r="116">
@@ -7081,10 +7081,10 @@
         <v>1.15</v>
       </c>
       <c r="I116" t="n">
-        <v>0.4158</v>
+        <v>0.3841</v>
       </c>
       <c r="J116" t="n">
-        <v>9.979200000000001</v>
+        <v>9.218400000000001</v>
       </c>
     </row>
     <row r="117">
@@ -7121,10 +7121,10 @@
         <v>1.16</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4517</v>
+        <v>0.41</v>
       </c>
       <c r="J117" t="n">
-        <v>10.8408</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="118">
@@ -7161,10 +7161,10 @@
         <v>0.91</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.1087</v>
+        <v>-0.0939</v>
       </c>
       <c r="J118" t="n">
-        <v>-2.6088</v>
+        <v>-2.2536</v>
       </c>
     </row>
     <row r="119">
@@ -7201,10 +7201,10 @@
         <v>0.77</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2585</v>
+        <v>-0.2427</v>
       </c>
       <c r="J119" t="n">
-        <v>-6.204</v>
+        <v>-5.8248</v>
       </c>
     </row>
     <row r="120">
@@ -7241,10 +7241,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.4473</v>
+        <v>-0.4399</v>
       </c>
       <c r="J120" t="n">
-        <v>-10.7352</v>
+        <v>-10.5576</v>
       </c>
     </row>
     <row r="121">
@@ -7281,10 +7281,10 @@
         <v>0.34</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.6373</v>
+        <v>-0.6575</v>
       </c>
       <c r="J121" t="n">
-        <v>-15.2952</v>
+        <v>-15.78</v>
       </c>
     </row>
     <row r="122">
@@ -7321,10 +7321,10 @@
         <v>1.28</v>
       </c>
       <c r="I122" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.4951</v>
       </c>
       <c r="J122" t="n">
-        <v>15.5372</v>
+        <v>13.8628</v>
       </c>
     </row>
     <row r="123">
@@ -7361,10 +7361,10 @@
         <v>1.14</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3202</v>
+        <v>0.2688</v>
       </c>
       <c r="J123" t="n">
-        <v>8.9656</v>
+        <v>7.5264</v>
       </c>
     </row>
     <row r="124">
@@ -7401,10 +7401,10 @@
         <v>1.09</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2262</v>
+        <v>0.1833</v>
       </c>
       <c r="J124" t="n">
-        <v>6.3336</v>
+        <v>5.1324</v>
       </c>
     </row>
     <row r="125">
@@ -7441,10 +7441,10 @@
         <v>1.04</v>
       </c>
       <c r="I125" t="n">
-        <v>0.1204</v>
+        <v>0.092</v>
       </c>
       <c r="J125" t="n">
-        <v>3.3712</v>
+        <v>2.576</v>
       </c>
     </row>
     <row r="126">
@@ -7481,10 +7481,10 @@
         <v>0.66</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3875</v>
+        <v>-0.3766</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.85</v>
+        <v>-10.5448</v>
       </c>
     </row>
     <row r="127">
@@ -7521,10 +7521,10 @@
         <v>1.3</v>
       </c>
       <c r="I127" t="n">
-        <v>0.7961</v>
+        <v>0.7695</v>
       </c>
       <c r="J127" t="n">
-        <v>22.2908</v>
+        <v>21.546</v>
       </c>
     </row>
     <row r="128">
@@ -7561,10 +7561,10 @@
         <v>1.05</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1943</v>
+        <v>0.162</v>
       </c>
       <c r="J128" t="n">
-        <v>5.4404</v>
+        <v>4.536</v>
       </c>
     </row>
     <row r="129">
@@ -7601,10 +7601,10 @@
         <v>1.02</v>
       </c>
       <c r="I129" t="n">
-        <v>0.0954</v>
+        <v>0.0746</v>
       </c>
       <c r="J129" t="n">
-        <v>2.6712</v>
+        <v>2.0888</v>
       </c>
     </row>
     <row r="130">
@@ -7641,10 +7641,10 @@
         <v>0.93</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2664</v>
+        <v>-0.2268</v>
       </c>
       <c r="J130" t="n">
-        <v>-7.4592</v>
+        <v>-6.3504</v>
       </c>
     </row>
     <row r="131">
@@ -7681,10 +7681,10 @@
         <v>0.88</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4013</v>
+        <v>-0.3582</v>
       </c>
       <c r="J131" t="n">
-        <v>-11.2364</v>
+        <v>-10.0296</v>
       </c>
     </row>
     <row r="132">
@@ -7721,10 +7721,10 @@
         <v>0.82</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.1977</v>
+        <v>-0.1823</v>
       </c>
       <c r="J132" t="n">
-        <v>-4.7448</v>
+        <v>-4.3752</v>
       </c>
     </row>
     <row r="133">
@@ -7761,10 +7761,10 @@
         <v>0.72</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.2976</v>
+        <v>-0.2844</v>
       </c>
       <c r="J133" t="n">
-        <v>-7.1424</v>
+        <v>-6.8256</v>
       </c>
     </row>
     <row r="134">
@@ -7801,10 +7801,10 @@
         <v>0.65</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.3591</v>
+        <v>-0.3469</v>
       </c>
       <c r="J134" t="n">
-        <v>-8.618399999999999</v>
+        <v>-8.3256</v>
       </c>
     </row>
     <row r="135">
@@ -7841,10 +7841,10 @@
         <v>0.65</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3591</v>
+        <v>-0.3469</v>
       </c>
       <c r="J135" t="n">
-        <v>-8.618399999999999</v>
+        <v>-8.3256</v>
       </c>
     </row>
     <row r="136">
@@ -7881,10 +7881,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4386</v>
+        <v>-0.4307</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.5264</v>
+        <v>-10.3368</v>
       </c>
     </row>
     <row r="137">
@@ -7921,10 +7921,10 @@
         <v>2.07</v>
       </c>
       <c r="I137" t="n">
-        <v>1.7583</v>
+        <v>1.8123</v>
       </c>
       <c r="J137" t="n">
-        <v>42.1992</v>
+        <v>43.4952</v>
       </c>
     </row>
     <row r="138">
@@ -7961,10 +7961,10 @@
         <v>1.46</v>
       </c>
       <c r="I138" t="n">
-        <v>1.0098</v>
+        <v>1.0173</v>
       </c>
       <c r="J138" t="n">
-        <v>24.2352</v>
+        <v>24.4152</v>
       </c>
     </row>
     <row r="139">
@@ -8001,10 +8001,10 @@
         <v>1.38</v>
       </c>
       <c r="I139" t="n">
-        <v>0.8741</v>
+        <v>0.8666</v>
       </c>
       <c r="J139" t="n">
-        <v>20.9784</v>
+        <v>20.7984</v>
       </c>
     </row>
     <row r="140">
@@ -8041,10 +8041,10 @@
         <v>1.38</v>
       </c>
       <c r="I140" t="n">
-        <v>0.8741</v>
+        <v>0.8666</v>
       </c>
       <c r="J140" t="n">
-        <v>20.9784</v>
+        <v>20.7984</v>
       </c>
     </row>
     <row r="141">
@@ -8081,10 +8081,10 @@
         <v>1</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.07439999999999999</v>
+        <v>-0.0735</v>
       </c>
       <c r="J141" t="n">
-        <v>-1.7856</v>
+        <v>-1.764</v>
       </c>
     </row>
     <row r="142">
@@ -8121,10 +8121,10 @@
         <v>1.04</v>
       </c>
       <c r="I142" t="n">
-        <v>0.1529</v>
+        <v>0.1274</v>
       </c>
       <c r="J142" t="n">
-        <v>4.587</v>
+        <v>3.822</v>
       </c>
     </row>
     <row r="143">
@@ -8161,10 +8161,10 @@
         <v>1</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.0178</v>
+        <v>-0.013</v>
       </c>
       <c r="J143" t="n">
-        <v>-0.534</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="144">
@@ -8201,10 +8201,10 @@
         <v>0.78</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.6554</v>
+        <v>-0.6213</v>
       </c>
       <c r="J144" t="n">
-        <v>-19.662</v>
+        <v>-18.639</v>
       </c>
     </row>
     <row r="145">
@@ -8241,10 +8241,10 @@
         <v>1.52</v>
       </c>
       <c r="I145" t="n">
-        <v>1.1537</v>
+        <v>1.1684</v>
       </c>
       <c r="J145" t="n">
-        <v>34.611</v>
+        <v>35.052</v>
       </c>
     </row>
     <row r="146">
@@ -8281,10 +8281,10 @@
         <v>1.22</v>
       </c>
       <c r="I146" t="n">
-        <v>0.6027</v>
+        <v>0.5656</v>
       </c>
       <c r="J146" t="n">
-        <v>18.081</v>
+        <v>16.968</v>
       </c>
     </row>
     <row r="147">
@@ -8321,10 +8321,10 @@
         <v>1.25</v>
       </c>
       <c r="I147" t="n">
-        <v>0.4816</v>
+        <v>0.4256</v>
       </c>
       <c r="J147" t="n">
-        <v>14.448</v>
+        <v>12.768</v>
       </c>
     </row>
     <row r="148">
@@ -8361,10 +8361,10 @@
         <v>1.24</v>
       </c>
       <c r="I148" t="n">
-        <v>0.4662</v>
+        <v>0.4107</v>
       </c>
       <c r="J148" t="n">
-        <v>13.986</v>
+        <v>12.321</v>
       </c>
     </row>
     <row r="149">
@@ -8401,10 +8401,10 @@
         <v>1.23</v>
       </c>
       <c r="I149" t="n">
-        <v>0.4506</v>
+        <v>0.3959</v>
       </c>
       <c r="J149" t="n">
-        <v>13.518</v>
+        <v>11.877</v>
       </c>
     </row>
     <row r="150">
@@ -8441,10 +8441,10 @@
         <v>1.13</v>
       </c>
       <c r="I150" t="n">
-        <v>0.2862</v>
+        <v>0.2422</v>
       </c>
       <c r="J150" t="n">
-        <v>8.586</v>
+        <v>7.266</v>
       </c>
     </row>
     <row r="151">
@@ -8481,10 +8481,10 @@
         <v>1.09</v>
       </c>
       <c r="I151" t="n">
-        <v>0.211</v>
+        <v>0.174</v>
       </c>
       <c r="J151" t="n">
-        <v>6.33</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="152">
@@ -8521,10 +8521,10 @@
         <v>0.95</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.2238</v>
+        <v>-0.1868</v>
       </c>
       <c r="J152" t="n">
-        <v>-6.0426</v>
+        <v>-5.0436</v>
       </c>
     </row>
     <row r="153">
@@ -8561,10 +8561,10 @@
         <v>0.88</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.4189</v>
+        <v>-0.3765</v>
       </c>
       <c r="J153" t="n">
-        <v>-11.3103</v>
+        <v>-10.1655</v>
       </c>
     </row>
     <row r="154">
@@ -8601,10 +8601,10 @@
         <v>0.85</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.4939</v>
+        <v>-0.4527</v>
       </c>
       <c r="J154" t="n">
-        <v>-13.3353</v>
+        <v>-12.2229</v>
       </c>
     </row>
     <row r="155">
@@ -8641,10 +8641,10 @@
         <v>1.61</v>
       </c>
       <c r="I155" t="n">
-        <v>1.2733</v>
+        <v>1.2943</v>
       </c>
       <c r="J155" t="n">
-        <v>34.3791</v>
+        <v>34.9461</v>
       </c>
     </row>
     <row r="156">
@@ -8681,10 +8681,10 @@
         <v>1.34</v>
       </c>
       <c r="I156" t="n">
-        <v>0.8512</v>
+        <v>0.8288</v>
       </c>
       <c r="J156" t="n">
-        <v>22.9824</v>
+        <v>22.3776</v>
       </c>
     </row>
     <row r="157">
@@ -8721,10 +8721,10 @@
         <v>0.89</v>
       </c>
       <c r="I157" t="n">
-        <v>-0.1536</v>
+        <v>-0.1344</v>
       </c>
       <c r="J157" t="n">
-        <v>-4.1472</v>
+        <v>-3.6288</v>
       </c>
     </row>
     <row r="158">
@@ -8761,10 +8761,10 @@
         <v>0.8</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.2474</v>
+        <v>-0.2274</v>
       </c>
       <c r="J158" t="n">
-        <v>-6.6798</v>
+        <v>-6.1398</v>
       </c>
     </row>
     <row r="159">
@@ -8801,10 +8801,10 @@
         <v>0.72</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.3242</v>
+        <v>-0.3074</v>
       </c>
       <c r="J159" t="n">
-        <v>-8.753399999999999</v>
+        <v>-8.299799999999999</v>
       </c>
     </row>
     <row r="160">
@@ -8841,10 +8841,10 @@
         <v>1.27</v>
       </c>
       <c r="I160" t="n">
-        <v>0.5653</v>
+        <v>0.5078</v>
       </c>
       <c r="J160" t="n">
-        <v>15.2631</v>
+        <v>13.7106</v>
       </c>
     </row>
     <row r="161">
@@ -8881,10 +8881,10 @@
         <v>1.05</v>
       </c>
       <c r="I161" t="n">
-        <v>0.1571</v>
+        <v>0.121</v>
       </c>
       <c r="J161" t="n">
-        <v>4.2417</v>
+        <v>3.267</v>
       </c>
     </row>
     <row r="162">
@@ -8921,10 +8921,10 @@
         <v>1</v>
       </c>
       <c r="I162" t="n">
-        <v>0.0036</v>
+        <v>0.0022</v>
       </c>
       <c r="J162" t="n">
-        <v>0.108</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="163">
@@ -8961,10 +8961,10 @@
         <v>0.99</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.0229</v>
+        <v>-0.0169</v>
       </c>
       <c r="J163" t="n">
-        <v>-0.6870000000000001</v>
+        <v>-0.507</v>
       </c>
     </row>
     <row r="164">
@@ -9001,10 +9001,10 @@
         <v>0.96</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.0701</v>
+        <v>-0.0569</v>
       </c>
       <c r="J164" t="n">
-        <v>-2.103</v>
+        <v>-1.707</v>
       </c>
     </row>
     <row r="165">
@@ -9041,10 +9041,10 @@
         <v>0.92</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1203</v>
+        <v>-0.1026</v>
       </c>
       <c r="J165" t="n">
-        <v>-3.609</v>
+        <v>-3.078</v>
       </c>
     </row>
     <row r="166">
@@ -9081,10 +9081,10 @@
         <v>0.92</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.1203</v>
+        <v>-0.1026</v>
       </c>
       <c r="J166" t="n">
-        <v>-3.609</v>
+        <v>-3.078</v>
       </c>
     </row>
     <row r="167">
@@ -9121,10 +9121,10 @@
         <v>1.44</v>
       </c>
       <c r="I167" t="n">
-        <v>0.5923</v>
+        <v>0.5229</v>
       </c>
       <c r="J167" t="n">
-        <v>17.769</v>
+        <v>15.687</v>
       </c>
     </row>
     <row r="168">
@@ -9161,10 +9161,10 @@
         <v>1.03</v>
       </c>
       <c r="I168" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.0507</v>
       </c>
       <c r="J168" t="n">
-        <v>2.145</v>
+        <v>1.521</v>
       </c>
     </row>
     <row r="169">
@@ -9201,10 +9201,10 @@
         <v>1.02</v>
       </c>
       <c r="I169" t="n">
-        <v>0.0519</v>
+        <v>0.0358</v>
       </c>
       <c r="J169" t="n">
-        <v>1.557</v>
+        <v>1.074</v>
       </c>
     </row>
     <row r="170">
@@ -9241,10 +9241,10 @@
         <v>0.95</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.08939999999999999</v>
+        <v>-0.073</v>
       </c>
       <c r="J170" t="n">
-        <v>-2.682</v>
+        <v>-2.19</v>
       </c>
     </row>
     <row r="171">
@@ -9281,10 +9281,10 @@
         <v>0.77</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2855</v>
+        <v>-0.2671</v>
       </c>
       <c r="J171" t="n">
-        <v>-8.565</v>
+        <v>-8.013</v>
       </c>
     </row>
     <row r="172">
@@ -9321,10 +9321,10 @@
         <v>1.48</v>
       </c>
       <c r="I172" t="n">
-        <v>1.0728</v>
+        <v>1.0814</v>
       </c>
       <c r="J172" t="n">
-        <v>25.7472</v>
+        <v>25.9536</v>
       </c>
     </row>
     <row r="173">
@@ -9361,10 +9361,10 @@
         <v>1.34</v>
       </c>
       <c r="I173" t="n">
-        <v>0.8293</v>
+        <v>0.8075</v>
       </c>
       <c r="J173" t="n">
-        <v>19.9032</v>
+        <v>19.38</v>
       </c>
     </row>
     <row r="174">
@@ -9401,10 +9401,10 @@
         <v>1.19</v>
       </c>
       <c r="I174" t="n">
-        <v>0.5219</v>
+        <v>0.4884</v>
       </c>
       <c r="J174" t="n">
-        <v>12.5256</v>
+        <v>11.7216</v>
       </c>
     </row>
     <row r="175">
@@ -9441,10 +9441,10 @@
         <v>1.1</v>
       </c>
       <c r="I175" t="n">
-        <v>0.3073</v>
+        <v>0.275</v>
       </c>
       <c r="J175" t="n">
-        <v>7.3752</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="176">
@@ -9481,10 +9481,10 @@
         <v>0.98</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.138</v>
+        <v>-0.111</v>
       </c>
       <c r="J176" t="n">
-        <v>-3.312</v>
+        <v>-2.664</v>
       </c>
     </row>
     <row r="177">
@@ -9521,10 +9521,10 @@
         <v>1.03</v>
       </c>
       <c r="I177" t="n">
-        <v>0.1147</v>
+        <v>0.0851</v>
       </c>
       <c r="J177" t="n">
-        <v>2.7528</v>
+        <v>2.0424</v>
       </c>
     </row>
     <row r="178">
@@ -9561,10 +9561,10 @@
         <v>0.99</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.0188</v>
+        <v>-0.0138</v>
       </c>
       <c r="J178" t="n">
-        <v>-0.4512</v>
+        <v>-0.3312</v>
       </c>
     </row>
     <row r="179">
@@ -9601,10 +9601,10 @@
         <v>0.86</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1832</v>
+        <v>-0.1636</v>
       </c>
       <c r="J179" t="n">
-        <v>-4.3968</v>
+        <v>-3.9264</v>
       </c>
     </row>
     <row r="180">
@@ -9641,10 +9641,10 @@
         <v>0.85</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1937</v>
+        <v>-0.1739</v>
       </c>
       <c r="J180" t="n">
-        <v>-4.6488</v>
+        <v>-4.1736</v>
       </c>
     </row>
     <row r="181">
@@ -9681,10 +9681,10 @@
         <v>0.84</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.204</v>
+        <v>-0.1841</v>
       </c>
       <c r="J181" t="n">
-        <v>-4.896</v>
+        <v>-4.4184</v>
       </c>
     </row>
     <row r="182">
@@ -9721,10 +9721,10 @@
         <v>1.57</v>
       </c>
       <c r="I182" t="n">
-        <v>1.2183</v>
+        <v>1.2358</v>
       </c>
       <c r="J182" t="n">
-        <v>36.549</v>
+        <v>37.074</v>
       </c>
     </row>
     <row r="183">
@@ -9761,10 +9761,10 @@
         <v>1.16</v>
       </c>
       <c r="I183" t="n">
-        <v>0.4649</v>
+        <v>0.4264</v>
       </c>
       <c r="J183" t="n">
-        <v>13.947</v>
+        <v>12.792</v>
       </c>
     </row>
     <row r="184">
@@ -9801,10 +9801,10 @@
         <v>1.06</v>
       </c>
       <c r="I184" t="n">
-        <v>0.2118</v>
+        <v>0.1819</v>
       </c>
       <c r="J184" t="n">
-        <v>6.354</v>
+        <v>5.457</v>
       </c>
     </row>
     <row r="185">
@@ -9841,10 +9841,10 @@
         <v>0.98</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1219</v>
+        <v>-0.0948</v>
       </c>
       <c r="J185" t="n">
-        <v>-3.657</v>
+        <v>-2.844</v>
       </c>
     </row>
     <row r="186">
@@ -9881,10 +9881,10 @@
         <v>0.87</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4447</v>
+        <v>-0.4026</v>
       </c>
       <c r="J186" t="n">
-        <v>-13.341</v>
+        <v>-12.078</v>
       </c>
     </row>
     <row r="187">
@@ -9921,10 +9921,10 @@
         <v>1.05</v>
       </c>
       <c r="I187" t="n">
-        <v>0.1552</v>
+        <v>0.1194</v>
       </c>
       <c r="J187" t="n">
-        <v>4.656</v>
+        <v>3.582</v>
       </c>
     </row>
     <row r="188">
@@ -9961,10 +9961,10 @@
         <v>1.01</v>
       </c>
       <c r="I188" t="n">
-        <v>0.049</v>
+        <v>0.0328</v>
       </c>
       <c r="J188" t="n">
-        <v>1.47</v>
+        <v>0.984</v>
       </c>
     </row>
     <row r="189">
@@ -10001,10 +10001,10 @@
         <v>0.97</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.0558</v>
+        <v>-0.0445</v>
       </c>
       <c r="J189" t="n">
-        <v>-1.674</v>
+        <v>-1.335</v>
       </c>
     </row>
     <row r="190">
@@ -10041,10 +10041,10 @@
         <v>0.95</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="J190" t="n">
-        <v>-2.493</v>
+        <v>-2.058</v>
       </c>
     </row>
     <row r="191">
@@ -10081,10 +10081,10 @@
         <v>0.8</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2483</v>
+        <v>-0.2284</v>
       </c>
       <c r="J191" t="n">
-        <v>-7.449</v>
+        <v>-6.852</v>
       </c>
     </row>
     <row r="192">
@@ -10121,10 +10121,10 @@
         <v>1.02</v>
       </c>
       <c r="I192" t="n">
-        <v>0.0556</v>
+        <v>0.0375</v>
       </c>
       <c r="J192" t="n">
-        <v>2.0016</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="193">
@@ -10161,10 +10161,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.09810000000000001</v>
+        <v>-0.0815</v>
       </c>
       <c r="J193" t="n">
-        <v>-3.5316</v>
+        <v>-2.934</v>
       </c>
     </row>
     <row r="194">
@@ -10201,10 +10201,10 @@
         <v>0.72</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.3281</v>
+        <v>-0.3118</v>
       </c>
       <c r="J194" t="n">
-        <v>-11.8116</v>
+        <v>-11.2248</v>
       </c>
     </row>
     <row r="195">
@@ -10241,10 +10241,10 @@
         <v>1.16</v>
       </c>
       <c r="I195" t="n">
-        <v>0.2725</v>
+        <v>0.2193</v>
       </c>
       <c r="J195" t="n">
-        <v>9.81</v>
+        <v>7.8948</v>
       </c>
     </row>
     <row r="196">
@@ -10281,10 +10281,10 @@
         <v>1.1</v>
       </c>
       <c r="I196" t="n">
-        <v>0.1893</v>
+        <v>0.1461</v>
       </c>
       <c r="J196" t="n">
-        <v>6.8148</v>
+        <v>5.2596</v>
       </c>
     </row>
     <row r="197">
@@ -10321,10 +10321,10 @@
         <v>1.42</v>
       </c>
       <c r="I197" t="n">
-        <v>0.5573</v>
+        <v>0.5768</v>
       </c>
       <c r="J197" t="n">
-        <v>20.0628</v>
+        <v>20.7648</v>
       </c>
     </row>
     <row r="198">
@@ -10361,10 +10361,10 @@
         <v>1.39</v>
       </c>
       <c r="I198" t="n">
-        <v>0.525</v>
+        <v>0.5405</v>
       </c>
       <c r="J198" t="n">
-        <v>18.9</v>
+        <v>19.458</v>
       </c>
     </row>
     <row r="199">
@@ -10401,10 +10401,10 @@
         <v>1.31</v>
       </c>
       <c r="I199" t="n">
-        <v>0.4376</v>
+        <v>0.4439</v>
       </c>
       <c r="J199" t="n">
-        <v>15.7536</v>
+        <v>15.9804</v>
       </c>
     </row>
     <row r="200">
@@ -10441,10 +10441,10 @@
         <v>1.29</v>
       </c>
       <c r="I200" t="n">
-        <v>0.4151</v>
+        <v>0.4193</v>
       </c>
       <c r="J200" t="n">
-        <v>14.9436</v>
+        <v>15.0948</v>
       </c>
     </row>
     <row r="201">
@@ -10481,10 +10481,10 @@
         <v>1.18</v>
       </c>
       <c r="I201" t="n">
-        <v>0.2805</v>
+        <v>0.2742</v>
       </c>
       <c r="J201" t="n">
-        <v>10.098</v>
+        <v>9.8712</v>
       </c>
     </row>
     <row r="202">
@@ -10521,10 +10521,10 @@
         <v>1.28</v>
       </c>
       <c r="I202" t="n">
-        <v>0.5455</v>
+        <v>0.4858</v>
       </c>
       <c r="J202" t="n">
-        <v>13.092</v>
+        <v>11.6592</v>
       </c>
     </row>
     <row r="203">
@@ -10561,10 +10561,10 @@
         <v>1.26</v>
       </c>
       <c r="I203" t="n">
-        <v>0.514</v>
+        <v>0.4548</v>
       </c>
       <c r="J203" t="n">
-        <v>12.336</v>
+        <v>10.9152</v>
       </c>
     </row>
     <row r="204">
@@ -10601,10 +10601,10 @@
         <v>0.84</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2192</v>
+        <v>-0.1989</v>
       </c>
       <c r="J204" t="n">
-        <v>-5.2608</v>
+        <v>-4.7736</v>
       </c>
     </row>
     <row r="205">
@@ -10641,10 +10641,10 @@
         <v>1.09</v>
       </c>
       <c r="I205" t="n">
-        <v>0.2216</v>
+        <v>0.1807</v>
       </c>
       <c r="J205" t="n">
-        <v>5.3184</v>
+        <v>4.3368</v>
       </c>
     </row>
     <row r="206">
@@ -10681,10 +10681,10 @@
         <v>0.95</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.09279999999999999</v>
+        <v>-0.076</v>
       </c>
       <c r="J206" t="n">
-        <v>-2.2272</v>
+        <v>-1.824</v>
       </c>
     </row>
     <row r="207">
@@ -10721,10 +10721,10 @@
         <v>0.83</v>
       </c>
       <c r="I207" t="n">
-        <v>-0.5021</v>
+        <v>-0.4609</v>
       </c>
       <c r="J207" t="n">
-        <v>-12.0504</v>
+        <v>-11.0616</v>
       </c>
     </row>
     <row r="208">
@@ -10761,10 +10761,10 @@
         <v>0.5</v>
       </c>
       <c r="I208" t="n">
-        <v>-1.2045</v>
+        <v>-1.2274</v>
       </c>
       <c r="J208" t="n">
-        <v>-28.908</v>
+        <v>-29.4576</v>
       </c>
     </row>
     <row r="209">
@@ -10801,10 +10801,10 @@
         <v>0.36</v>
       </c>
       <c r="I209" t="n">
-        <v>-1.4761</v>
+        <v>-1.5478</v>
       </c>
       <c r="J209" t="n">
-        <v>-35.4264</v>
+        <v>-37.1472</v>
       </c>
     </row>
     <row r="210">
@@ -10841,10 +10841,10 @@
         <v>1.49</v>
       </c>
       <c r="I210" t="n">
-        <v>1.1754</v>
+        <v>1.2024</v>
       </c>
       <c r="J210" t="n">
-        <v>28.2096</v>
+        <v>28.8576</v>
       </c>
     </row>
     <row r="211">
@@ -10881,10 +10881,10 @@
         <v>1.47</v>
       </c>
       <c r="I211" t="n">
-        <v>1.1456</v>
+        <v>1.1704</v>
       </c>
       <c r="J211" t="n">
-        <v>27.4944</v>
+        <v>28.0896</v>
       </c>
     </row>
     <row r="212">
@@ -10921,10 +10921,10 @@
         <v>1.53</v>
       </c>
       <c r="I212" t="n">
-        <v>0.8959</v>
+        <v>0.8451</v>
       </c>
       <c r="J212" t="n">
-        <v>24.1893</v>
+        <v>22.8177</v>
       </c>
     </row>
     <row r="213">
@@ -10961,10 +10961,10 @@
         <v>1.07</v>
       </c>
       <c r="I213" t="n">
-        <v>0.1757</v>
+        <v>0.142</v>
       </c>
       <c r="J213" t="n">
-        <v>4.7439</v>
+        <v>3.834</v>
       </c>
     </row>
     <row r="214">
@@ -11001,10 +11001,10 @@
         <v>0.83</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.2344</v>
+        <v>-0.2148</v>
       </c>
       <c r="J214" t="n">
-        <v>-6.3288</v>
+        <v>-5.7996</v>
       </c>
     </row>
     <row r="215">
@@ -11041,10 +11041,10 @@
         <v>1.15</v>
       </c>
       <c r="I215" t="n">
-        <v>0.3248</v>
+        <v>0.2763</v>
       </c>
       <c r="J215" t="n">
-        <v>8.769600000000001</v>
+        <v>7.4601</v>
       </c>
     </row>
     <row r="216">
@@ -11081,10 +11081,10 @@
         <v>1.14</v>
       </c>
       <c r="I216" t="n">
-        <v>0.3079</v>
+        <v>0.2607</v>
       </c>
       <c r="J216" t="n">
-        <v>8.3133</v>
+        <v>7.0389</v>
       </c>
     </row>
     <row r="217">
@@ -11121,10 +11121,10 @@
         <v>1.14</v>
       </c>
       <c r="I217" t="n">
-        <v>0.4182</v>
+        <v>0.3803</v>
       </c>
       <c r="J217" t="n">
-        <v>11.2914</v>
+        <v>10.2681</v>
       </c>
     </row>
     <row r="218">
@@ -11161,10 +11161,10 @@
         <v>0.88</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.4197</v>
+        <v>-0.3773</v>
       </c>
       <c r="J218" t="n">
-        <v>-11.3319</v>
+        <v>-10.1871</v>
       </c>
     </row>
     <row r="219">
@@ -11201,10 +11201,10 @@
         <v>0.77</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.6812</v>
+        <v>-0.6492</v>
       </c>
       <c r="J219" t="n">
-        <v>-18.3924</v>
+        <v>-17.5284</v>
       </c>
     </row>
     <row r="220">
@@ -11241,10 +11241,10 @@
         <v>1.5</v>
       </c>
       <c r="I220" t="n">
-        <v>1.1209</v>
+        <v>1.1338</v>
       </c>
       <c r="J220" t="n">
-        <v>30.2643</v>
+        <v>30.6126</v>
       </c>
     </row>
     <row r="221">
@@ -11281,10 +11281,10 @@
         <v>1.36</v>
       </c>
       <c r="I221" t="n">
-        <v>0.8902</v>
+        <v>0.8712</v>
       </c>
       <c r="J221" t="n">
-        <v>24.0354</v>
+        <v>23.5224</v>
       </c>
     </row>
     <row r="222">
@@ -11321,10 +11321,10 @@
         <v>1.03</v>
       </c>
       <c r="I222" t="n">
-        <v>0.0968</v>
+        <v>0.082</v>
       </c>
       <c r="J222" t="n">
-        <v>2.42</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="223">
@@ -11361,10 +11361,10 @@
         <v>1.02</v>
       </c>
       <c r="I223" t="n">
-        <v>0.0752</v>
+        <v>0.062</v>
       </c>
       <c r="J223" t="n">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="224">
@@ -11401,10 +11401,10 @@
         <v>0.83</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.2108</v>
+        <v>-0.1915</v>
       </c>
       <c r="J224" t="n">
-        <v>-5.27</v>
+        <v>-4.7875</v>
       </c>
     </row>
     <row r="225">
@@ -11441,10 +11441,10 @@
         <v>0.77</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2698</v>
+        <v>-0.2509</v>
       </c>
       <c r="J225" t="n">
-        <v>-6.745</v>
+        <v>-6.2725</v>
       </c>
     </row>
     <row r="226">
@@ -11481,10 +11481,10 @@
         <v>0.73</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3078</v>
+        <v>-0.2902</v>
       </c>
       <c r="J226" t="n">
-        <v>-7.695</v>
+        <v>-7.255</v>
       </c>
     </row>
     <row r="227">
@@ -11521,10 +11521,10 @@
         <v>1.66</v>
       </c>
       <c r="I227" t="n">
-        <v>0.7741</v>
+        <v>0.7025</v>
       </c>
       <c r="J227" t="n">
-        <v>19.3525</v>
+        <v>17.5625</v>
       </c>
     </row>
     <row r="228">
@@ -11561,10 +11561,10 @@
         <v>1.3</v>
       </c>
       <c r="I228" t="n">
-        <v>0.408</v>
+        <v>0.3468</v>
       </c>
       <c r="J228" t="n">
-        <v>10.2</v>
+        <v>8.67</v>
       </c>
     </row>
     <row r="229">
@@ -11601,10 +11601,10 @@
         <v>1.3</v>
       </c>
       <c r="I229" t="n">
-        <v>0.408</v>
+        <v>0.3468</v>
       </c>
       <c r="J229" t="n">
-        <v>10.2</v>
+        <v>8.67</v>
       </c>
     </row>
     <row r="230">
@@ -11641,10 +11641,10 @@
         <v>1.19</v>
       </c>
       <c r="I230" t="n">
-        <v>0.2835</v>
+        <v>0.234</v>
       </c>
       <c r="J230" t="n">
-        <v>7.0875</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="231">
@@ -11681,10 +11681,10 @@
         <v>0.83</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.2426</v>
+        <v>-0.2245</v>
       </c>
       <c r="J231" t="n">
-        <v>-6.065</v>
+        <v>-5.6125</v>
       </c>
     </row>
     <row r="232">
@@ -11721,10 +11721,10 @@
         <v>1.26</v>
       </c>
       <c r="I232" t="n">
-        <v>0.7000999999999999</v>
+        <v>0.6665</v>
       </c>
       <c r="J232" t="n">
-        <v>21.003</v>
+        <v>19.995</v>
       </c>
     </row>
     <row r="233">
@@ -11761,10 +11761,10 @@
         <v>1.24</v>
       </c>
       <c r="I233" t="n">
-        <v>0.6567</v>
+        <v>0.6208</v>
       </c>
       <c r="J233" t="n">
-        <v>19.701</v>
+        <v>18.624</v>
       </c>
     </row>
     <row r="234">
@@ -11801,10 +11801,10 @@
         <v>1.01</v>
       </c>
       <c r="I234" t="n">
-        <v>0.0492</v>
+        <v>0.037</v>
       </c>
       <c r="J234" t="n">
-        <v>1.476</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="235">
@@ -11841,10 +11841,10 @@
         <v>0.98</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1113</v>
+        <v>-0.0852</v>
       </c>
       <c r="J235" t="n">
-        <v>-3.339</v>
+        <v>-2.556</v>
       </c>
     </row>
     <row r="236">
@@ -11881,10 +11881,10 @@
         <v>0.86</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4585</v>
+        <v>-0.4158</v>
       </c>
       <c r="J236" t="n">
-        <v>-13.755</v>
+        <v>-12.474</v>
       </c>
     </row>
     <row r="237">
@@ -11921,10 +11921,10 @@
         <v>1.27</v>
       </c>
       <c r="I237" t="n">
-        <v>0.5454</v>
+        <v>0.4859</v>
       </c>
       <c r="J237" t="n">
-        <v>16.362</v>
+        <v>14.577</v>
       </c>
     </row>
     <row r="238">
@@ -11961,10 +11961,10 @@
         <v>1.07</v>
       </c>
       <c r="I238" t="n">
-        <v>0.1892</v>
+        <v>0.1499</v>
       </c>
       <c r="J238" t="n">
-        <v>5.676</v>
+        <v>4.497</v>
       </c>
     </row>
     <row r="239">
@@ -12001,10 +12001,10 @@
         <v>0.99</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.0262</v>
+        <v>-0.0186</v>
       </c>
       <c r="J239" t="n">
-        <v>-0.786</v>
+        <v>-0.5580000000000001</v>
       </c>
     </row>
     <row r="240">
@@ -12041,10 +12041,10 @@
         <v>0.95</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.0873</v>
+        <v>-0.0713</v>
       </c>
       <c r="J240" t="n">
-        <v>-2.619</v>
+        <v>-2.139</v>
       </c>
     </row>
     <row r="241">
@@ -12081,10 +12081,10 @@
         <v>0.8</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.2539</v>
+        <v>-0.2341</v>
       </c>
       <c r="J241" t="n">
-        <v>-7.617</v>
+        <v>-7.023</v>
       </c>
     </row>
     <row r="242">
@@ -12121,10 +12121,10 @@
         <v>1.67</v>
       </c>
       <c r="I242" t="n">
-        <v>1.3194</v>
+        <v>1.3401</v>
       </c>
       <c r="J242" t="n">
-        <v>29.0268</v>
+        <v>29.4822</v>
       </c>
     </row>
     <row r="243">
@@ -12161,10 +12161,10 @@
         <v>1.24</v>
       </c>
       <c r="I243" t="n">
-        <v>0.6243</v>
+        <v>0.5945</v>
       </c>
       <c r="J243" t="n">
-        <v>13.7346</v>
+        <v>13.079</v>
       </c>
     </row>
     <row r="244">
@@ -12201,10 +12201,10 @@
         <v>1.19</v>
       </c>
       <c r="I244" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.4856</v>
       </c>
       <c r="J244" t="n">
-        <v>11.3872</v>
+        <v>10.6832</v>
       </c>
     </row>
     <row r="245">
@@ -12241,10 +12241,10 @@
         <v>1.09</v>
       </c>
       <c r="I245" t="n">
-        <v>0.2756</v>
+        <v>0.2444</v>
       </c>
       <c r="J245" t="n">
-        <v>6.0632</v>
+        <v>5.3768</v>
       </c>
     </row>
     <row r="246">
@@ -12281,10 +12281,10 @@
         <v>1.06</v>
       </c>
       <c r="I246" t="n">
-        <v>0.1912</v>
+        <v>0.1635</v>
       </c>
       <c r="J246" t="n">
-        <v>4.2064</v>
+        <v>3.597</v>
       </c>
     </row>
     <row r="247">
@@ -12321,10 +12321,10 @@
         <v>1.39</v>
       </c>
       <c r="I247" t="n">
-        <v>0.7863</v>
+        <v>0.7443</v>
       </c>
       <c r="J247" t="n">
-        <v>17.2986</v>
+        <v>16.3746</v>
       </c>
     </row>
     <row r="248">
@@ -12361,10 +12361,10 @@
         <v>0.98</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.0318</v>
+        <v>-0.0244</v>
       </c>
       <c r="J248" t="n">
-        <v>-0.6996</v>
+        <v>-0.5368000000000001</v>
       </c>
     </row>
     <row r="249">
@@ -12401,10 +12401,10 @@
         <v>0.82</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.2205</v>
+        <v>-0.2012</v>
       </c>
       <c r="J249" t="n">
-        <v>-4.851</v>
+        <v>-4.4264</v>
       </c>
     </row>
     <row r="250">
@@ -12441,10 +12441,10 @@
         <v>0.68</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.3537</v>
+        <v>-0.3387</v>
       </c>
       <c r="J250" t="n">
-        <v>-7.7814</v>
+        <v>-7.4514</v>
       </c>
     </row>
     <row r="251">
@@ -12481,10 +12481,10 @@
         <v>0.49</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.5211</v>
+        <v>-0.524</v>
       </c>
       <c r="J251" t="n">
-        <v>-11.4642</v>
+        <v>-11.528</v>
       </c>
     </row>
     <row r="252">
@@ -12521,10 +12521,10 @@
         <v>1.12</v>
       </c>
       <c r="I252" t="n">
-        <v>0.2997</v>
+        <v>0.249</v>
       </c>
       <c r="J252" t="n">
-        <v>6.5934</v>
+        <v>5.478</v>
       </c>
     </row>
     <row r="253">
@@ -12561,10 +12561,10 @@
         <v>0.84</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.2081</v>
+        <v>-0.1876</v>
       </c>
       <c r="J253" t="n">
-        <v>-4.5782</v>
+        <v>-4.1272</v>
       </c>
     </row>
     <row r="254">
@@ -12601,10 +12601,10 @@
         <v>0.65</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.3893</v>
+        <v>-0.3777</v>
       </c>
       <c r="J254" t="n">
-        <v>-8.5646</v>
+        <v>-8.3094</v>
       </c>
     </row>
     <row r="255">
@@ -12641,10 +12641,10 @@
         <v>1.14</v>
       </c>
       <c r="I255" t="n">
-        <v>0.3373</v>
+        <v>0.2842</v>
       </c>
       <c r="J255" t="n">
-        <v>7.4206</v>
+        <v>6.2524</v>
       </c>
     </row>
     <row r="256">
@@ -12681,10 +12681,10 @@
         <v>1.04</v>
       </c>
       <c r="I256" t="n">
-        <v>0.1312</v>
+        <v>0.099</v>
       </c>
       <c r="J256" t="n">
-        <v>2.8864</v>
+        <v>2.178</v>
       </c>
     </row>
     <row r="257">
@@ -12721,10 +12721,10 @@
         <v>0.9</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.3352</v>
+        <v>-0.2944</v>
       </c>
       <c r="J257" t="n">
-        <v>-7.3744</v>
+        <v>-6.4768</v>
       </c>
     </row>
     <row r="258">
@@ -12761,10 +12761,10 @@
         <v>0.61</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.9903999999999999</v>
+        <v>-0.9843</v>
       </c>
       <c r="J258" t="n">
-        <v>-21.7888</v>
+        <v>-21.6546</v>
       </c>
     </row>
     <row r="259">
@@ -12801,10 +12801,10 @@
         <v>0.32</v>
       </c>
       <c r="I259" t="n">
-        <v>-1.5566</v>
+        <v>-1.6462</v>
       </c>
       <c r="J259" t="n">
-        <v>-34.2452</v>
+        <v>-36.2164</v>
       </c>
     </row>
     <row r="260">
@@ -12841,10 +12841,10 @@
         <v>1.7</v>
       </c>
       <c r="I260" t="n">
-        <v>1.4596</v>
+        <v>1.511</v>
       </c>
       <c r="J260" t="n">
-        <v>32.1112</v>
+        <v>33.242</v>
       </c>
     </row>
     <row r="261">
@@ -12881,10 +12881,10 @@
         <v>1.3</v>
       </c>
       <c r="I261" t="n">
-        <v>0.8228</v>
+        <v>0.8011</v>
       </c>
       <c r="J261" t="n">
-        <v>18.1016</v>
+        <v>17.6242</v>
       </c>
     </row>
     <row r="262">
@@ -12921,10 +12921,10 @@
         <v>1.17</v>
       </c>
       <c r="I262" t="n">
-        <v>0.3509</v>
+        <v>0.3034</v>
       </c>
       <c r="J262" t="n">
-        <v>10.527</v>
+        <v>9.102</v>
       </c>
     </row>
     <row r="263">
@@ -12961,10 +12961,10 @@
         <v>1.13</v>
       </c>
       <c r="I263" t="n">
-        <v>0.2812</v>
+        <v>0.2386</v>
       </c>
       <c r="J263" t="n">
-        <v>8.436</v>
+        <v>7.158</v>
       </c>
     </row>
     <row r="264">
@@ -13001,10 +13001,10 @@
         <v>0.87</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.199</v>
+        <v>-0.1797</v>
       </c>
       <c r="J264" t="n">
-        <v>-5.97</v>
+        <v>-5.391</v>
       </c>
     </row>
     <row r="265">
@@ -13041,10 +13041,10 @@
         <v>1.77</v>
       </c>
       <c r="I265" t="n">
-        <v>1.1408</v>
+        <v>1.1244</v>
       </c>
       <c r="J265" t="n">
-        <v>34.224</v>
+        <v>33.732</v>
       </c>
     </row>
     <row r="266">
@@ -13081,10 +13081,10 @@
         <v>1.22</v>
       </c>
       <c r="I266" t="n">
-        <v>0.4317</v>
+        <v>0.3795</v>
       </c>
       <c r="J266" t="n">
-        <v>12.951</v>
+        <v>11.385</v>
       </c>
     </row>
     <row r="267">
@@ -13121,10 +13121,10 @@
         <v>0.6</v>
       </c>
       <c r="I267" t="n">
-        <v>-0.9705</v>
+        <v>-0.9591</v>
       </c>
       <c r="J267" t="n">
-        <v>-29.115</v>
+        <v>-28.773</v>
       </c>
     </row>
     <row r="268">
@@ -13161,10 +13161,10 @@
         <v>0.6</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.9705</v>
+        <v>-0.9591</v>
       </c>
       <c r="J268" t="n">
-        <v>-29.115</v>
+        <v>-28.773</v>
       </c>
     </row>
     <row r="269">
@@ -13201,10 +13201,10 @@
         <v>0.36</v>
       </c>
       <c r="I269" t="n">
-        <v>-1.4526</v>
+        <v>-1.5148</v>
       </c>
       <c r="J269" t="n">
-        <v>-43.578</v>
+        <v>-45.444</v>
       </c>
     </row>
     <row r="270">
@@ -13241,10 +13241,10 @@
         <v>1.28</v>
       </c>
       <c r="I270" t="n">
-        <v>0.8749</v>
+        <v>0.8811</v>
       </c>
       <c r="J270" t="n">
-        <v>26.247</v>
+        <v>26.433</v>
       </c>
     </row>
     <row r="271">
@@ -13281,10 +13281,10 @@
         <v>1.12</v>
       </c>
       <c r="I271" t="n">
-        <v>0.477</v>
+        <v>0.4461</v>
       </c>
       <c r="J271" t="n">
-        <v>14.31</v>
+        <v>13.383</v>
       </c>
     </row>
     <row r="272">
@@ -13321,10 +13321,10 @@
         <v>0.8</v>
       </c>
       <c r="I272" t="n">
-        <v>-0.5866</v>
+        <v>-0.5472</v>
       </c>
       <c r="J272" t="n">
-        <v>-14.665</v>
+        <v>-13.68</v>
       </c>
     </row>
     <row r="273">
@@ -13361,10 +13361,10 @@
         <v>0.72</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.7652</v>
+        <v>-0.7368</v>
       </c>
       <c r="J273" t="n">
-        <v>-19.13</v>
+        <v>-18.42</v>
       </c>
     </row>
     <row r="274">
@@ -13401,10 +13401,10 @@
         <v>0.64</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.9346</v>
+        <v>-0.9227</v>
       </c>
       <c r="J274" t="n">
-        <v>-23.365</v>
+        <v>-23.0675</v>
       </c>
     </row>
     <row r="275">
@@ -13441,10 +13441,10 @@
         <v>1.55</v>
       </c>
       <c r="I275" t="n">
-        <v>1.235</v>
+        <v>1.2607</v>
       </c>
       <c r="J275" t="n">
-        <v>30.875</v>
+        <v>31.5175</v>
       </c>
     </row>
     <row r="276">
@@ -13481,10 +13481,10 @@
         <v>1.27</v>
       </c>
       <c r="I276" t="n">
-        <v>0.7458</v>
+        <v>0.716</v>
       </c>
       <c r="J276" t="n">
-        <v>18.645</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="277">
@@ -13521,10 +13521,10 @@
         <v>1.14</v>
       </c>
       <c r="I277" t="n">
-        <v>0.3301</v>
+        <v>0.2774</v>
       </c>
       <c r="J277" t="n">
-        <v>8.2525</v>
+        <v>6.935</v>
       </c>
     </row>
     <row r="278">
@@ -13561,10 +13561,10 @@
         <v>1</v>
       </c>
       <c r="I278" t="n">
-        <v>0.0007</v>
+        <v>0.0003</v>
       </c>
       <c r="J278" t="n">
-        <v>0.0175</v>
+        <v>0.0075</v>
       </c>
     </row>
     <row r="279">
@@ -13601,10 +13601,10 @@
         <v>0.97</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.0575</v>
+        <v>-0.0453</v>
       </c>
       <c r="J279" t="n">
-        <v>-1.4375</v>
+        <v>-1.1325</v>
       </c>
     </row>
     <row r="280">
@@ -13641,10 +13641,10 @@
         <v>0.96</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.0718</v>
+        <v>-0.0578</v>
       </c>
       <c r="J280" t="n">
-        <v>-1.795</v>
+        <v>-1.445</v>
       </c>
     </row>
     <row r="281">
@@ -13681,10 +13681,10 @@
         <v>0.88</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.1684</v>
+        <v>-0.1482</v>
       </c>
       <c r="J281" t="n">
-        <v>-4.21</v>
+        <v>-3.705</v>
       </c>
     </row>
     <row r="282">
@@ -13721,10 +13721,10 @@
         <v>0.98</v>
       </c>
       <c r="I282" t="n">
-        <v>-0.1149</v>
+        <v>-0.08840000000000001</v>
       </c>
       <c r="J282" t="n">
-        <v>-2.7576</v>
+        <v>-2.1216</v>
       </c>
     </row>
     <row r="283">
@@ -13761,10 +13761,10 @@
         <v>0.85</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.4871</v>
+        <v>-0.4451</v>
       </c>
       <c r="J283" t="n">
-        <v>-11.6904</v>
+        <v>-10.6824</v>
       </c>
     </row>
     <row r="284">
@@ -13801,10 +13801,10 @@
         <v>0.62</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.9928</v>
+        <v>-0.9906</v>
       </c>
       <c r="J284" t="n">
-        <v>-23.8272</v>
+        <v>-23.7744</v>
       </c>
     </row>
     <row r="285">
@@ -13841,10 +13841,10 @@
         <v>1.84</v>
       </c>
       <c r="I285" t="n">
-        <v>1.5911</v>
+        <v>1.6447</v>
       </c>
       <c r="J285" t="n">
-        <v>38.1864</v>
+        <v>39.4728</v>
       </c>
     </row>
     <row r="286">
@@ -13881,10 +13881,10 @@
         <v>1.16</v>
       </c>
       <c r="I286" t="n">
-        <v>0.4714</v>
+        <v>0.4311</v>
       </c>
       <c r="J286" t="n">
-        <v>11.3136</v>
+        <v>10.3464</v>
       </c>
     </row>
     <row r="287">
@@ -13921,10 +13921,10 @@
         <v>0.89</v>
       </c>
       <c r="I287" t="n">
-        <v>-0.1494</v>
+        <v>-0.1318</v>
       </c>
       <c r="J287" t="n">
-        <v>-3.5856</v>
+        <v>-3.1632</v>
       </c>
     </row>
     <row r="288">
@@ -13961,10 +13961,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.2315</v>
+        <v>-0.212</v>
       </c>
       <c r="J288" t="n">
-        <v>-5.556</v>
+        <v>-5.088</v>
       </c>
     </row>
     <row r="289">
@@ -14001,10 +14001,10 @@
         <v>0.52</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.4965</v>
+        <v>-0.4962</v>
       </c>
       <c r="J289" t="n">
-        <v>-11.916</v>
+        <v>-11.9088</v>
       </c>
     </row>
     <row r="290">
@@ -14041,10 +14041,10 @@
         <v>1.27</v>
       </c>
       <c r="I290" t="n">
-        <v>0.5872000000000001</v>
+        <v>0.5335</v>
       </c>
       <c r="J290" t="n">
-        <v>14.0928</v>
+        <v>12.804</v>
       </c>
     </row>
     <row r="291">
@@ -14081,10 +14081,10 @@
         <v>0.93</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.1033</v>
+        <v>-0.0886</v>
       </c>
       <c r="J291" t="n">
-        <v>-2.4792</v>
+        <v>-2.1264</v>
       </c>
     </row>
     <row r="292">
@@ -14121,10 +14121,10 @@
         <v>1.33</v>
       </c>
       <c r="I292" t="n">
-        <v>0.8381999999999999</v>
+        <v>0.8146</v>
       </c>
       <c r="J292" t="n">
-        <v>23.4696</v>
+        <v>22.8088</v>
       </c>
     </row>
     <row r="293">
@@ -14161,10 +14161,10 @@
         <v>1.26</v>
       </c>
       <c r="I293" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.6585</v>
       </c>
       <c r="J293" t="n">
-        <v>19.376</v>
+        <v>18.438</v>
       </c>
     </row>
     <row r="294">
@@ -14201,10 +14201,10 @@
         <v>1.13</v>
       </c>
       <c r="I294" t="n">
-        <v>0.3982</v>
+        <v>0.359</v>
       </c>
       <c r="J294" t="n">
-        <v>11.1496</v>
+        <v>10.052</v>
       </c>
     </row>
     <row r="295">
@@ -14241,10 +14241,10 @@
         <v>1.1</v>
       </c>
       <c r="I295" t="n">
-        <v>0.3243</v>
+        <v>0.2872</v>
       </c>
       <c r="J295" t="n">
-        <v>9.080399999999999</v>
+        <v>8.041600000000001</v>
       </c>
     </row>
     <row r="296">
@@ -14281,10 +14281,10 @@
         <v>0.68</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.8705000000000001</v>
+        <v>-0.8544</v>
       </c>
       <c r="J296" t="n">
-        <v>-24.374</v>
+        <v>-23.9232</v>
       </c>
     </row>
     <row r="297">
@@ -14321,10 +14321,10 @@
         <v>1.13</v>
       </c>
       <c r="I297" t="n">
-        <v>0.3164</v>
+        <v>0.2645</v>
       </c>
       <c r="J297" t="n">
-        <v>8.8592</v>
+        <v>7.406</v>
       </c>
     </row>
     <row r="298">
@@ -14361,10 +14361,10 @@
         <v>1.06</v>
       </c>
       <c r="I298" t="n">
-        <v>0.1755</v>
+        <v>0.1371</v>
       </c>
       <c r="J298" t="n">
-        <v>4.914</v>
+        <v>3.8388</v>
       </c>
     </row>
     <row r="299">
@@ -14401,10 +14401,10 @@
         <v>0.97</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.0565</v>
+        <v>-0.0448</v>
       </c>
       <c r="J299" t="n">
-        <v>-1.582</v>
+        <v>-1.2544</v>
       </c>
     </row>
     <row r="300">
@@ -14441,10 +14441,10 @@
         <v>0.92</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.121</v>
+        <v>-0.1031</v>
       </c>
       <c r="J300" t="n">
-        <v>-3.388</v>
+        <v>-2.8868</v>
       </c>
     </row>
     <row r="301">
@@ -14481,10 +14481,10 @@
         <v>0.76</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.2884</v>
+        <v>-0.2698</v>
       </c>
       <c r="J301" t="n">
-        <v>-8.075200000000001</v>
+        <v>-7.5544</v>
       </c>
     </row>
     <row r="302">
@@ -14521,10 +14521,10 @@
         <v>1.22</v>
       </c>
       <c r="I302" t="n">
-        <v>0.3636</v>
+        <v>0.3567</v>
       </c>
       <c r="J302" t="n">
-        <v>10.908</v>
+        <v>10.701</v>
       </c>
     </row>
     <row r="303">
@@ -14561,10 +14561,10 @@
         <v>1.12</v>
       </c>
       <c r="I303" t="n">
-        <v>0.2258</v>
+        <v>0.21</v>
       </c>
       <c r="J303" t="n">
-        <v>6.774</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="304">
@@ -14601,10 +14601,10 @@
         <v>0.99</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.026</v>
+        <v>-0.0186</v>
       </c>
       <c r="J304" t="n">
-        <v>-0.78</v>
+        <v>-0.5580000000000001</v>
       </c>
     </row>
     <row r="305">
@@ -14641,10 +14641,10 @@
         <v>0.89</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.1594</v>
+        <v>-0.1393</v>
       </c>
       <c r="J305" t="n">
-        <v>-4.782</v>
+        <v>-4.179</v>
       </c>
     </row>
     <row r="306">
@@ -14681,10 +14681,10 @@
         <v>0.85</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.2027</v>
+        <v>-0.1821</v>
       </c>
       <c r="J306" t="n">
-        <v>-6.081</v>
+        <v>-5.463</v>
       </c>
     </row>
     <row r="307">
@@ -14721,10 +14721,10 @@
         <v>1.44</v>
       </c>
       <c r="I307" t="n">
-        <v>0.5901</v>
+        <v>0.5204</v>
       </c>
       <c r="J307" t="n">
-        <v>17.703</v>
+        <v>15.612</v>
       </c>
     </row>
     <row r="308">
@@ -14761,10 +14761,10 @@
         <v>1.14</v>
       </c>
       <c r="I308" t="n">
-        <v>0.2367</v>
+        <v>0.1881</v>
       </c>
       <c r="J308" t="n">
-        <v>7.101</v>
+        <v>5.643</v>
       </c>
     </row>
     <row r="309">
@@ -14801,10 +14801,10 @@
         <v>1.13</v>
       </c>
       <c r="I309" t="n">
-        <v>0.2232</v>
+        <v>0.1763</v>
       </c>
       <c r="J309" t="n">
-        <v>6.696</v>
+        <v>5.289</v>
       </c>
     </row>
     <row r="310">
@@ -14841,10 +14841,10 @@
         <v>0.79</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.2669</v>
+        <v>-0.2477</v>
       </c>
       <c r="J310" t="n">
-        <v>-8.007</v>
+        <v>-7.431</v>
       </c>
     </row>
     <row r="311">
@@ -14881,10 +14881,10 @@
         <v>0.76</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.296</v>
+        <v>-0.2782</v>
       </c>
       <c r="J311" t="n">
-        <v>-8.880000000000001</v>
+        <v>-8.346</v>
       </c>
     </row>
     <row r="312">
@@ -14921,10 +14921,10 @@
         <v>1.43</v>
       </c>
       <c r="I312" t="n">
-        <v>0.9996</v>
+        <v>0.9966</v>
       </c>
       <c r="J312" t="n">
-        <v>25.9896</v>
+        <v>25.9116</v>
       </c>
     </row>
     <row r="313">
@@ -14961,10 +14961,10 @@
         <v>1.34</v>
       </c>
       <c r="I313" t="n">
-        <v>0.8318</v>
+        <v>0.8097</v>
       </c>
       <c r="J313" t="n">
-        <v>21.6268</v>
+        <v>21.0522</v>
       </c>
     </row>
     <row r="314">
@@ -15001,10 +15001,10 @@
         <v>1.22</v>
       </c>
       <c r="I314" t="n">
-        <v>0.5868</v>
+        <v>0.5538</v>
       </c>
       <c r="J314" t="n">
-        <v>15.2568</v>
+        <v>14.3988</v>
       </c>
     </row>
     <row r="315">
@@ -15041,10 +15041,10 @@
         <v>1.07</v>
       </c>
       <c r="I315" t="n">
-        <v>0.2277</v>
+        <v>0.1981</v>
       </c>
       <c r="J315" t="n">
-        <v>5.9202</v>
+        <v>5.1506</v>
       </c>
     </row>
     <row r="316">
@@ -15081,10 +15081,10 @@
         <v>0.97</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.1726</v>
+        <v>-0.1413</v>
       </c>
       <c r="J316" t="n">
-        <v>-4.4876</v>
+        <v>-3.6738</v>
       </c>
     </row>
     <row r="317">
@@ -15121,10 +15121,10 @@
         <v>1.39</v>
       </c>
       <c r="I317" t="n">
-        <v>0.7931</v>
+        <v>0.7533</v>
       </c>
       <c r="J317" t="n">
-        <v>20.6206</v>
+        <v>19.5858</v>
       </c>
     </row>
     <row r="318">
@@ -15161,10 +15161,10 @@
         <v>0.91</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.1247</v>
+        <v>-0.1091</v>
       </c>
       <c r="J318" t="n">
-        <v>-3.2422</v>
+        <v>-2.8366</v>
       </c>
     </row>
     <row r="319">
@@ -15201,10 +15201,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.2291</v>
+        <v>-0.2101</v>
       </c>
       <c r="J319" t="n">
-        <v>-5.9566</v>
+        <v>-5.4626</v>
       </c>
     </row>
     <row r="320">
@@ -15241,10 +15241,10 @@
         <v>0.68</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.3522</v>
+        <v>-0.3371</v>
       </c>
       <c r="J320" t="n">
-        <v>-9.1572</v>
+        <v>-8.7646</v>
       </c>
     </row>
     <row r="321">
@@ -15281,10 +15281,10 @@
         <v>0.5</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.5113</v>
+        <v>-0.5125999999999999</v>
       </c>
       <c r="J321" t="n">
-        <v>-13.2938</v>
+        <v>-13.3276</v>
       </c>
     </row>
     <row r="322">
@@ -15321,10 +15321,10 @@
         <v>1.14</v>
       </c>
       <c r="I322" t="n">
-        <v>0.2589</v>
+        <v>0.2442</v>
       </c>
       <c r="J322" t="n">
-        <v>7.767</v>
+        <v>7.326</v>
       </c>
     </row>
     <row r="323">
@@ -15361,10 +15361,10 @@
         <v>1.06</v>
       </c>
       <c r="I323" t="n">
-        <v>0.1347</v>
+        <v>0.1181</v>
       </c>
       <c r="J323" t="n">
-        <v>4.041</v>
+        <v>3.543</v>
       </c>
     </row>
     <row r="324">
@@ -15401,10 +15401,10 @@
         <v>0.99</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.0247</v>
+        <v>-0.0179</v>
       </c>
       <c r="J324" t="n">
-        <v>-0.741</v>
+        <v>-0.537</v>
       </c>
     </row>
     <row r="325">
@@ -15441,10 +15441,10 @@
         <v>0.89</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.1572</v>
+        <v>-0.1373</v>
       </c>
       <c r="J325" t="n">
-        <v>-4.716</v>
+        <v>-4.119</v>
       </c>
     </row>
     <row r="326">
@@ -15481,10 +15481,10 @@
         <v>0.86</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.1898</v>
+        <v>-0.1693</v>
       </c>
       <c r="J326" t="n">
-        <v>-5.694</v>
+        <v>-5.079</v>
       </c>
     </row>
     <row r="327">
@@ -15521,10 +15521,10 @@
         <v>1.38</v>
       </c>
       <c r="I327" t="n">
-        <v>0.5178</v>
+        <v>0.4489</v>
       </c>
       <c r="J327" t="n">
-        <v>15.534</v>
+        <v>13.467</v>
       </c>
     </row>
     <row r="328">
@@ -15561,10 +15561,10 @@
         <v>1.31</v>
       </c>
       <c r="I328" t="n">
-        <v>0.4395</v>
+        <v>0.3738</v>
       </c>
       <c r="J328" t="n">
-        <v>13.185</v>
+        <v>11.214</v>
       </c>
     </row>
     <row r="329">
@@ -15601,10 +15601,10 @@
         <v>1.02</v>
       </c>
       <c r="I329" t="n">
-        <v>0.0481</v>
+        <v>0.0334</v>
       </c>
       <c r="J329" t="n">
-        <v>1.443</v>
+        <v>1.002</v>
       </c>
     </row>
     <row r="330">
@@ -15641,10 +15641,10 @@
         <v>0.91</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.1427</v>
+        <v>-0.123</v>
       </c>
       <c r="J330" t="n">
-        <v>-4.281</v>
+        <v>-3.69</v>
       </c>
     </row>
     <row r="331">
@@ -15681,10 +15681,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.2499</v>
+        <v>-0.2304</v>
       </c>
       <c r="J331" t="n">
-        <v>-7.497</v>
+        <v>-6.912</v>
       </c>
     </row>
     <row r="332">
@@ -15721,10 +15721,10 @@
         <v>1.65</v>
       </c>
       <c r="I332" t="n">
-        <v>1.2769</v>
+        <v>1.295</v>
       </c>
       <c r="J332" t="n">
-        <v>30.6456</v>
+        <v>31.08</v>
       </c>
     </row>
     <row r="333">
@@ -15761,10 +15761,10 @@
         <v>1.51</v>
       </c>
       <c r="I333" t="n">
-        <v>1.0943</v>
+        <v>1.1065</v>
       </c>
       <c r="J333" t="n">
-        <v>26.2632</v>
+        <v>26.556</v>
       </c>
     </row>
     <row r="334">
@@ -15801,10 +15801,10 @@
         <v>1.37</v>
       </c>
       <c r="I334" t="n">
-        <v>0.8689</v>
+        <v>0.8547</v>
       </c>
       <c r="J334" t="n">
-        <v>20.8536</v>
+        <v>20.5128</v>
       </c>
     </row>
     <row r="335">
@@ -15841,10 +15841,10 @@
         <v>1.15</v>
       </c>
       <c r="I335" t="n">
-        <v>0.4139</v>
+        <v>0.3823</v>
       </c>
       <c r="J335" t="n">
-        <v>9.9336</v>
+        <v>9.1752</v>
       </c>
     </row>
     <row r="336">
@@ -15881,10 +15881,10 @@
         <v>0.96</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.2267</v>
+        <v>-0.1948</v>
       </c>
       <c r="J336" t="n">
-        <v>-5.4408</v>
+        <v>-4.6752</v>
       </c>
     </row>
     <row r="337">
@@ -15921,10 +15921,10 @@
         <v>0.97</v>
       </c>
       <c r="I337" t="n">
-        <v>-0.0227</v>
+        <v>-0.0114</v>
       </c>
       <c r="J337" t="n">
-        <v>-0.5448</v>
+        <v>-0.2736</v>
       </c>
     </row>
     <row r="338">
@@ -15961,10 +15961,10 @@
         <v>0.83</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.1961</v>
+        <v>-0.1806</v>
       </c>
       <c r="J338" t="n">
-        <v>-4.7064</v>
+        <v>-4.3344</v>
       </c>
     </row>
     <row r="339">
@@ -16001,10 +16001,10 @@
         <v>0.63</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.3828</v>
+        <v>-0.3705</v>
       </c>
       <c r="J339" t="n">
-        <v>-9.187200000000001</v>
+        <v>-8.891999999999999</v>
       </c>
     </row>
     <row r="340">
@@ -16041,10 +16041,10 @@
         <v>0.62</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.3918</v>
+        <v>-0.38</v>
       </c>
       <c r="J340" t="n">
-        <v>-9.4032</v>
+        <v>-9.119999999999999</v>
       </c>
     </row>
     <row r="341">
@@ -16081,10 +16081,10 @@
         <v>0.6</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.4096</v>
+        <v>-0.3991</v>
       </c>
       <c r="J341" t="n">
-        <v>-9.830399999999999</v>
+        <v>-9.5784</v>
       </c>
     </row>
     <row r="342">
@@ -16121,10 +16121,10 @@
         <v>1.57</v>
       </c>
       <c r="I342" t="n">
-        <v>1.1748</v>
+        <v>1.1892</v>
       </c>
       <c r="J342" t="n">
-        <v>25.8456</v>
+        <v>26.1624</v>
       </c>
     </row>
     <row r="343">
@@ -16161,10 +16161,10 @@
         <v>1.52</v>
       </c>
       <c r="I343" t="n">
-        <v>1.1089</v>
+        <v>1.1216</v>
       </c>
       <c r="J343" t="n">
-        <v>24.3958</v>
+        <v>24.6752</v>
       </c>
     </row>
     <row r="344">
@@ -16201,10 +16201,10 @@
         <v>1.45</v>
       </c>
       <c r="I344" t="n">
-        <v>1.0103</v>
+        <v>1.0119</v>
       </c>
       <c r="J344" t="n">
-        <v>22.2266</v>
+        <v>22.2618</v>
       </c>
     </row>
     <row r="345">
@@ -16241,10 +16241,10 @@
         <v>1.18</v>
       </c>
       <c r="I345" t="n">
-        <v>0.4848</v>
+        <v>0.4542</v>
       </c>
       <c r="J345" t="n">
-        <v>10.6656</v>
+        <v>9.9924</v>
       </c>
     </row>
     <row r="346">
@@ -16281,10 +16281,10 @@
         <v>0.88</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.4519</v>
+        <v>-0.4146</v>
       </c>
       <c r="J346" t="n">
-        <v>-9.941800000000001</v>
+        <v>-9.1212</v>
       </c>
     </row>
     <row r="347">
@@ -16321,10 +16321,10 @@
         <v>0.93</v>
       </c>
       <c r="I347" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="J347" t="n">
-        <v>-1.8282</v>
+        <v>-1.518</v>
       </c>
     </row>
     <row r="348">
@@ -16361,10 +16361,10 @@
         <v>0.91</v>
       </c>
       <c r="I348" t="n">
-        <v>-0.1083</v>
+        <v>-0.0935</v>
       </c>
       <c r="J348" t="n">
-        <v>-2.3826</v>
+        <v>-2.057</v>
       </c>
     </row>
     <row r="349">
@@ -16401,10 +16401,10 @@
         <v>0.67</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.3488</v>
+        <v>-0.3345</v>
       </c>
       <c r="J349" t="n">
-        <v>-7.6736</v>
+        <v>-7.359</v>
       </c>
     </row>
     <row r="350">
@@ -16441,10 +16441,10 @@
         <v>0.65</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.3668</v>
+        <v>-0.3534</v>
       </c>
       <c r="J350" t="n">
-        <v>-8.069599999999999</v>
+        <v>-7.7748</v>
       </c>
     </row>
     <row r="351">
@@ -16481,10 +16481,10 @@
         <v>0.57</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.4382</v>
+        <v>-0.43</v>
       </c>
       <c r="J351" t="n">
-        <v>-9.6404</v>
+        <v>-9.460000000000001</v>
       </c>
     </row>
   </sheetData>
